--- a/EQE/Plots/best Voc JVs.xlsx
+++ b/EQE/Plots/best Voc JVs.xlsx
@@ -413,48 +413,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I151"/>
+  <dimension ref="A1:I201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>V_Mo_200Sb_25Se_13</t>
+          <t>V_CdS1_10</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>J_Mo_200Sb_25Se_13</t>
+          <t>J_CdS1_10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>V_Mo_300Sb_35Se_12</t>
+          <t>V_CdS2_2</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>J_Mo_300Sb_35Se_12</t>
+          <t>J_CdS2_2</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>V_Mo_400Sb_30Se_11</t>
+          <t>V_CdS3_6</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>J_Mo_400Sb_30Se_11</t>
+          <t>J_CdS3_6</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>V_Mo_400deg_400Sb_35Se_2</t>
+          <t>V_2_CdS3_21</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>J_Mo_400deg_400Sb_35Se_2</t>
+          <t>J_2_CdS3_21</t>
         </is>
       </c>
     </row>
@@ -466,25 +466,25 @@
         <v>-0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>-14.94475528358725</v>
+        <v>-5.987042395001961</v>
       </c>
       <c r="D2" t="n">
         <v>-0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>-24.13399942939242</v>
+        <v>-12.85647183961906</v>
       </c>
       <c r="F2" t="n">
         <v>-0.1</v>
       </c>
       <c r="G2" t="n">
-        <v>-15.67587975552999</v>
+        <v>-24.01418143766559</v>
       </c>
       <c r="H2" t="n">
         <v>-0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>-5.554813910759389</v>
+        <v>-12.43638074931563</v>
       </c>
     </row>
     <row r="3">
@@ -492,28 +492,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.0953</v>
+        <v>-0.097</v>
       </c>
       <c r="C3" t="n">
-        <v>-14.94011749944744</v>
+        <v>-5.954385466545786</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0953</v>
+        <v>-0.097</v>
       </c>
       <c r="E3" t="n">
-        <v>-24.11857453936321</v>
+        <v>-12.80828871723049</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0953</v>
+        <v>-0.097</v>
       </c>
       <c r="G3" t="n">
-        <v>-15.55606341071186</v>
+        <v>-24.00181025620344</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0953</v>
+        <v>-0.09445000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-5.501131470410666</v>
+        <v>-12.43021063441953</v>
       </c>
     </row>
     <row r="4">
@@ -521,28 +521,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0906</v>
+        <v>-0.09395000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>-14.92015486336736</v>
+        <v>-5.958788647910663</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0906</v>
+        <v>-0.09395000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-24.08555986245858</v>
+        <v>-12.76791493565278</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0906</v>
+        <v>-0.09395000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-15.42906912818572</v>
+        <v>-24.00352847585097</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0906</v>
+        <v>-0.08895</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.447023654147928</v>
+        <v>-12.42052698187428</v>
       </c>
     </row>
     <row r="5">
@@ -550,28 +550,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0859</v>
+        <v>-0.09095</v>
       </c>
       <c r="C5" t="n">
-        <v>-14.90200701238547</v>
+        <v>-5.955027597161497</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0859</v>
+        <v>-0.09095</v>
       </c>
       <c r="E5" t="n">
-        <v>-24.04135988518188</v>
+        <v>-12.73111405509964</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0859</v>
+        <v>-0.09095</v>
       </c>
       <c r="G5" t="n">
-        <v>-15.29728955385426</v>
+        <v>-23.98668992330527</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0859</v>
+        <v>-0.0834</v>
       </c>
       <c r="I5" t="n">
-        <v>-5.391044183863522</v>
+        <v>-12.41675635610444</v>
       </c>
     </row>
     <row r="6">
@@ -579,28 +579,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.08795</v>
       </c>
       <c r="C6" t="n">
-        <v>-14.88143944793932</v>
+        <v>-5.944753507310115</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.08795</v>
       </c>
       <c r="E6" t="n">
-        <v>-24.01041990108819</v>
+        <v>-12.68844340857756</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.08795</v>
       </c>
       <c r="G6" t="n">
-        <v>-15.16182898582639</v>
+        <v>-23.96280667020475</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.0779</v>
       </c>
       <c r="I6" t="n">
-        <v>-5.332895296417639</v>
+        <v>-12.40587295899606</v>
       </c>
     </row>
     <row r="7">
@@ -608,28 +608,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.0765</v>
+        <v>-0.0849</v>
       </c>
       <c r="C7" t="n">
-        <v>-14.86450145368956</v>
+        <v>-5.933929019788126</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0765</v>
+        <v>-0.0849</v>
       </c>
       <c r="E7" t="n">
-        <v>-24.00248194598544</v>
+        <v>-12.64255715113336</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0765</v>
+        <v>-0.0849</v>
       </c>
       <c r="G7" t="n">
-        <v>-15.03600035130412</v>
+        <v>-23.95387192803765</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0765</v>
+        <v>-0.07235</v>
       </c>
       <c r="I7" t="n">
-        <v>-5.27763896518706</v>
+        <v>-12.39533234604857</v>
       </c>
     </row>
     <row r="8">
@@ -637,28 +637,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.0718</v>
+        <v>-0.0819</v>
       </c>
       <c r="C8" t="n">
-        <v>-14.83304517865428</v>
+        <v>-5.919802146242477</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0718</v>
+        <v>-0.0819</v>
       </c>
       <c r="E8" t="n">
-        <v>-23.96964767715133</v>
+        <v>-12.60376565429511</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0718</v>
+        <v>-0.0819</v>
       </c>
       <c r="G8" t="n">
-        <v>-14.89495694283669</v>
+        <v>-23.93789248531571</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0718</v>
+        <v>-0.06685000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.220170679203601</v>
+        <v>-12.38410616477929</v>
       </c>
     </row>
     <row r="9">
@@ -666,28 +666,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.0789</v>
       </c>
       <c r="C9" t="n">
-        <v>-14.81106611468732</v>
+        <v>-5.903015017288881</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.0789</v>
       </c>
       <c r="E9" t="n">
-        <v>-23.92427504741627</v>
+        <v>-12.57002726033446</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.0789</v>
       </c>
       <c r="G9" t="n">
-        <v>-14.75685832932639</v>
+        <v>-23.91864842526349</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.0613</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.165552411844045</v>
+        <v>-12.36268215472341</v>
       </c>
     </row>
     <row r="10">
@@ -695,28 +695,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0624</v>
+        <v>-0.0759</v>
       </c>
       <c r="C10" t="n">
-        <v>-14.80078233246425</v>
+        <v>-5.878889252727157</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0624</v>
+        <v>-0.0759</v>
       </c>
       <c r="E10" t="n">
-        <v>-23.88801302524233</v>
+        <v>-12.53072534906413</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0624</v>
+        <v>-0.0759</v>
       </c>
       <c r="G10" t="n">
-        <v>-14.62906649816604</v>
+        <v>-23.87414653639273</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0624</v>
+        <v>-0.0558</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.107743825129373</v>
+        <v>-12.34897078828765</v>
       </c>
     </row>
     <row r="11">
@@ -724,28 +724,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0577</v>
+        <v>-0.07285</v>
       </c>
       <c r="C11" t="n">
-        <v>-14.75863898962853</v>
+        <v>-5.854396556385026</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0577</v>
+        <v>-0.07285</v>
       </c>
       <c r="E11" t="n">
-        <v>-23.84597794481184</v>
+        <v>-12.48050056894723</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0577</v>
+        <v>-0.07285</v>
       </c>
       <c r="G11" t="n">
-        <v>-14.48992493644175</v>
+        <v>-23.84115671916035</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0577</v>
+        <v>-0.05025</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.051041215791142</v>
+        <v>-12.33003196339826</v>
       </c>
     </row>
     <row r="12">
@@ -753,28 +753,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.053</v>
+        <v>-0.06985</v>
       </c>
       <c r="C12" t="n">
-        <v>-14.73020735642356</v>
+        <v>-5.831279854219419</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.053</v>
+        <v>-0.06985</v>
       </c>
       <c r="E12" t="n">
-        <v>-23.8034016401698</v>
+        <v>-12.43155182491053</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.053</v>
+        <v>-0.06985</v>
       </c>
       <c r="G12" t="n">
-        <v>-14.34507783448803</v>
+        <v>-23.82672367412118</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.053</v>
+        <v>-0.0447</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.990595298409577</v>
+        <v>-12.32420463266306</v>
       </c>
     </row>
     <row r="13">
@@ -782,28 +782,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0483</v>
+        <v>-0.06685000000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>-14.70439707947154</v>
+        <v>-5.802750908292817</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0483</v>
+        <v>-0.06685000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-23.75757799025846</v>
+        <v>-12.38954471715016</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0483</v>
+        <v>-0.06685000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-14.20612032244857</v>
+        <v>-23.81813257588358</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0483</v>
+        <v>-0.0392</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.936827782878051</v>
+        <v>-12.30055252556137</v>
       </c>
     </row>
     <row r="14">
@@ -811,28 +811,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.0436</v>
+        <v>-0.0638</v>
       </c>
       <c r="C14" t="n">
-        <v>-14.67616708905527</v>
+        <v>-5.775689689487842</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0436</v>
+        <v>-0.0638</v>
       </c>
       <c r="E14" t="n">
-        <v>-23.72681841423529</v>
+        <v>-12.33952410280609</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0436</v>
+        <v>-0.0638</v>
       </c>
       <c r="G14" t="n">
-        <v>-14.06452476492668</v>
+        <v>-23.79974762565512</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0436</v>
+        <v>-0.03365</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.878678895432167</v>
+        <v>-12.28829799180941</v>
       </c>
     </row>
     <row r="15">
@@ -840,28 +840,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.03895</v>
+        <v>-0.0608</v>
       </c>
       <c r="C15" t="n">
-        <v>-14.64370260007655</v>
+        <v>-5.752114322596726</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.03895</v>
+        <v>-0.0608</v>
       </c>
       <c r="E15" t="n">
-        <v>-23.67828864326618</v>
+        <v>-12.29608783463588</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.03895</v>
+        <v>-0.0608</v>
       </c>
       <c r="G15" t="n">
-        <v>-13.93121144322171</v>
+        <v>-23.80936965568123</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.03895</v>
+        <v>-0.02815</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.816276248846132</v>
+        <v>-12.27655763429879</v>
       </c>
     </row>
     <row r="16">
@@ -869,28 +869,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.03425</v>
+        <v>-0.0578</v>
       </c>
       <c r="C16" t="n">
-        <v>-14.60135761445214</v>
+        <v>-5.725328302627054</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.03425</v>
+        <v>-0.0578</v>
       </c>
       <c r="E16" t="n">
-        <v>-23.64040294845758</v>
+        <v>-12.25372343677305</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.03425</v>
+        <v>-0.0578</v>
       </c>
       <c r="G16" t="n">
-        <v>-13.78538274294895</v>
+        <v>-23.78754826615774</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.03425</v>
+        <v>-0.0226</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.758127361400249</v>
+        <v>-12.26224639558146</v>
       </c>
     </row>
     <row r="17">
@@ -898,28 +898,28 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.02955</v>
+        <v>-0.05475</v>
       </c>
       <c r="C17" t="n">
-        <v>-14.57837033654174</v>
+        <v>-5.696248959029844</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.02955</v>
+        <v>-0.05475</v>
       </c>
       <c r="E17" t="n">
-        <v>-23.59178297345322</v>
+        <v>-12.21064445870531</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.02955</v>
+        <v>-0.05475</v>
       </c>
       <c r="G17" t="n">
-        <v>-13.64967677534132</v>
+        <v>-23.76589869859898</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.02955</v>
+        <v>-0.0171</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.702488191847056</v>
+        <v>-12.24793515686414</v>
       </c>
     </row>
     <row r="18">
@@ -927,28 +927,28 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.02485</v>
+        <v>-0.05175</v>
       </c>
       <c r="C18" t="n">
-        <v>-14.54671241871778</v>
+        <v>-5.659280582153893</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.02485</v>
+        <v>-0.05175</v>
       </c>
       <c r="E18" t="n">
-        <v>-23.55479931899721</v>
+        <v>-12.16123634167974</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.02485</v>
+        <v>-0.05175</v>
       </c>
       <c r="G18" t="n">
-        <v>-13.50532047254712</v>
+        <v>-23.73771989637966</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.02485</v>
+        <v>-0.01155</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.641872124099885</v>
+        <v>-12.25384818363956</v>
       </c>
     </row>
     <row r="19">
@@ -956,28 +956,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.02015</v>
+        <v>-0.04875</v>
       </c>
       <c r="C19" t="n">
-        <v>-14.51747421435806</v>
+        <v>-5.634512686976457</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.02015</v>
+        <v>-0.04875</v>
       </c>
       <c r="E19" t="n">
-        <v>-23.50175934626518</v>
+        <v>-12.11004177414188</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.02015</v>
+        <v>-0.04875</v>
       </c>
       <c r="G19" t="n">
-        <v>-13.35771262532109</v>
+        <v>-23.73479892297888</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.02015</v>
+        <v>-0.00605</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.584106074976615</v>
+        <v>-12.2343094864686</v>
       </c>
     </row>
     <row r="20">
@@ -985,28 +985,28 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.01545</v>
+        <v>-0.04575</v>
       </c>
       <c r="C20" t="n">
-        <v>-14.47996865566216</v>
+        <v>-5.605616809269447</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.01545</v>
+        <v>-0.04575</v>
       </c>
       <c r="E20" t="n">
-        <v>-23.45837120530581</v>
+        <v>-12.07370026657762</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.01545</v>
+        <v>-0.04575</v>
       </c>
       <c r="G20" t="n">
-        <v>-13.20660783408348</v>
+        <v>-23.72380231723475</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.01545</v>
+        <v>-0.0005</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.52446837183168</v>
+        <v>-12.2186271111077</v>
       </c>
     </row>
     <row r="21">
@@ -1014,28 +1014,28 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.01075</v>
+        <v>-0.0427</v>
       </c>
       <c r="C21" t="n">
-        <v>-14.45173866524588</v>
+        <v>-5.570850023075937</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.01075</v>
+        <v>-0.0427</v>
       </c>
       <c r="E21" t="n">
-        <v>-23.40415858011541</v>
+        <v>-12.02648693161</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.01075</v>
+        <v>-0.0427</v>
       </c>
       <c r="G21" t="n">
-        <v>-13.05004290219619</v>
+        <v>-23.69613898090968</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.01075</v>
+        <v>0.00505</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.466404559568599</v>
+        <v>-12.19488930796579</v>
       </c>
     </row>
     <row r="22">
@@ -1043,28 +1043,28 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.00605</v>
+        <v>-0.0397</v>
       </c>
       <c r="C22" t="n">
-        <v>-14.41141010750834</v>
+        <v>-5.543880537216062</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.00605</v>
+        <v>-0.0397</v>
       </c>
       <c r="E22" t="n">
-        <v>-23.35671125756941</v>
+        <v>-11.97605798572027</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.00605</v>
+        <v>-0.0397</v>
       </c>
       <c r="G22" t="n">
-        <v>-12.90268045454992</v>
+        <v>-23.67586398906895</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.00605</v>
+        <v>0.01055</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.405831029412829</v>
+        <v>-12.17680744347863</v>
       </c>
     </row>
     <row r="23">
@@ -1072,28 +1072,28 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.00135</v>
+        <v>-0.0367</v>
       </c>
       <c r="C23" t="n">
-        <v>-14.38076040362782</v>
+        <v>-5.507095626230314</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.00135</v>
+        <v>-0.0367</v>
       </c>
       <c r="E23" t="n">
-        <v>-23.29997291939178</v>
+        <v>-11.93798106908693</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.00135</v>
+        <v>-0.0367</v>
       </c>
       <c r="G23" t="n">
-        <v>-12.74899896772482</v>
+        <v>-23.67019386423213</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.00135</v>
+        <v>0.0161</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.347724679558348</v>
+        <v>-12.16001101959482</v>
       </c>
     </row>
     <row r="24">
@@ -1101,28 +1101,28 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.00335</v>
+        <v>-0.03365</v>
       </c>
       <c r="C24" t="n">
-        <v>-14.34890084301516</v>
+        <v>-5.471870175311294</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00335</v>
+        <v>-0.03365</v>
       </c>
       <c r="E24" t="n">
-        <v>-23.25496110579776</v>
+        <v>-11.90015935966963</v>
       </c>
       <c r="F24" t="n">
-        <v>0.00335</v>
+        <v>-0.03365</v>
       </c>
       <c r="G24" t="n">
-        <v>-12.59746472722263</v>
+        <v>-23.64802883077913</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00335</v>
+        <v>0.0216</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.284471281144282</v>
+        <v>-12.14595686899817</v>
       </c>
     </row>
     <row r="25">
@@ -1130,28 +1130,28 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.00805</v>
+        <v>-0.03065</v>
       </c>
       <c r="C25" t="n">
-        <v>-14.30232135882831</v>
+        <v>-5.438295917404103</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00805</v>
+        <v>-0.03065</v>
       </c>
       <c r="E25" t="n">
-        <v>-23.19515583042133</v>
+        <v>-11.85075124264406</v>
       </c>
       <c r="F25" t="n">
-        <v>0.00805</v>
+        <v>-0.03065</v>
       </c>
       <c r="G25" t="n">
-        <v>-12.44513293808621</v>
+        <v>-23.62826930483265</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00805</v>
+        <v>0.02715</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.224748502816542</v>
+        <v>-12.13447359960822</v>
       </c>
     </row>
     <row r="26">
@@ -1159,28 +1159,28 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01275</v>
+        <v>-0.02765</v>
       </c>
       <c r="C26" t="n">
-        <v>-14.26017801599259</v>
+        <v>-5.40453819360671</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01275</v>
+        <v>-0.02765</v>
       </c>
       <c r="E26" t="n">
-        <v>-23.14861054822792</v>
+        <v>-11.80348686623324</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01275</v>
+        <v>-0.02765</v>
       </c>
       <c r="G26" t="n">
-        <v>-12.29703429170066</v>
+        <v>-23.61933456266555</v>
       </c>
       <c r="H26" t="n">
-        <v>0.01275</v>
+        <v>0.03265</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.162345856230506</v>
+        <v>-12.11493490243726</v>
       </c>
     </row>
     <row r="27">
@@ -1188,28 +1188,28 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.01745</v>
+        <v>-0.0246</v>
       </c>
       <c r="C27" t="n">
-        <v>-14.21380017459442</v>
+        <v>-5.368945810907283</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01745</v>
+        <v>-0.0246</v>
       </c>
       <c r="E27" t="n">
-        <v>-23.08907588495727</v>
+        <v>-11.74611628406719</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01745</v>
+        <v>-0.0246</v>
       </c>
       <c r="G27" t="n">
-        <v>-12.13230982378633</v>
+        <v>-23.59527948760027</v>
       </c>
       <c r="H27" t="n">
-        <v>0.01745</v>
+        <v>0.0382</v>
       </c>
       <c r="I27" t="n">
-        <v>-4.099262608182046</v>
+        <v>-12.09693873399032</v>
       </c>
     </row>
     <row r="28">
@@ -1217,28 +1217,28 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.02215</v>
+        <v>-0.0216</v>
       </c>
       <c r="C28" t="n">
-        <v>-14.17266504570213</v>
+        <v>-5.333628627043161</v>
       </c>
       <c r="D28" t="n">
-        <v>0.02215</v>
+        <v>-0.0216</v>
       </c>
       <c r="E28" t="n">
-        <v>-23.02863918133403</v>
+        <v>-11.70303730599944</v>
       </c>
       <c r="F28" t="n">
-        <v>0.02215</v>
+        <v>-0.0216</v>
       </c>
       <c r="G28" t="n">
-        <v>-11.97451789400024</v>
+        <v>-23.57741000326607</v>
       </c>
       <c r="H28" t="n">
-        <v>0.02215</v>
+        <v>0.0437</v>
       </c>
       <c r="I28" t="n">
-        <v>-4.037455487875633</v>
+        <v>-12.07714294869869</v>
       </c>
     </row>
     <row r="29">
@@ -1246,28 +1246,28 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.02685</v>
+        <v>-0.0186</v>
       </c>
       <c r="C29" t="n">
-        <v>-14.13677262931573</v>
+        <v>-5.298127977288837</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02685</v>
+        <v>-0.0186</v>
       </c>
       <c r="E29" t="n">
-        <v>-22.97623063684881</v>
+        <v>-11.65347606464425</v>
       </c>
       <c r="F29" t="n">
-        <v>0.02685</v>
+        <v>-0.0186</v>
       </c>
       <c r="G29" t="n">
-        <v>-11.811756622724</v>
+        <v>-23.56039962875562</v>
       </c>
       <c r="H29" t="n">
-        <v>0.02685</v>
+        <v>0.04925</v>
       </c>
       <c r="I29" t="n">
-        <v>-3.973606563181946</v>
+        <v>-12.06283170998137</v>
       </c>
     </row>
     <row r="30">
@@ -1275,28 +1275,28 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.03155</v>
+        <v>-0.0156</v>
       </c>
       <c r="C30" t="n">
-        <v>-14.09745228552163</v>
+        <v>-5.267489173624898</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03155</v>
+        <v>-0.0156</v>
       </c>
       <c r="E30" t="n">
-        <v>-22.89603924950395</v>
+        <v>-11.61218353708878</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03155</v>
+        <v>-0.0156</v>
       </c>
       <c r="G30" t="n">
-        <v>-11.64850455228823</v>
+        <v>-23.52689434562898</v>
       </c>
       <c r="H30" t="n">
-        <v>0.03155</v>
+        <v>0.05475</v>
       </c>
       <c r="I30" t="n">
-        <v>-3.914862149456441</v>
+        <v>-12.03986517120147</v>
       </c>
     </row>
     <row r="31">
@@ -1304,28 +1304,28 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.03625</v>
+        <v>-0.01255</v>
       </c>
       <c r="C31" t="n">
-        <v>-14.05087280133478</v>
+        <v>-5.230704262639151</v>
       </c>
       <c r="D31" t="n">
-        <v>0.03625</v>
+        <v>-0.01255</v>
       </c>
       <c r="E31" t="n">
-        <v>-22.85003519152209</v>
+        <v>-11.55853898027694</v>
       </c>
       <c r="F31" t="n">
-        <v>0.03625</v>
+        <v>-0.01255</v>
       </c>
       <c r="G31" t="n">
-        <v>-11.49482306546312</v>
+        <v>-23.50730664164726</v>
       </c>
       <c r="H31" t="n">
-        <v>0.03625</v>
+        <v>0.0603</v>
       </c>
       <c r="I31" t="n">
-        <v>-3.853437867472641</v>
+        <v>-12.0264965889266</v>
       </c>
     </row>
     <row r="32">
@@ -1333,28 +1333,28 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0.04095</v>
+        <v>-0.009549999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>-14.00691467340086</v>
+        <v>-5.194561482269115</v>
       </c>
       <c r="D32" t="n">
-        <v>0.04095</v>
+        <v>-0.009549999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-22.77236951716446</v>
+        <v>-11.50744649562549</v>
       </c>
       <c r="F32" t="n">
-        <v>0.04095</v>
+        <v>-0.009549999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>-11.32770595164613</v>
+        <v>-23.50387020235222</v>
       </c>
       <c r="H32" t="n">
-        <v>0.04095</v>
+        <v>0.06585000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>-3.792098660671643</v>
+        <v>-12.01578458389866</v>
       </c>
     </row>
     <row r="33">
@@ -1362,28 +1362,28 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0.04565</v>
+        <v>-0.00655</v>
       </c>
       <c r="C33" t="n">
-        <v>-13.97485346999952</v>
+        <v>-5.154749384095013</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04565</v>
+        <v>-0.00655</v>
       </c>
       <c r="E33" t="n">
-        <v>-22.70074751316917</v>
+        <v>-11.45895712457767</v>
       </c>
       <c r="F33" t="n">
-        <v>0.04565</v>
+        <v>-0.00655</v>
       </c>
       <c r="G33" t="n">
-        <v>-11.16905512333088</v>
+        <v>-23.47655050995666</v>
       </c>
       <c r="H33" t="n">
-        <v>0.04565</v>
+        <v>0.07135</v>
       </c>
       <c r="I33" t="n">
-        <v>-3.728292273569358</v>
+        <v>-11.98921881142937</v>
       </c>
     </row>
     <row r="34">
@@ -1391,28 +1391,28 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>0.05035</v>
+        <v>-0.0035</v>
       </c>
       <c r="C34" t="n">
-        <v>-13.93391998389592</v>
+        <v>-5.118606603724977</v>
       </c>
       <c r="D34" t="n">
-        <v>0.05035</v>
+        <v>-0.0035</v>
       </c>
       <c r="E34" t="n">
-        <v>-22.6299373454912</v>
+        <v>-11.41327503290631</v>
       </c>
       <c r="F34" t="n">
-        <v>0.05035</v>
+        <v>-0.0035</v>
       </c>
       <c r="G34" t="n">
-        <v>-10.99807296613265</v>
+        <v>-23.44373251468903</v>
       </c>
       <c r="H34" t="n">
-        <v>0.05035</v>
+        <v>0.0769</v>
       </c>
       <c r="I34" t="n">
-        <v>-3.665591863843511</v>
+        <v>-11.97490757271205</v>
       </c>
     </row>
     <row r="35">
@@ -1420,28 +1420,28 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>0.05505</v>
+        <v>-0.0005</v>
       </c>
       <c r="C35" t="n">
-        <v>-13.8901634987507</v>
+        <v>-5.085857942323702</v>
       </c>
       <c r="D35" t="n">
-        <v>0.05505</v>
+        <v>-0.0005</v>
       </c>
       <c r="E35" t="n">
-        <v>-22.54207861514936</v>
+        <v>-11.35835444001425</v>
       </c>
       <c r="F35" t="n">
-        <v>0.05505</v>
+        <v>-0.0005</v>
       </c>
       <c r="G35" t="n">
-        <v>-10.82966750452191</v>
+        <v>-23.42156748123602</v>
       </c>
       <c r="H35" t="n">
-        <v>0.05505</v>
+        <v>0.0824</v>
       </c>
       <c r="I35" t="n">
-        <v>-3.599190683665733</v>
+        <v>-11.94499965467404</v>
       </c>
     </row>
     <row r="36">
@@ -1449,28 +1449,28 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>0.05975</v>
+        <v>0.0025</v>
       </c>
       <c r="C36" t="n">
-        <v>-13.85548093909642</v>
+        <v>-5.024305136160518</v>
       </c>
       <c r="D36" t="n">
-        <v>0.05975</v>
+        <v>0.0025</v>
       </c>
       <c r="E36" t="n">
-        <v>-22.46378151254493</v>
+        <v>-11.31185568525155</v>
       </c>
       <c r="F36" t="n">
-        <v>0.05975</v>
+        <v>0.0025</v>
       </c>
       <c r="G36" t="n">
-        <v>-10.65966694564272</v>
+        <v>-23.41710011015247</v>
       </c>
       <c r="H36" t="n">
-        <v>0.05975</v>
+        <v>0.08795</v>
       </c>
       <c r="I36" t="n">
-        <v>-3.539255217380986</v>
+        <v>-11.92049058717012</v>
       </c>
     </row>
     <row r="37">
@@ -1478,28 +1478,28 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>0.06444999999999999</v>
+        <v>0.00555</v>
       </c>
       <c r="C37" t="n">
-        <v>-13.80769159817744</v>
+        <v>-5.002656161116537</v>
       </c>
       <c r="D37" t="n">
-        <v>0.06444999999999999</v>
+        <v>0.00555</v>
       </c>
       <c r="E37" t="n">
-        <v>-22.38755910275145</v>
+        <v>-11.26290694121486</v>
       </c>
       <c r="F37" t="n">
-        <v>0.06444999999999999</v>
+        <v>0.00555</v>
       </c>
       <c r="G37" t="n">
-        <v>-10.497396473526</v>
+        <v>-23.39682511831174</v>
       </c>
       <c r="H37" t="n">
-        <v>0.06444999999999999</v>
+        <v>0.09345000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-3.475661518235708</v>
+        <v>-11.90994997422263</v>
       </c>
     </row>
     <row r="38">
@@ -1507,28 +1507,28 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>0.06915</v>
+        <v>0.00855</v>
       </c>
       <c r="C38" t="n">
-        <v>-13.76373347024352</v>
+        <v>-4.970457897385871</v>
       </c>
       <c r="D38" t="n">
-        <v>0.06915</v>
+        <v>0.00855</v>
       </c>
       <c r="E38" t="n">
-        <v>-22.2905897648485</v>
+        <v>-11.21508110892874</v>
       </c>
       <c r="F38" t="n">
-        <v>0.06915</v>
+        <v>0.00855</v>
       </c>
       <c r="G38" t="n">
-        <v>-10.32678241569742</v>
+        <v>-23.37569101664725</v>
       </c>
       <c r="H38" t="n">
-        <v>0.06915</v>
+        <v>0.099</v>
       </c>
       <c r="I38" t="n">
-        <v>-3.412535732595846</v>
+        <v>-11.89298215825838</v>
       </c>
     </row>
     <row r="39">
@@ -1536,28 +1536,28 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>0.07385</v>
+        <v>0.01155</v>
       </c>
       <c r="C39" t="n">
-        <v>-13.72340491250599</v>
+        <v>-4.936516707698273</v>
       </c>
       <c r="D39" t="n">
-        <v>0.07385</v>
+        <v>0.01155</v>
       </c>
       <c r="E39" t="n">
-        <v>-22.19064369378201</v>
+        <v>-11.17348233271403</v>
       </c>
       <c r="F39" t="n">
-        <v>0.07385</v>
+        <v>0.01155</v>
       </c>
       <c r="G39" t="n">
-        <v>-10.14457322772514</v>
+        <v>-23.35060500979346</v>
       </c>
       <c r="H39" t="n">
-        <v>0.07385</v>
+        <v>0.1045</v>
       </c>
       <c r="I39" t="n">
-        <v>-3.345411413364242</v>
+        <v>-11.87052979571982</v>
       </c>
     </row>
     <row r="40">
@@ -1565,28 +1565,28 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0785</v>
+        <v>0.01455</v>
       </c>
       <c r="C40" t="n">
-        <v>-13.66291207589968</v>
+        <v>-4.896429410688868</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0785</v>
+        <v>0.01455</v>
       </c>
       <c r="E40" t="n">
-        <v>-22.0951176204432</v>
+        <v>-11.12203255796014</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0785</v>
+        <v>0.01455</v>
       </c>
       <c r="G40" t="n">
-        <v>-9.96475668565553</v>
+        <v>-23.32002070006761</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0785</v>
+        <v>0.11005</v>
       </c>
       <c r="I40" t="n">
-        <v>-3.284625195251464</v>
+        <v>-11.84679199257791</v>
       </c>
     </row>
     <row r="41">
@@ -1594,28 +1594,28 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>0.0832</v>
+        <v>0.0176</v>
       </c>
       <c r="C41" t="n">
-        <v>-13.59516009890062</v>
+        <v>-4.856525579569666</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0832</v>
+        <v>0.0176</v>
       </c>
       <c r="E41" t="n">
-        <v>-21.99499114130619</v>
+        <v>-11.06491718301012</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0832</v>
+        <v>0.0176</v>
       </c>
       <c r="G41" t="n">
-        <v>-9.797516872048654</v>
+        <v>-23.32173891971512</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0832</v>
+        <v>0.1156</v>
       </c>
       <c r="I41" t="n">
-        <v>-3.219670293181338</v>
+        <v>-11.81662698641923</v>
       </c>
     </row>
     <row r="42">
@@ -1623,28 +1623,28 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0206</v>
       </c>
       <c r="C42" t="n">
-        <v>-13.5497904714459</v>
+        <v>-4.816530015505362</v>
       </c>
       <c r="D42" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0206</v>
       </c>
       <c r="E42" t="n">
-        <v>-21.88656589092541</v>
+        <v>-11.01673406062155</v>
       </c>
       <c r="F42" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0206</v>
       </c>
       <c r="G42" t="n">
-        <v>-9.623651269788239</v>
+        <v>-23.28565630711721</v>
       </c>
       <c r="H42" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.1211</v>
       </c>
       <c r="I42" t="n">
-        <v>-3.157012421046893</v>
+        <v>-11.79366044763933</v>
       </c>
     </row>
     <row r="43">
@@ -1652,28 +1652,28 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>0.0926</v>
+        <v>0.0236</v>
       </c>
       <c r="C43" t="n">
-        <v>-13.49796827475316</v>
+        <v>-4.780295502190224</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0926</v>
+        <v>0.0236</v>
       </c>
       <c r="E43" t="n">
-        <v>-21.77155574597074</v>
+        <v>-10.96548845164049</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0926</v>
+        <v>0.0236</v>
       </c>
       <c r="G43" t="n">
-        <v>-9.443343928559107</v>
+        <v>-23.25558746328561</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0926</v>
+        <v>0.12665</v>
       </c>
       <c r="I43" t="n">
-        <v>-3.090398552912107</v>
+        <v>-11.76478088208401</v>
       </c>
     </row>
     <row r="44">
@@ -1681,28 +1681,28 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>0.0973</v>
+        <v>0.02665</v>
       </c>
       <c r="C44" t="n">
-        <v>-13.44816250594731</v>
+        <v>-4.74195113113775</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0973</v>
+        <v>0.02665</v>
       </c>
       <c r="E44" t="n">
-        <v>-21.64247377151575</v>
+        <v>-10.91648866616059</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0973</v>
+        <v>0.02665</v>
       </c>
       <c r="G44" t="n">
-        <v>-9.257392396995483</v>
+        <v>-23.25146373613157</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0973</v>
+        <v>0.13215</v>
       </c>
       <c r="I44" t="n">
-        <v>-3.019658538411373</v>
+        <v>-11.73195929867841</v>
       </c>
     </row>
     <row r="45">
@@ -1710,28 +1710,28 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>0.102</v>
+        <v>0.02965</v>
       </c>
       <c r="C45" t="n">
-        <v>-13.3910975967487</v>
+        <v>-4.702322498853852</v>
       </c>
       <c r="D45" t="n">
-        <v>0.102</v>
+        <v>0.02965</v>
       </c>
       <c r="E45" t="n">
-        <v>-21.53431913324073</v>
+        <v>-10.85967953986983</v>
       </c>
       <c r="F45" t="n">
-        <v>0.102</v>
+        <v>0.02965</v>
       </c>
       <c r="G45" t="n">
-        <v>-9.075183209023207</v>
+        <v>-23.20782095708457</v>
       </c>
       <c r="H45" t="n">
-        <v>0.102</v>
+        <v>0.1377</v>
       </c>
       <c r="I45" t="n">
-        <v>-2.95427826042723</v>
+        <v>-11.70136581231862</v>
       </c>
     </row>
     <row r="46">
@@ -1739,28 +1739,28 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>0.1067</v>
+        <v>0.03265</v>
       </c>
       <c r="C46" t="n">
-        <v>-13.32798340388945</v>
+        <v>-4.668014377385848</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1067</v>
+        <v>0.03265</v>
       </c>
       <c r="E46" t="n">
-        <v>-21.39603634718936</v>
+        <v>-10.80955684263934</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1067</v>
+        <v>0.03265</v>
       </c>
       <c r="G46" t="n">
-        <v>-8.883832886704846</v>
+        <v>-23.18325041612503</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1067</v>
+        <v>0.1432</v>
       </c>
       <c r="I46" t="n">
-        <v>-2.884771836077141</v>
+        <v>-11.6652020833443</v>
       </c>
     </row>
     <row r="47">
@@ -1768,28 +1768,28 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>0.1114</v>
+        <v>0.0357</v>
       </c>
       <c r="C47" t="n">
-        <v>-13.26708728170577</v>
+        <v>-4.631321199345202</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1114</v>
+        <v>0.0357</v>
       </c>
       <c r="E47" t="n">
-        <v>-21.25622009253859</v>
+        <v>-10.76392579241118</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1114</v>
+        <v>0.0357</v>
       </c>
       <c r="G47" t="n">
-        <v>-8.696961106717117</v>
+        <v>-23.16469364393182</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1114</v>
+        <v>0.14875</v>
       </c>
       <c r="I47" t="n">
-        <v>-2.819731858824211</v>
+        <v>-11.63263758805937</v>
       </c>
     </row>
     <row r="48">
@@ -1797,28 +1797,28 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1161</v>
+        <v>0.0387</v>
       </c>
       <c r="C48" t="n">
-        <v>-13.20820758740897</v>
+        <v>-4.593068561237829</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1161</v>
+        <v>0.0387</v>
       </c>
       <c r="E48" t="n">
-        <v>-21.1188393468398</v>
+        <v>-10.70732083189325</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1161</v>
+        <v>0.0387</v>
       </c>
       <c r="G48" t="n">
-        <v>-8.49855554648064</v>
+        <v>-23.16211631446054</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1161</v>
+        <v>0.15425</v>
       </c>
       <c r="I48" t="n">
-        <v>-2.753926204926053</v>
+        <v>-11.60718586411299</v>
       </c>
     </row>
     <row r="49">
@@ -1826,28 +1826,28 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1208</v>
+        <v>0.0417</v>
       </c>
       <c r="C49" t="n">
-        <v>-13.13964903925516</v>
+        <v>-4.553715127789236</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1208</v>
+        <v>0.0417</v>
       </c>
       <c r="E49" t="n">
-        <v>-20.99417737011247</v>
+        <v>-10.66276165197247</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1208</v>
+        <v>0.0417</v>
       </c>
       <c r="G49" t="n">
-        <v>-8.312358615337255</v>
+        <v>-23.14527776191485</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1208</v>
+        <v>0.1598</v>
       </c>
       <c r="I49" t="n">
-        <v>-2.688333238984904</v>
+        <v>-11.57153631138001</v>
       </c>
     </row>
     <row r="50">
@@ -1855,28 +1855,28 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1255</v>
+        <v>0.0447</v>
       </c>
       <c r="C50" t="n">
-        <v>-13.06665434975022</v>
+        <v>-4.515370756736761</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1255</v>
+        <v>0.0447</v>
       </c>
       <c r="E50" t="n">
-        <v>-20.8295550057656</v>
+        <v>-10.61575248277768</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1255</v>
+        <v>0.0447</v>
       </c>
       <c r="G50" t="n">
-        <v>-8.109474512770143</v>
+        <v>-23.11486527415375</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1255</v>
+        <v>0.16535</v>
       </c>
       <c r="I50" t="n">
-        <v>-2.618571589086404</v>
+        <v>-11.53922890421574</v>
       </c>
     </row>
     <row r="51">
@@ -1884,28 +1884,28 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>0.1302</v>
+        <v>0.04775</v>
       </c>
       <c r="C51" t="n">
-        <v>-13.01120258286111</v>
+        <v>-4.479503175202031</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1302</v>
+        <v>0.04775</v>
       </c>
       <c r="E51" t="n">
-        <v>-20.66619549791235</v>
+        <v>-10.55480899958706</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1302</v>
+        <v>0.04775</v>
       </c>
       <c r="G51" t="n">
-        <v>-7.916099643918758</v>
+        <v>-23.06933245349448</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1302</v>
+        <v>0.17085</v>
       </c>
       <c r="I51" t="n">
-        <v>-2.546895747574837</v>
+        <v>-11.49569531578221</v>
       </c>
     </row>
     <row r="52">
@@ -1913,28 +1913,28 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1349</v>
+        <v>0.05075</v>
       </c>
       <c r="C52" t="n">
-        <v>-12.93961939287698</v>
+        <v>-4.44198440065547</v>
       </c>
       <c r="D52" t="n">
-        <v>0.1349</v>
+        <v>0.05075</v>
       </c>
       <c r="E52" t="n">
-        <v>-20.4934547703922</v>
+        <v>-10.49080302980393</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1349</v>
+        <v>0.05075</v>
       </c>
       <c r="G52" t="n">
-        <v>-7.716221686203717</v>
+        <v>-23.0499165714775</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1349</v>
+        <v>0.1764</v>
       </c>
       <c r="I52" t="n">
-        <v>-2.473816165547019</v>
+        <v>-11.45199033526822</v>
       </c>
     </row>
     <row r="53">
@@ -1942,28 +1942,28 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>0.1396</v>
+        <v>0.05375</v>
       </c>
       <c r="C53" t="n">
-        <v>-12.86642306058336</v>
+        <v>-4.40272270015198</v>
       </c>
       <c r="D53" t="n">
-        <v>0.1396</v>
+        <v>0.05375</v>
       </c>
       <c r="E53" t="n">
-        <v>-20.30754425372432</v>
+        <v>-10.44307928040424</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1396</v>
+        <v>0.05375</v>
       </c>
       <c r="G53" t="n">
-        <v>-7.505791546558966</v>
+        <v>-23.02672060623599</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1396</v>
+        <v>0.1819</v>
       </c>
       <c r="I53" t="n">
-        <v>-2.402735850315073</v>
+        <v>-11.40502890522573</v>
       </c>
     </row>
     <row r="54">
@@ -1971,28 +1971,28 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>0.1443</v>
+        <v>0.0568</v>
       </c>
       <c r="C54" t="n">
-        <v>-12.7920168715576</v>
+        <v>-4.358690886503204</v>
       </c>
       <c r="D54" t="n">
-        <v>0.1443</v>
+        <v>0.0568</v>
       </c>
       <c r="E54" t="n">
-        <v>-20.13516434234521</v>
+        <v>-10.39035346957013</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1443</v>
+        <v>0.0568</v>
       </c>
       <c r="G54" t="n">
-        <v>-7.305668189264164</v>
+        <v>-23.02483056462371</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1443</v>
+        <v>0.18745</v>
       </c>
       <c r="I54" t="n">
-        <v>-2.331017471212104</v>
+        <v>-11.36106683659107</v>
       </c>
     </row>
     <row r="55">
@@ -2000,28 +2000,28 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>0.149</v>
+        <v>0.0598</v>
       </c>
       <c r="C55" t="n">
-        <v>-12.71055318492778</v>
+        <v>-4.321355577846847</v>
       </c>
       <c r="D55" t="n">
-        <v>0.149</v>
+        <v>0.0598</v>
       </c>
       <c r="E55" t="n">
-        <v>-19.93545260828276</v>
+        <v>-10.33752557584961</v>
       </c>
       <c r="F55" t="n">
-        <v>0.149</v>
+        <v>0.0598</v>
       </c>
       <c r="G55" t="n">
-        <v>-7.100268741004507</v>
+        <v>-22.98256236129473</v>
       </c>
       <c r="H55" t="n">
-        <v>0.149</v>
+        <v>0.19295</v>
       </c>
       <c r="I55" t="n">
-        <v>-2.253854280409739</v>
+        <v>-11.30622137084803</v>
       </c>
     </row>
     <row r="56">
@@ -2029,28 +2029,28 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1537</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="C56" t="n">
-        <v>-12.62929114108665</v>
+        <v>-4.282919473849271</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1537</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>-19.73321516123306</v>
+        <v>-10.27959353780827</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1537</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>-6.884071711235382</v>
+        <v>-22.96520834285478</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1537</v>
+        <v>0.1985</v>
       </c>
       <c r="I56" t="n">
-        <v>-2.183667254597225</v>
+        <v>-11.24674831893292</v>
       </c>
     </row>
     <row r="57">
@@ -2058,28 +2058,28 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>0.1584</v>
+        <v>0.06585000000000001</v>
       </c>
       <c r="C57" t="n">
-        <v>-12.5433913131057</v>
+        <v>-4.241089250882935</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1584</v>
+        <v>0.06585000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>-19.52340057522166</v>
+        <v>-10.22758230717908</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1584</v>
+        <v>0.06585000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>-6.658058698275831</v>
+        <v>-22.93445221116417</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1584</v>
+        <v>0.204</v>
       </c>
       <c r="I57" t="n">
-        <v>-2.105270473644217</v>
+        <v>-11.18393312144909</v>
       </c>
     </row>
     <row r="58">
@@ -2087,28 +2087,28 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>0.1631</v>
+        <v>0.06884999999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>-12.45628162839262</v>
+        <v>-4.204029141061882</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1631</v>
+        <v>0.06884999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>-19.29725905882844</v>
+        <v>-10.1656690365675</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1631</v>
+        <v>0.06884999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>-6.440818720292725</v>
+        <v>-22.91056895806365</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1631</v>
+        <v>0.20955</v>
       </c>
       <c r="I58" t="n">
-        <v>-2.036061812433938</v>
+        <v>-11.13611473100437</v>
       </c>
     </row>
     <row r="59">
@@ -2116,28 +2116,28 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>0.1678</v>
+        <v>0.07185</v>
       </c>
       <c r="C59" t="n">
-        <v>-12.36513908790579</v>
+        <v>-4.164217042887782</v>
       </c>
       <c r="D59" t="n">
-        <v>0.1678</v>
+        <v>0.07185</v>
       </c>
       <c r="E59" t="n">
-        <v>-19.06985468594162</v>
+        <v>-10.10834949584465</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1678</v>
+        <v>0.07185</v>
       </c>
       <c r="G59" t="n">
-        <v>-6.223578742309617</v>
+        <v>-22.8846238413861</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1678</v>
+        <v>0.2151</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.961621027481271</v>
+        <v>-11.07115713251495</v>
       </c>
     </row>
     <row r="60">
@@ -2145,28 +2145,28 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>0.1725</v>
+        <v>0.07485</v>
       </c>
       <c r="C60" t="n">
-        <v>-12.27863433155878</v>
+        <v>-4.124680143548987</v>
       </c>
       <c r="D60" t="n">
-        <v>0.1725</v>
+        <v>0.07485</v>
       </c>
       <c r="E60" t="n">
-        <v>-18.81475767423041</v>
+        <v>-10.05230599120201</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1725</v>
+        <v>0.07485</v>
       </c>
       <c r="G60" t="n">
-        <v>-5.993455286389077</v>
+        <v>-22.86108423221508</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1725</v>
+        <v>0.2206</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.886839941797392</v>
+        <v>-11.00662801422665</v>
       </c>
     </row>
     <row r="61">
@@ -2174,28 +2174,28 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>0.1772</v>
+        <v>0.0779</v>
       </c>
       <c r="C61" t="n">
-        <v>-12.17156201076562</v>
+        <v>-4.088537363178951</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1772</v>
+        <v>0.0779</v>
       </c>
       <c r="E61" t="n">
-        <v>-18.55948025444868</v>
+        <v>-9.995394782024835</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1772</v>
+        <v>0.0779</v>
       </c>
       <c r="G61" t="n">
-        <v>-5.770632467966414</v>
+        <v>-22.82311157800489</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1772</v>
+        <v>0.22615</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.808825999166997</v>
+        <v>-10.9353289087607</v>
       </c>
     </row>
     <row r="62">
@@ -2203,28 +2203,28 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1819</v>
+        <v>0.0809</v>
       </c>
       <c r="C62" t="n">
-        <v>-12.07618497171635</v>
+        <v>-4.051385520412796</v>
       </c>
       <c r="D62" t="n">
-        <v>0.1819</v>
+        <v>0.0809</v>
       </c>
       <c r="E62" t="n">
-        <v>-18.29545304324688</v>
+        <v>-9.939759608927863</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1819</v>
+        <v>0.0809</v>
       </c>
       <c r="G62" t="n">
-        <v>-5.544496755216984</v>
+        <v>-22.78342070414719</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1819</v>
+        <v>0.23165</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.734512826988535</v>
+        <v>-10.84577654672713</v>
       </c>
     </row>
     <row r="63">
@@ -2232,28 +2232,28 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>0.1866</v>
+        <v>0.0839</v>
       </c>
       <c r="C63" t="n">
-        <v>-11.98423586007477</v>
+        <v>-4.014325410591745</v>
       </c>
       <c r="D63" t="n">
-        <v>0.1866</v>
+        <v>0.0839</v>
       </c>
       <c r="E63" t="n">
-        <v>-18.01771481868577</v>
+        <v>-9.879071332953274</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1866</v>
+        <v>0.0839</v>
       </c>
       <c r="G63" t="n">
-        <v>-5.320140189420817</v>
+        <v>-22.74665080369027</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1866</v>
+        <v>0.2372</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.654712305519277</v>
+        <v>-10.74979698167681</v>
       </c>
     </row>
     <row r="64">
@@ -2261,28 +2261,28 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1913</v>
+        <v>0.08695</v>
       </c>
       <c r="C64" t="n">
-        <v>-11.86929947052279</v>
+        <v>-3.972770386460714</v>
       </c>
       <c r="D64" t="n">
-        <v>0.1913</v>
+        <v>0.08695</v>
       </c>
       <c r="E64" t="n">
-        <v>-17.71931987005046</v>
+        <v>-9.826906977994462</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1913</v>
+        <v>0.08695</v>
       </c>
       <c r="G64" t="n">
-        <v>-5.078605653041406</v>
+        <v>-22.72637581184953</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1913</v>
+        <v>0.2427</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.575549847921041</v>
+        <v>-10.64858995817285</v>
       </c>
     </row>
     <row r="65">
@@ -2290,28 +2290,28 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>0.19595</v>
+        <v>0.08995</v>
       </c>
       <c r="C65" t="n">
-        <v>-11.74407929874774</v>
+        <v>-3.932591356506207</v>
       </c>
       <c r="D65" t="n">
-        <v>0.19595</v>
+        <v>0.08995</v>
       </c>
       <c r="E65" t="n">
-        <v>-17.43427511863341</v>
+        <v>-9.767290572327246</v>
       </c>
       <c r="F65" t="n">
-        <v>0.19595</v>
+        <v>0.08995</v>
       </c>
       <c r="G65" t="n">
-        <v>-4.835721418973312</v>
+        <v>-22.71726924771768</v>
       </c>
       <c r="H65" t="n">
-        <v>0.19595</v>
+        <v>0.24825</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.496557540688411</v>
+        <v>-10.53932750688788</v>
       </c>
     </row>
     <row r="66">
@@ -2319,28 +2319,28 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>0.20065</v>
+        <v>0.09295</v>
       </c>
       <c r="C66" t="n">
-        <v>-11.6204722692822</v>
+        <v>-3.892962724222309</v>
       </c>
       <c r="D66" t="n">
-        <v>0.20065</v>
+        <v>0.09295</v>
       </c>
       <c r="E66" t="n">
-        <v>-17.13308384490508</v>
+        <v>-9.711042901911776</v>
       </c>
       <c r="F66" t="n">
-        <v>0.20065</v>
+        <v>0.09295</v>
       </c>
       <c r="G66" t="n">
-        <v>-4.585659247197219</v>
+        <v>-22.70300802464326</v>
       </c>
       <c r="H66" t="n">
-        <v>0.20065</v>
+        <v>0.25375</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.41947942506885</v>
+        <v>-10.41386850400066</v>
       </c>
     </row>
     <row r="67">
@@ -2348,28 +2348,28 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>0.20535</v>
+        <v>0.096</v>
       </c>
       <c r="C67" t="n">
-        <v>-11.49363895519764</v>
+        <v>-3.855902614401256</v>
       </c>
       <c r="D67" t="n">
-        <v>0.20535</v>
+        <v>0.096</v>
       </c>
       <c r="E67" t="n">
-        <v>-16.81755012957064</v>
+        <v>-9.652038993563059</v>
       </c>
       <c r="F67" t="n">
-        <v>0.20535</v>
+        <v>0.096</v>
       </c>
       <c r="G67" t="n">
-        <v>-4.338357820693433</v>
+        <v>-22.67345464670592</v>
       </c>
       <c r="H67" t="n">
-        <v>0.20535</v>
+        <v>0.2593</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.334489317448605</v>
+        <v>-10.28866658923412</v>
       </c>
     </row>
     <row r="68">
@@ -2377,28 +2377,28 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>0.21005</v>
+        <v>0.099</v>
       </c>
       <c r="C68" t="n">
-        <v>-11.35753007283346</v>
+        <v>-3.814714522050632</v>
       </c>
       <c r="D68" t="n">
-        <v>0.21005</v>
+        <v>0.099</v>
       </c>
       <c r="E68" t="n">
-        <v>-16.47134704224829</v>
+        <v>-9.586961153472563</v>
       </c>
       <c r="F68" t="n">
-        <v>0.21005</v>
+        <v>0.099</v>
       </c>
       <c r="G68" t="n">
-        <v>-4.079829363415597</v>
+        <v>-22.64905592771114</v>
       </c>
       <c r="H68" t="n">
-        <v>0.21005</v>
+        <v>0.2648</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.249414134645558</v>
+        <v>-10.14186927233126</v>
       </c>
     </row>
     <row r="69">
@@ -2406,28 +2406,28 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>0.21475</v>
+        <v>0.102</v>
       </c>
       <c r="C69" t="n">
-        <v>-11.22061461931453</v>
+        <v>-3.774994156821633</v>
       </c>
       <c r="D69" t="n">
-        <v>0.21475</v>
+        <v>0.102</v>
       </c>
       <c r="E69" t="n">
-        <v>-16.1306464010767</v>
+        <v>-9.529182239760846</v>
       </c>
       <c r="F69" t="n">
-        <v>0.21475</v>
+        <v>0.102</v>
       </c>
       <c r="G69" t="n">
-        <v>-3.815349966328567</v>
+        <v>-22.61417606886649</v>
       </c>
       <c r="H69" t="n">
-        <v>0.21475</v>
+        <v>0.27035</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.163318049648873</v>
+        <v>-9.969963015642904</v>
       </c>
     </row>
     <row r="70">
@@ -2435,28 +2435,28 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>0.21945</v>
+        <v>0.10505</v>
       </c>
       <c r="C70" t="n">
-        <v>-11.08087616675397</v>
+        <v>-3.73619112104365</v>
       </c>
       <c r="D70" t="n">
-        <v>0.21945</v>
+        <v>0.10505</v>
       </c>
       <c r="E70" t="n">
-        <v>-15.76270414125704</v>
+        <v>-9.46665647183076</v>
       </c>
       <c r="F70" t="n">
-        <v>0.21945</v>
+        <v>0.10505</v>
       </c>
       <c r="G70" t="n">
-        <v>-3.554122113673365</v>
+        <v>-22.57259515339651</v>
       </c>
       <c r="H70" t="n">
-        <v>0.21945</v>
+        <v>0.2759</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.078455554802833</v>
+        <v>-9.788030322248401</v>
       </c>
     </row>
     <row r="71">
@@ -2464,28 +2464,28 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>0.22415</v>
+        <v>0.10805</v>
       </c>
       <c r="C71" t="n">
-        <v>-10.9231915060002</v>
+        <v>-3.696470755814651</v>
       </c>
       <c r="D71" t="n">
-        <v>0.22415</v>
+        <v>0.10805</v>
       </c>
       <c r="E71" t="n">
-        <v>-15.37266189279902</v>
+        <v>-9.399536974011935</v>
       </c>
       <c r="F71" t="n">
-        <v>0.22415</v>
+        <v>0.10805</v>
       </c>
       <c r="G71" t="n">
-        <v>-3.273200944742371</v>
+        <v>-22.54888372226074</v>
       </c>
       <c r="H71" t="n">
-        <v>0.22415</v>
+        <v>0.2814</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9875952595691784</v>
+        <v>-9.589986773291878</v>
       </c>
     </row>
     <row r="72">
@@ -2493,28 +2493,28 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>0.22885</v>
+        <v>0.11105</v>
       </c>
       <c r="C72" t="n">
-        <v>-10.75441649186862</v>
+        <v>-3.659410645993598</v>
       </c>
       <c r="D72" t="n">
-        <v>0.22885</v>
+        <v>0.11105</v>
       </c>
       <c r="E72" t="n">
-        <v>-14.99263229225471</v>
+        <v>-9.341502853084176</v>
       </c>
       <c r="F72" t="n">
-        <v>0.22885</v>
+        <v>0.11105</v>
       </c>
       <c r="G72" t="n">
-        <v>-2.990561978753052</v>
+        <v>-22.51915852235865</v>
       </c>
       <c r="H72" t="n">
-        <v>0.22885</v>
+        <v>0.28695</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.9020947008521155</v>
+        <v>-9.373175791526409</v>
       </c>
     </row>
     <row r="73">
@@ -2522,28 +2522,28 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>0.23355</v>
+        <v>0.11405</v>
       </c>
       <c r="C73" t="n">
-        <v>-10.57172812531758</v>
+        <v>-3.620057212545006</v>
       </c>
       <c r="D73" t="n">
-        <v>0.23355</v>
+        <v>0.11405</v>
       </c>
       <c r="E73" t="n">
-        <v>-14.60655902134808</v>
+        <v>-9.275455225572724</v>
       </c>
       <c r="F73" t="n">
-        <v>0.23355</v>
+        <v>0.11405</v>
       </c>
       <c r="G73" t="n">
-        <v>-2.712892354253887</v>
+        <v>-22.48943332245656</v>
       </c>
       <c r="H73" t="n">
-        <v>0.23355</v>
+        <v>0.29245</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.8122553078120973</v>
+        <v>-9.141710786882717</v>
       </c>
     </row>
     <row r="74">
@@ -2551,28 +2551,28 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>0.23825</v>
+        <v>0.1171</v>
       </c>
       <c r="C74" t="n">
-        <v>-10.37754611981135</v>
+        <v>-3.579969915535601</v>
       </c>
       <c r="D74" t="n">
-        <v>0.23825</v>
+        <v>0.1171</v>
       </c>
       <c r="E74" t="n">
-        <v>-14.18043515878664</v>
+        <v>-9.202670127557784</v>
       </c>
       <c r="F74" t="n">
-        <v>0.23825</v>
+        <v>0.1171</v>
       </c>
       <c r="G74" t="n">
-        <v>-2.426265645093458</v>
+        <v>-22.44922698270459</v>
       </c>
       <c r="H74" t="n">
-        <v>0.23825</v>
+        <v>0.298</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.7213524749870409</v>
+        <v>-8.872710916621134</v>
       </c>
     </row>
     <row r="75">
@@ -2580,28 +2580,28 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>0.24295</v>
+        <v>0.1201</v>
       </c>
       <c r="C75" t="n">
-        <v>-10.16945076188566</v>
+        <v>-3.541258612702719</v>
       </c>
       <c r="D75" t="n">
-        <v>0.24295</v>
+        <v>0.1201</v>
       </c>
       <c r="E75" t="n">
-        <v>-13.74646354515771</v>
+        <v>-9.143615177765861</v>
       </c>
       <c r="F75" t="n">
-        <v>0.24295</v>
+        <v>0.1201</v>
       </c>
       <c r="G75" t="n">
-        <v>-2.129270803688142</v>
+        <v>-22.43135749837039</v>
       </c>
       <c r="H75" t="n">
-        <v>0.24295</v>
+        <v>0.3035</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.6262809582046353</v>
+        <v>-8.589999679923789</v>
       </c>
     </row>
     <row r="76">
@@ -2609,28 +2609,28 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>0.24765</v>
+        <v>0.1231</v>
       </c>
       <c r="C76" t="n">
-        <v>-9.962766903480793</v>
+        <v>-3.503831571101261</v>
       </c>
       <c r="D76" t="n">
-        <v>0.24765</v>
+        <v>0.1231</v>
       </c>
       <c r="E76" t="n">
-        <v>-13.29778867378163</v>
+        <v>-9.081752948597483</v>
       </c>
       <c r="F76" t="n">
-        <v>0.24765</v>
+        <v>0.1231</v>
       </c>
       <c r="G76" t="n">
-        <v>-1.821539730668298</v>
+        <v>-22.37963908698005</v>
       </c>
       <c r="H76" t="n">
-        <v>0.24765</v>
+        <v>0.30905</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5320601932502599</v>
+        <v>-8.28012279847559</v>
       </c>
     </row>
     <row r="77">
@@ -2638,28 +2638,28 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>0.25235</v>
+        <v>0.12615</v>
       </c>
       <c r="C77" t="n">
-        <v>-9.731079339278653</v>
+        <v>-3.46346907525655</v>
       </c>
       <c r="D77" t="n">
-        <v>0.25235</v>
+        <v>0.12615</v>
       </c>
       <c r="E77" t="n">
-        <v>-12.82719422183773</v>
+        <v>-9.008661601923297</v>
       </c>
       <c r="F77" t="n">
-        <v>0.25235</v>
+        <v>0.12615</v>
       </c>
       <c r="G77" t="n">
-        <v>-1.519636897667769</v>
+        <v>-22.36331600032861</v>
       </c>
       <c r="H77" t="n">
-        <v>0.25235</v>
+        <v>0.31455</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.4374140523818694</v>
+        <v>-7.941109263351401</v>
       </c>
     </row>
     <row r="78">
@@ -2667,28 +2667,28 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>0.25705</v>
+        <v>0.12915</v>
       </c>
       <c r="C78" t="n">
-        <v>-9.487293207755247</v>
+        <v>-3.428610556117937</v>
       </c>
       <c r="D78" t="n">
-        <v>0.25705</v>
+        <v>0.12915</v>
       </c>
       <c r="E78" t="n">
-        <v>-12.3548858932239</v>
+        <v>-8.938836907614435</v>
       </c>
       <c r="F78" t="n">
-        <v>0.25705</v>
+        <v>0.12915</v>
       </c>
       <c r="G78" t="n">
-        <v>-1.20196714166762</v>
+        <v>-22.3232814825414</v>
       </c>
       <c r="H78" t="n">
-        <v>0.25705</v>
+        <v>0.3201</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.3401305808465844</v>
+        <v>-7.572701986430549</v>
       </c>
     </row>
     <row r="79">
@@ -2696,28 +2696,28 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>0.26175</v>
+        <v>0.13215</v>
       </c>
       <c r="C79" t="n">
-        <v>-9.209832730521004</v>
+        <v>-3.389807520339954</v>
       </c>
       <c r="D79" t="n">
-        <v>0.26175</v>
+        <v>0.13215</v>
       </c>
       <c r="E79" t="n">
-        <v>-11.85253962086899</v>
+        <v>-8.869930959283321</v>
       </c>
       <c r="F79" t="n">
-        <v>0.26175</v>
+        <v>0.13215</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.8730703548934208</v>
+        <v>-22.28668340404923</v>
       </c>
       <c r="H79" t="n">
-        <v>0.26175</v>
+        <v>0.32565</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2391463388593669</v>
+        <v>-7.172929958787893</v>
       </c>
     </row>
     <row r="80">
@@ -2725,28 +2725,28 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>0.26645</v>
+        <v>0.1352</v>
       </c>
       <c r="C80" t="n">
-        <v>-8.912812902784054</v>
+        <v>-3.34806903031872</v>
       </c>
       <c r="D80" t="n">
-        <v>0.26645</v>
+        <v>0.1352</v>
       </c>
       <c r="E80" t="n">
-        <v>-11.33549009076692</v>
+        <v>-8.798728146007837</v>
       </c>
       <c r="F80" t="n">
-        <v>0.26645</v>
+        <v>0.1352</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.529449593333583</v>
+        <v>-22.24544613250875</v>
       </c>
       <c r="H80" t="n">
-        <v>0.26645</v>
+        <v>0.33115</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.136673281173096</v>
+        <v>-6.74265014082567</v>
       </c>
     </row>
     <row r="81">
@@ -2754,28 +2754,28 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>0.27115</v>
+        <v>0.1382</v>
       </c>
       <c r="C81" t="n">
-        <v>-8.608130649076973</v>
+        <v>-3.310458522827058</v>
       </c>
       <c r="D81" t="n">
-        <v>0.27115</v>
+        <v>0.1382</v>
       </c>
       <c r="E81" t="n">
-        <v>-10.80797689257486</v>
+        <v>-8.73257843560997</v>
       </c>
       <c r="F81" t="n">
-        <v>0.27115</v>
+        <v>0.1382</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.1892644258903944</v>
+        <v>-22.20523979275679</v>
       </c>
       <c r="H81" t="n">
-        <v>0.27115</v>
+        <v>0.3367</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.02994646434667277</v>
+        <v>-6.270464959194153</v>
       </c>
     </row>
     <row r="82">
@@ -2783,28 +2783,28 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>0.27585</v>
+        <v>0.1412</v>
       </c>
       <c r="C82" t="n">
-        <v>-8.255659054450913</v>
+        <v>-3.273031481225599</v>
       </c>
       <c r="D82" t="n">
-        <v>0.27585</v>
+        <v>0.1412</v>
       </c>
       <c r="E82" t="n">
-        <v>-10.24636656905507</v>
+        <v>-8.656271478013663</v>
       </c>
       <c r="F82" t="n">
-        <v>0.27585</v>
+        <v>0.1412</v>
       </c>
       <c r="G82" t="n">
-        <v>0.159264327264656</v>
+        <v>-22.17087539980639</v>
       </c>
       <c r="H82" t="n">
-        <v>0.27585</v>
+        <v>0.3422</v>
       </c>
       <c r="I82" t="n">
-        <v>0.07427063458706057</v>
+        <v>-5.766486546639714</v>
       </c>
     </row>
     <row r="83">
@@ -2812,28 +2812,28 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>0.28055</v>
+        <v>0.1442</v>
       </c>
       <c r="C83" t="n">
-        <v>-7.884636323265585</v>
+        <v>-3.237989496196783</v>
       </c>
       <c r="D83" t="n">
-        <v>0.28055</v>
+        <v>0.1442</v>
       </c>
       <c r="E83" t="n">
-        <v>-9.689988079580273</v>
+        <v>-8.581597846600021</v>
       </c>
       <c r="F83" t="n">
-        <v>0.28055</v>
+        <v>0.1442</v>
       </c>
       <c r="G83" t="n">
-        <v>0.5177317634000124</v>
+        <v>-22.14269659758707</v>
       </c>
       <c r="H83" t="n">
-        <v>0.28055</v>
+        <v>0.34775</v>
       </c>
       <c r="I83" t="n">
-        <v>0.18312433098356</v>
+        <v>-5.220859858536652</v>
       </c>
     </row>
     <row r="84">
@@ -2841,28 +2841,28 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>0.28525</v>
+        <v>0.14725</v>
       </c>
       <c r="C84" t="n">
-        <v>-7.482560602622354</v>
+        <v>-3.196709670901056</v>
       </c>
       <c r="D84" t="n">
-        <v>0.28525</v>
+        <v>0.14725</v>
       </c>
       <c r="E84" t="n">
-        <v>-9.094641446873778</v>
+        <v>-8.504933598901255</v>
       </c>
       <c r="F84" t="n">
-        <v>0.28525</v>
+        <v>0.14725</v>
       </c>
       <c r="G84" t="n">
-        <v>0.9008618573013133</v>
+        <v>-22.08599534921892</v>
       </c>
       <c r="H84" t="n">
-        <v>0.28525</v>
+        <v>0.35325</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2976355270364621</v>
+        <v>-4.642925763269328</v>
       </c>
     </row>
     <row r="85">
@@ -2870,28 +2870,28 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>0.28995</v>
+        <v>0.15025</v>
       </c>
       <c r="C85" t="n">
-        <v>-7.053061462717601</v>
+        <v>-3.159099163409394</v>
       </c>
       <c r="D85" t="n">
-        <v>0.28995</v>
+        <v>0.15025</v>
       </c>
       <c r="E85" t="n">
-        <v>-8.486305433090051</v>
+        <v>-8.429902677385154</v>
       </c>
       <c r="F85" t="n">
-        <v>0.28995</v>
+        <v>0.15025</v>
       </c>
       <c r="G85" t="n">
-        <v>1.281783354984768</v>
+        <v>-22.05077184644476</v>
       </c>
       <c r="H85" t="n">
-        <v>0.28995</v>
+        <v>0.3588</v>
       </c>
       <c r="I85" t="n">
-        <v>0.4088713285514469</v>
+        <v>-4.016916189436617</v>
       </c>
     </row>
     <row r="86">
@@ -2899,28 +2899,28 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>0.29465</v>
+        <v>0.15325</v>
       </c>
       <c r="C86" t="n">
-        <v>-6.582830479497935</v>
+        <v>-3.1196539970157</v>
       </c>
       <c r="D86" t="n">
-        <v>0.29465</v>
+        <v>0.15325</v>
       </c>
       <c r="E86" t="n">
-        <v>-7.852982901539702</v>
+        <v>-8.357730076688716</v>
       </c>
       <c r="F86" t="n">
-        <v>0.29465</v>
+        <v>0.15325</v>
       </c>
       <c r="G86" t="n">
-        <v>1.673563784072632</v>
+        <v>-21.99905343505442</v>
       </c>
       <c r="H86" t="n">
-        <v>0.29465</v>
+        <v>0.3643</v>
       </c>
       <c r="I86" t="n">
-        <v>0.5249564154862055</v>
+        <v>-3.354657190589363</v>
       </c>
     </row>
     <row r="87">
@@ -2928,28 +2928,28 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>0.29935</v>
+        <v>0.1563</v>
       </c>
       <c r="C87" t="n">
-        <v>-6.05795430054391</v>
+        <v>-3.080759228292616</v>
       </c>
       <c r="D87" t="n">
-        <v>0.29935</v>
+        <v>0.1563</v>
       </c>
       <c r="E87" t="n">
-        <v>-7.197470177315747</v>
+        <v>-8.270500250245847</v>
       </c>
       <c r="F87" t="n">
-        <v>0.29935</v>
+        <v>0.1563</v>
       </c>
       <c r="G87" t="n">
-        <v>2.065712312530136</v>
+        <v>-21.96795365943431</v>
       </c>
       <c r="H87" t="n">
-        <v>0.29935</v>
+        <v>0.36985</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6432109195824416</v>
+        <v>-2.637295637878395</v>
       </c>
     </row>
     <row r="88">
@@ -2957,28 +2957,28 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>0.30405</v>
+        <v>0.1593</v>
       </c>
       <c r="C88" t="n">
-        <v>-5.506662916271797</v>
+        <v>-3.043056987855852</v>
       </c>
       <c r="D88" t="n">
-        <v>0.30405</v>
+        <v>0.1593</v>
       </c>
       <c r="E88" t="n">
-        <v>-6.516700323219396</v>
+        <v>-8.195928701718621</v>
       </c>
       <c r="F88" t="n">
-        <v>0.30405</v>
+        <v>0.1593</v>
       </c>
       <c r="G88" t="n">
-        <v>2.472707515563159</v>
+        <v>-21.94029032310924</v>
       </c>
       <c r="H88" t="n">
-        <v>0.30405</v>
+        <v>0.3754</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7648684309907997</v>
+        <v>-1.874600879889192</v>
       </c>
     </row>
     <row r="89">
@@ -2986,28 +2986,28 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>0.3087</v>
+        <v>0.1623</v>
       </c>
       <c r="C89" t="n">
-        <v>-4.908993690601521</v>
+        <v>-3.00315315673665</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3087</v>
+        <v>0.1623</v>
       </c>
       <c r="E89" t="n">
-        <v>-5.822941088045813</v>
+        <v>-8.117171754848318</v>
       </c>
       <c r="F89" t="n">
-        <v>0.3087</v>
+        <v>0.1623</v>
       </c>
       <c r="G89" t="n">
-        <v>2.888353053782745</v>
+        <v>-21.896819366027</v>
       </c>
       <c r="H89" t="n">
-        <v>0.3087</v>
+        <v>0.3809</v>
       </c>
       <c r="I89" t="n">
-        <v>0.8890781978832493</v>
+        <v>-1.072485943397177</v>
       </c>
     </row>
     <row r="90">
@@ -3015,28 +3015,28 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>0.3134</v>
+        <v>0.16535</v>
       </c>
       <c r="C90" t="n">
-        <v>-4.259703911027198</v>
+        <v>-2.964441853903769</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3134</v>
+        <v>0.16535</v>
       </c>
       <c r="E90" t="n">
-        <v>-5.103924722999832</v>
+        <v>-8.031626296031323</v>
       </c>
       <c r="F90" t="n">
-        <v>0.3134</v>
+        <v>0.16535</v>
       </c>
       <c r="G90" t="n">
-        <v>3.320869813110875</v>
+        <v>-21.86228315111185</v>
       </c>
       <c r="H90" t="n">
-        <v>0.3134</v>
+        <v>0.38645</v>
       </c>
       <c r="I90" t="n">
-        <v>1.013415577549903</v>
+        <v>-0.2113264351911656</v>
       </c>
     </row>
     <row r="91">
@@ -3044,28 +3044,28 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>0.3181</v>
+        <v>0.16835</v>
       </c>
       <c r="C91" t="n">
-        <v>-3.55173607994476</v>
+        <v>-2.926189215796395</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3181</v>
+        <v>0.16835</v>
       </c>
       <c r="E91" t="n">
-        <v>-4.348195315603617</v>
+        <v>-7.951950603183273</v>
       </c>
       <c r="F91" t="n">
-        <v>0.3181</v>
+        <v>0.16835</v>
       </c>
       <c r="G91" t="n">
-        <v>3.757865114769637</v>
+        <v>-21.81898401599435</v>
       </c>
       <c r="H91" t="n">
-        <v>0.3181</v>
+        <v>0.39195</v>
       </c>
       <c r="I91" t="n">
-        <v>1.143708220012771</v>
+        <v>0.7033074021143132</v>
       </c>
     </row>
     <row r="92">
@@ -3073,28 +3073,28 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>0.3228</v>
+        <v>0.17135</v>
       </c>
       <c r="C92" t="n">
-        <v>-2.788316481973211</v>
+        <v>-2.887294447073311</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3228</v>
+        <v>0.17135</v>
       </c>
       <c r="E92" t="n">
-        <v>-3.573793672908882</v>
+        <v>-7.867936387662523</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3228</v>
+        <v>0.17135</v>
       </c>
       <c r="G92" t="n">
-        <v>4.213204035015505</v>
+        <v>-21.76331369941471</v>
       </c>
       <c r="H92" t="n">
-        <v>0.3228</v>
+        <v>0.3975</v>
       </c>
       <c r="I92" t="n">
-        <v>1.275872516497305</v>
+        <v>1.683241622070104</v>
       </c>
     </row>
     <row r="93">
@@ -3102,28 +3102,28 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>0.3275</v>
+        <v>0.17435</v>
       </c>
       <c r="C93" t="n">
-        <v>-1.96783197480305</v>
+        <v>-2.852711126770002</v>
       </c>
       <c r="D93" t="n">
-        <v>0.3275</v>
+        <v>0.17435</v>
       </c>
       <c r="E93" t="n">
-        <v>-2.763581028216497</v>
+        <v>-7.782288845959109</v>
       </c>
       <c r="F93" t="n">
-        <v>0.3275</v>
+        <v>0.17435</v>
       </c>
       <c r="G93" t="n">
-        <v>4.682776130887492</v>
+        <v>-21.70850249265883</v>
       </c>
       <c r="H93" t="n">
-        <v>0.3275</v>
+        <v>0.403</v>
       </c>
       <c r="I93" t="n">
-        <v>1.411865196207977</v>
+        <v>2.69265527986278</v>
       </c>
     </row>
     <row r="94">
@@ -3131,28 +3131,28 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>0.3322</v>
+        <v>0.1774</v>
       </c>
       <c r="C94" t="n">
-        <v>-1.071328136297633</v>
+        <v>-2.815834482839153</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3322</v>
+        <v>0.1774</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.921977379254134</v>
+        <v>-7.692404864469413</v>
       </c>
       <c r="F94" t="n">
-        <v>0.3322</v>
+        <v>0.1774</v>
       </c>
       <c r="G94" t="n">
-        <v>5.161612060895443</v>
+        <v>-21.68169826615752</v>
       </c>
       <c r="H94" t="n">
-        <v>0.3322</v>
+        <v>0.40855</v>
       </c>
       <c r="I94" t="n">
-        <v>1.55151610877918</v>
+        <v>3.783394479827563</v>
       </c>
     </row>
     <row r="95">
@@ -3160,28 +3160,28 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>0.3369</v>
+        <v>0.1804</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.1046526073289049</v>
+        <v>-2.777673577676882</v>
       </c>
       <c r="D95" t="n">
-        <v>0.3369</v>
+        <v>0.1804</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.055928436736701</v>
+        <v>-7.602878173082175</v>
       </c>
       <c r="F95" t="n">
-        <v>0.3369</v>
+        <v>0.1804</v>
       </c>
       <c r="G95" t="n">
-        <v>5.643208736175701</v>
+        <v>-21.61331312418624</v>
       </c>
       <c r="H95" t="n">
-        <v>0.3369</v>
+        <v>0.41405</v>
       </c>
       <c r="I95" t="n">
-        <v>1.694272265522693</v>
+        <v>4.919381189030358</v>
       </c>
     </row>
     <row r="96">
@@ -3189,28 +3189,28 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>0.3416</v>
+        <v>0.1834</v>
       </c>
       <c r="C96" t="n">
-        <v>0.9469145356773357</v>
+        <v>-2.742539859702964</v>
       </c>
       <c r="D96" t="n">
-        <v>0.3416</v>
+        <v>0.1834</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.1464913532599012</v>
+        <v>-7.516975424162721</v>
       </c>
       <c r="F96" t="n">
-        <v>0.3416</v>
+        <v>0.1834</v>
       </c>
       <c r="G96" t="n">
-        <v>6.145664375735614</v>
+        <v>-21.60455020398388</v>
       </c>
       <c r="H96" t="n">
-        <v>0.3416</v>
+        <v>0.4196</v>
       </c>
       <c r="I96" t="n">
-        <v>1.841920245277383</v>
+        <v>6.132751422554978</v>
       </c>
     </row>
     <row r="97">
@@ -3218,28 +3218,28 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>0.3463</v>
+        <v>0.18645</v>
       </c>
       <c r="C97" t="n">
-        <v>2.070468154245078</v>
+        <v>-2.697682449548274</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3463</v>
+        <v>0.18645</v>
       </c>
       <c r="E97" t="n">
-        <v>0.8069652994230763</v>
+        <v>-7.432552877096305</v>
       </c>
       <c r="F97" t="n">
-        <v>0.3463</v>
+        <v>0.18645</v>
       </c>
       <c r="G97" t="n">
-        <v>6.645175220338398</v>
+        <v>-21.54028878916665</v>
       </c>
       <c r="H97" t="n">
-        <v>0.3463</v>
+        <v>0.42515</v>
       </c>
       <c r="I97" t="n">
-        <v>1.993183920301201</v>
+        <v>7.426933022010365</v>
       </c>
     </row>
     <row r="98">
@@ -3247,28 +3247,28 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>0.351</v>
+        <v>0.18945</v>
       </c>
       <c r="C98" t="n">
-        <v>3.2287043324671</v>
+        <v>-2.661906600958645</v>
       </c>
       <c r="D98" t="n">
-        <v>0.351</v>
+        <v>0.18945</v>
       </c>
       <c r="E98" t="n">
-        <v>1.777290106699404</v>
+        <v>-7.336135590875955</v>
       </c>
       <c r="F98" t="n">
-        <v>0.351</v>
+        <v>0.18945</v>
       </c>
       <c r="G98" t="n">
-        <v>7.165913128590478</v>
+        <v>-21.48410300669275</v>
       </c>
       <c r="H98" t="n">
-        <v>0.351</v>
+        <v>0.43065</v>
       </c>
       <c r="I98" t="n">
-        <v>2.145340884744452</v>
+        <v>8.766105042583092</v>
       </c>
     </row>
     <row r="99">
@@ -3276,28 +3276,28 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>0.3557</v>
+        <v>0.19245</v>
       </c>
       <c r="C99" t="n">
-        <v>4.449853060759678</v>
+        <v>-2.621819303949239</v>
       </c>
       <c r="D99" t="n">
-        <v>0.3557</v>
+        <v>0.19245</v>
       </c>
       <c r="E99" t="n">
-        <v>2.802819783553971</v>
+        <v>-7.244005785885097</v>
       </c>
       <c r="F99" t="n">
-        <v>0.3557</v>
+        <v>0.19245</v>
       </c>
       <c r="G99" t="n">
-        <v>7.699534514779992</v>
+        <v>-21.43169730744339</v>
       </c>
       <c r="H99" t="n">
-        <v>0.3557</v>
+        <v>0.4362</v>
       </c>
       <c r="I99" t="n">
-        <v>2.301538920370847</v>
+        <v>10.17349111117373</v>
       </c>
     </row>
     <row r="100">
@@ -3305,28 +3305,28 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>0.3604</v>
+        <v>0.1955</v>
       </c>
       <c r="C100" t="n">
-        <v>5.75831311655402</v>
+        <v>-2.585126125908594</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3604</v>
+        <v>0.1955</v>
       </c>
       <c r="E100" t="n">
-        <v>3.869392296451182</v>
+        <v>-7.144168722969795</v>
       </c>
       <c r="F100" t="n">
-        <v>0.3604</v>
+        <v>0.1955</v>
       </c>
       <c r="G100" t="n">
-        <v>8.230947304751663</v>
+        <v>-21.37259055156871</v>
       </c>
       <c r="H100" t="n">
-        <v>0.3604</v>
+        <v>0.4417</v>
       </c>
       <c r="I100" t="n">
-        <v>2.464457895438684</v>
+        <v>11.64592047429401</v>
       </c>
     </row>
     <row r="101">
@@ -3334,28 +3334,28 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>0.3651</v>
+        <v>0.1985</v>
       </c>
       <c r="C101" t="n">
-        <v>7.142994146472305</v>
+        <v>-2.548799879648354</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3651</v>
+        <v>0.1985</v>
       </c>
       <c r="E101" t="n">
-        <v>4.983682744000172</v>
+        <v>-7.047802478192652</v>
       </c>
       <c r="F101" t="n">
-        <v>0.3651</v>
+        <v>0.1985</v>
       </c>
       <c r="G101" t="n">
-        <v>8.773955224867018</v>
+        <v>-21.30953189050474</v>
       </c>
       <c r="H101" t="n">
-        <v>0.3651</v>
+        <v>0.44725</v>
       </c>
       <c r="I101" t="n">
-        <v>2.626015667581671</v>
+        <v>13.20670245488472</v>
       </c>
     </row>
     <row r="102">
@@ -3363,28 +3363,28 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>0.3698</v>
+        <v>0.2015</v>
       </c>
       <c r="C102" t="n">
-        <v>8.599258366374714</v>
+        <v>-2.511097639211591</v>
       </c>
       <c r="D102" t="n">
-        <v>0.3698</v>
+        <v>0.2015</v>
       </c>
       <c r="E102" t="n">
-        <v>6.146502962518267</v>
+        <v>-6.94281022951332</v>
       </c>
       <c r="F102" t="n">
-        <v>0.3698</v>
+        <v>0.2015</v>
       </c>
       <c r="G102" t="n">
-        <v>9.325184030904358</v>
+        <v>-21.25403339588986</v>
       </c>
       <c r="H102" t="n">
-        <v>0.3698</v>
+        <v>0.45275</v>
       </c>
       <c r="I102" t="n">
-        <v>2.79318840178966</v>
+        <v>14.82344394974139</v>
       </c>
     </row>
     <row r="103">
@@ -3392,28 +3392,28 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>0.3745</v>
+        <v>0.2045</v>
       </c>
       <c r="C103" t="n">
-        <v>10.12246799212143</v>
+        <v>-2.473670597610132</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3745</v>
+        <v>0.2045</v>
       </c>
       <c r="E103" t="n">
-        <v>7.331423169674709</v>
+        <v>-6.840982550312898</v>
       </c>
       <c r="F103" t="n">
-        <v>0.3745</v>
+        <v>0.2045</v>
       </c>
       <c r="G103" t="n">
-        <v>9.881198128747032</v>
+        <v>-21.18942833714311</v>
       </c>
       <c r="H103" t="n">
-        <v>0.3745</v>
+        <v>0.4583</v>
       </c>
       <c r="I103" t="n">
-        <v>2.963423842578558</v>
+        <v>16.5275097095858</v>
       </c>
     </row>
     <row r="104">
@@ -3421,28 +3421,28 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>0.3792</v>
+        <v>0.20755</v>
       </c>
       <c r="C104" t="n">
-        <v>11.73399715931336</v>
+        <v>-2.438628612581315</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3792</v>
+        <v>0.20755</v>
       </c>
       <c r="E104" t="n">
-        <v>8.570646206056805</v>
+        <v>-6.734867389882984</v>
       </c>
       <c r="F104" t="n">
-        <v>0.3792</v>
+        <v>0.20755</v>
       </c>
       <c r="G104" t="n">
-        <v>10.44604661146109</v>
+        <v>-21.12894700555042</v>
       </c>
       <c r="H104" t="n">
-        <v>0.3792</v>
+        <v>0.4638</v>
       </c>
       <c r="I104" t="n">
-        <v>3.136466764399957</v>
+        <v>18.28659232725371</v>
       </c>
     </row>
     <row r="105">
@@ -3450,28 +3450,28 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>0.3839</v>
+        <v>0.21055</v>
       </c>
       <c r="C105" t="n">
-        <v>13.39250909626951</v>
+        <v>-2.398541315571909</v>
       </c>
       <c r="D105" t="n">
-        <v>0.3839</v>
+        <v>0.21055</v>
       </c>
       <c r="E105" t="n">
-        <v>9.853798607609818</v>
+        <v>-6.636612611707138</v>
       </c>
       <c r="F105" t="n">
-        <v>0.3839</v>
+        <v>0.21055</v>
       </c>
       <c r="G105" t="n">
-        <v>11.01610983524506</v>
+        <v>-21.06898113985197</v>
       </c>
       <c r="H105" t="n">
-        <v>0.3839</v>
+        <v>0.46935</v>
       </c>
       <c r="I105" t="n">
-        <v>3.313848520544311</v>
+        <v>20.13394186635182</v>
       </c>
     </row>
     <row r="106">
@@ -3479,28 +3479,28 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>0.3886</v>
+        <v>0.21355</v>
       </c>
       <c r="C106" t="n">
-        <v>15.1371225039953</v>
+        <v>-2.364049728213703</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3886</v>
+        <v>0.21355</v>
       </c>
       <c r="E106" t="n">
-        <v>11.18079017029849</v>
+        <v>-6.524627685308277</v>
       </c>
       <c r="F106" t="n">
-        <v>0.3886</v>
+        <v>0.21355</v>
       </c>
       <c r="G106" t="n">
-        <v>11.59488474411053</v>
+        <v>-20.98032100603996</v>
       </c>
       <c r="H106" t="n">
-        <v>0.3886</v>
+        <v>0.47485</v>
       </c>
       <c r="I106" t="n">
-        <v>3.496292250065447</v>
+        <v>22.01137071556839</v>
       </c>
     </row>
     <row r="107">
@@ -3508,28 +3508,28 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>0.3933</v>
+        <v>0.2166</v>
       </c>
       <c r="C107" t="n">
-        <v>16.95291581612784</v>
+        <v>-2.327998680788768</v>
       </c>
       <c r="D107" t="n">
-        <v>0.3933</v>
+        <v>0.2166</v>
       </c>
       <c r="E107" t="n">
-        <v>12.55315436272222</v>
+        <v>-6.410907349840337</v>
       </c>
       <c r="F107" t="n">
-        <v>0.3933</v>
+        <v>0.2166</v>
       </c>
       <c r="G107" t="n">
-        <v>12.18089894057894</v>
+        <v>-20.91794963283499</v>
       </c>
       <c r="H107" t="n">
-        <v>0.3933</v>
+        <v>0.4804</v>
       </c>
       <c r="I107" t="n">
-        <v>3.683840490554766</v>
+        <v>23.99531974278278</v>
       </c>
     </row>
     <row r="108">
@@ -3537,28 +3537,28 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>0.398</v>
+        <v>0.2196</v>
       </c>
       <c r="C108" t="n">
-        <v>18.85279417114314</v>
+        <v>-2.291855900418732</v>
       </c>
       <c r="D108" t="n">
-        <v>0.398</v>
+        <v>0.2196</v>
       </c>
       <c r="E108" t="n">
-        <v>13.97034996066945</v>
+        <v>-6.295145356644067</v>
       </c>
       <c r="F108" t="n">
-        <v>0.398</v>
+        <v>0.2196</v>
       </c>
       <c r="G108" t="n">
-        <v>12.77304812654137</v>
+        <v>-20.8445816538859</v>
       </c>
       <c r="H108" t="n">
-        <v>0.398</v>
+        <v>0.48595</v>
       </c>
       <c r="I108" t="n">
-        <v>3.87491935113041</v>
+        <v>26.05219610022737</v>
       </c>
     </row>
     <row r="109">
@@ -3566,28 +3566,28 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>0.4027</v>
+        <v>0.2226</v>
       </c>
       <c r="C109" t="n">
-        <v>20.83937892529415</v>
+        <v>-2.25818990956644</v>
       </c>
       <c r="D109" t="n">
-        <v>0.4027</v>
+        <v>0.2226</v>
       </c>
       <c r="E109" t="n">
-        <v>15.43255737221071</v>
+        <v>-6.179689612107046</v>
       </c>
       <c r="F109" t="n">
-        <v>0.4027</v>
+        <v>0.2226</v>
       </c>
       <c r="G109" t="n">
-        <v>13.37004395420406</v>
+        <v>-20.76296622062871</v>
       </c>
       <c r="H109" t="n">
-        <v>0.4027</v>
+        <v>0.49145</v>
       </c>
       <c r="I109" t="n">
-        <v>4.067444489813708</v>
+        <v>28.1598902095245</v>
       </c>
     </row>
     <row r="110">
@@ -3595,28 +3595,28 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>0.4074</v>
+        <v>0.22565</v>
       </c>
       <c r="C110" t="n">
-        <v>22.87435794873019</v>
+        <v>-2.222230595086607</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4074</v>
+        <v>0.22565</v>
       </c>
       <c r="E110" t="n">
-        <v>16.94347496279159</v>
+        <v>-6.061579712523198</v>
       </c>
       <c r="F110" t="n">
-        <v>0.4074</v>
+        <v>0.22565</v>
       </c>
       <c r="G110" t="n">
-        <v>13.96912567829473</v>
+        <v>-20.67636795039371</v>
       </c>
       <c r="H110" t="n">
-        <v>0.4074</v>
+        <v>0.497</v>
       </c>
       <c r="I110" t="n">
-        <v>4.264095774862952</v>
+        <v>30.36767729380268</v>
       </c>
     </row>
     <row r="111">
@@ -3624,28 +3624,28 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>0.4121</v>
+        <v>0.22865</v>
       </c>
       <c r="C111" t="n">
-        <v>24.98999408764131</v>
+        <v>-2.183427559308624</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4121</v>
+        <v>0.22865</v>
       </c>
       <c r="E111" t="n">
-        <v>18.50653048575191</v>
+        <v>-5.951942692511916</v>
       </c>
       <c r="F111" t="n">
-        <v>0.4121</v>
+        <v>0.22865</v>
       </c>
       <c r="G111" t="n">
-        <v>14.57507859061869</v>
+        <v>-20.59320611945375</v>
       </c>
       <c r="H111" t="n">
-        <v>0.4121</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="I111" t="n">
-        <v>4.466234409202993</v>
+        <v>32.62791035469765</v>
       </c>
     </row>
     <row r="112">
@@ -3653,1160 +3653,2250 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>0.4168</v>
+        <v>0.23165</v>
       </c>
       <c r="C112" t="n">
-        <v>27.19314319684288</v>
+        <v>-2.15022023318184</v>
       </c>
       <c r="D112" t="n">
-        <v>0.4168</v>
+        <v>0.23165</v>
       </c>
       <c r="E112" t="n">
-        <v>20.13245822128745</v>
+        <v>-5.830617182005948</v>
       </c>
       <c r="F112" t="n">
-        <v>0.4168</v>
+        <v>0.23165</v>
       </c>
       <c r="G112" t="n">
-        <v>15.18992723770898</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0.4168</v>
-      </c>
-      <c r="I112" t="n">
-        <v>4.669861859242087</v>
-      </c>
+        <v>-20.51055975440805</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>0.4215</v>
+        <v>0.23465</v>
       </c>
       <c r="C113" t="n">
-        <v>29.46263278352269</v>
+        <v>-2.114352651647109</v>
       </c>
       <c r="D113" t="n">
-        <v>0.4215</v>
+        <v>0.23465</v>
       </c>
       <c r="E113" t="n">
-        <v>21.79329491846806</v>
+        <v>-5.701482330689122</v>
       </c>
       <c r="F113" t="n">
-        <v>0.4215</v>
+        <v>0.23465</v>
       </c>
       <c r="G113" t="n">
-        <v>15.80637098206771</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0.4215</v>
-      </c>
-      <c r="I113" t="n">
-        <v>4.877530380464327</v>
-      </c>
+        <v>-20.41330852235844</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>0.42615</v>
+        <v>0.2377</v>
       </c>
       <c r="C114" t="n">
-        <v>31.78394456689524</v>
+        <v>-2.077109075935853</v>
       </c>
       <c r="D114" t="n">
-        <v>0.42615</v>
+        <v>0.2377</v>
       </c>
       <c r="E114" t="n">
-        <v>23.49219771852777</v>
+        <v>-5.57770683090916</v>
       </c>
       <c r="F114" t="n">
-        <v>0.42615</v>
+        <v>0.2377</v>
       </c>
       <c r="G114" t="n">
-        <v>16.42232392726692</v>
-      </c>
-      <c r="H114" t="n">
-        <v>0.42615</v>
-      </c>
-      <c r="I114" t="n">
-        <v>5.088176533084672</v>
-      </c>
+        <v>-20.31657275620308</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>0.43085</v>
+        <v>0.2407</v>
       </c>
       <c r="C115" t="n">
-        <v>34.18551018016548</v>
+        <v>-2.041608426181528</v>
       </c>
       <c r="D115" t="n">
-        <v>0.43085</v>
+        <v>0.2407</v>
       </c>
       <c r="E115" t="n">
-        <v>25.28067312559924</v>
+        <v>-5.450868844536703</v>
       </c>
       <c r="F115" t="n">
-        <v>0.43085</v>
+        <v>0.2407</v>
       </c>
       <c r="G115" t="n">
-        <v>17.04956525313512</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0.43085</v>
-      </c>
-      <c r="I115" t="n">
-        <v>5.303671971124793</v>
-      </c>
+        <v>-20.21485415306991</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>0.43555</v>
+        <v>0.2437</v>
       </c>
       <c r="C116" t="n">
-        <v>36.66874112285424</v>
+        <v>-2.005557378756594</v>
       </c>
       <c r="D116" t="n">
-        <v>0.43555</v>
+        <v>0.2437</v>
       </c>
       <c r="E116" t="n">
-        <v>27.13995870034867</v>
+        <v>-5.319947542707589</v>
       </c>
       <c r="F116" t="n">
-        <v>0.43555</v>
+        <v>0.2437</v>
       </c>
       <c r="G116" t="n">
-        <v>17.68048757269973</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0.43555</v>
-      </c>
-      <c r="I116" t="n">
-        <v>5.521677127057601</v>
-      </c>
+        <v>-20.09079869451898</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>0.44025</v>
+        <v>0.24675</v>
       </c>
       <c r="C117" t="n">
-        <v>39.23565382284838</v>
+        <v>-1.97124925728859</v>
       </c>
       <c r="D117" t="n">
-        <v>0.44025</v>
+        <v>0.24675</v>
       </c>
       <c r="E117" t="n">
-        <v>29.06770913785935</v>
+        <v>-5.185045008308232</v>
       </c>
       <c r="F117" t="n">
-        <v>0.44025</v>
+        <v>0.24675</v>
       </c>
       <c r="G117" t="n">
-        <v>18.31772893144317</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0.44025</v>
-      </c>
-      <c r="I117" t="n">
-        <v>5.747041286302874</v>
-      </c>
+        <v>-19.98976737924482</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>0.44495</v>
+        <v>0.24975</v>
       </c>
       <c r="C118" t="n">
-        <v>41.88463513783841</v>
+        <v>-1.935840340479367</v>
       </c>
       <c r="D118" t="n">
-        <v>0.44495</v>
+        <v>0.24975</v>
       </c>
       <c r="E118" t="n">
-        <v>31.08052198061886</v>
+        <v>-5.046008117009008</v>
       </c>
       <c r="F118" t="n">
-        <v>0.44495</v>
+        <v>0.24975</v>
       </c>
       <c r="G118" t="n">
-        <v>18.95319114323335</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0.44495</v>
-      </c>
-      <c r="I118" t="n">
-        <v>5.974234561978413</v>
-      </c>
+        <v>-19.86725831837666</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>0.44965</v>
+        <v>0.25275</v>
       </c>
       <c r="C119" t="n">
-        <v>44.57858279470578</v>
+        <v>-1.90134875312116</v>
       </c>
       <c r="D119" t="n">
-        <v>0.44965</v>
+        <v>0.25275</v>
       </c>
       <c r="E119" t="n">
-        <v>33.17614212774572</v>
+        <v>-4.9120243285874</v>
       </c>
       <c r="F119" t="n">
-        <v>0.44965</v>
+        <v>0.25275</v>
       </c>
       <c r="G119" t="n">
-        <v>19.59067790155655</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0.44965</v>
-      </c>
-      <c r="I119" t="n">
-        <v>6.202108439116376</v>
-      </c>
+        <v>-19.74114099624871</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>0.45435</v>
+        <v>0.2558</v>
       </c>
       <c r="C120" t="n">
-        <v>47.37556991659257</v>
+        <v>-1.866857165762953</v>
       </c>
       <c r="D120" t="n">
-        <v>0.45435</v>
+        <v>0.2558</v>
       </c>
       <c r="E120" t="n">
-        <v>35.38262303420535</v>
+        <v>-4.772987437288176</v>
       </c>
       <c r="F120" t="n">
-        <v>0.45435</v>
+        <v>0.2558</v>
       </c>
       <c r="G120" t="n">
-        <v>20.23564934706246</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0.45435</v>
-      </c>
-      <c r="I120" t="n">
-        <v>6.436533105330175</v>
-      </c>
+        <v>-19.614164564297</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>0.45905</v>
+        <v>0.2588</v>
       </c>
       <c r="C121" t="n">
-        <v>50.26047329434717</v>
+        <v>-1.828971459435986</v>
       </c>
       <c r="D121" t="n">
-        <v>0.45905</v>
+        <v>0.2588</v>
       </c>
       <c r="E121" t="n">
-        <v>37.70537694211327</v>
+        <v>-4.630377644964377</v>
       </c>
       <c r="F121" t="n">
-        <v>0.45905</v>
+        <v>0.2588</v>
       </c>
       <c r="G121" t="n">
-        <v>20.89019137617903</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0.45905</v>
-      </c>
-      <c r="I121" t="n">
-        <v>6.678529462813444</v>
-      </c>
+        <v>-19.47481695088315</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>0.46375</v>
+        <v>0.2618</v>
       </c>
       <c r="C122" t="n">
-        <v>53.24801285154381</v>
+        <v>-1.794571605022881</v>
       </c>
       <c r="D122" t="n">
-        <v>0.46375</v>
+        <v>0.2618</v>
       </c>
       <c r="E122" t="n">
-        <v>40.15757364061722</v>
+        <v>-4.491340753665153</v>
       </c>
       <c r="F122" t="n">
-        <v>0.46375</v>
+        <v>0.2618</v>
       </c>
       <c r="G122" t="n">
-        <v>21.54884384825659</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0.46375</v>
-      </c>
-      <c r="I122" t="n">
-        <v>6.920610895479515</v>
-      </c>
+        <v>-19.32498819761943</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>0.46845</v>
+        <v>0.2648</v>
       </c>
       <c r="C123" t="n">
-        <v>56.32548509249515</v>
+        <v>-1.75870402348815</v>
       </c>
       <c r="D123" t="n">
-        <v>0.46845</v>
+        <v>0.2648</v>
       </c>
       <c r="E123" t="n">
-        <v>42.77276903083339</v>
+        <v>-4.340258081768787</v>
       </c>
       <c r="F123" t="n">
-        <v>0.46845</v>
+        <v>0.2648</v>
       </c>
       <c r="G123" t="n">
-        <v>22.21056381508116</v>
-      </c>
-      <c r="H123" t="n">
-        <v>0.46845</v>
-      </c>
-      <c r="I123" t="n">
-        <v>7.169583417952634</v>
-      </c>
+        <v>-19.17790859579173</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>0.47315</v>
+        <v>0.26785</v>
       </c>
       <c r="C124" t="n">
-        <v>59.52152329319485</v>
+        <v>-1.724487634965248</v>
       </c>
       <c r="D124" t="n">
-        <v>0.47315</v>
+        <v>0.26785</v>
       </c>
       <c r="E124" t="n">
-        <v>45.58948023581717</v>
+        <v>-4.200251403048607</v>
       </c>
       <c r="F124" t="n">
-        <v>0.47315</v>
+        <v>0.26785</v>
       </c>
       <c r="G124" t="n">
-        <v>22.87792797224022</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0.47315</v>
-      </c>
-      <c r="I124" t="n">
-        <v>7.42098058313564</v>
-      </c>
+        <v>-19.01141311194707</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>0.47785</v>
+        <v>0.27085</v>
       </c>
       <c r="C125" t="n">
-        <v>62.84641123586597</v>
+        <v>-1.691188575893362</v>
       </c>
       <c r="D125" t="n">
-        <v>0.47785</v>
+        <v>0.27085</v>
       </c>
       <c r="E125" t="n">
-        <v>48.59056848886946</v>
+        <v>-4.043094799410461</v>
       </c>
       <c r="F125" t="n">
-        <v>0.47785</v>
+        <v>0.27085</v>
       </c>
       <c r="G125" t="n">
-        <v>23.5514271188933</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0.47785</v>
-      </c>
-      <c r="I125" t="n">
-        <v>7.675695680447965</v>
-      </c>
+        <v>-18.86622355173165</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>0.48255</v>
+        <v>0.27385</v>
       </c>
       <c r="C126" t="n">
-        <v>66.30599656138047</v>
+        <v>-1.656696988535155</v>
       </c>
       <c r="D126" t="n">
-        <v>0.48255</v>
+        <v>0.27385</v>
       </c>
       <c r="E126" t="n">
-        <v>51.91350473972428</v>
+        <v>-3.885427781340233</v>
       </c>
       <c r="F126" t="n">
-        <v>0.48255</v>
+        <v>0.27385</v>
       </c>
       <c r="G126" t="n">
-        <v>24.23265635230884</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0.48255</v>
-      </c>
-      <c r="I126" t="n">
-        <v>7.938067544212564</v>
-      </c>
+        <v>-18.70024353378124</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>0.48725</v>
+        <v>0.2769</v>
       </c>
       <c r="C127" t="n">
-        <v>69.89685134233063</v>
+        <v>-1.623397929463269</v>
       </c>
       <c r="D127" t="n">
-        <v>0.48725</v>
+        <v>0.2769</v>
       </c>
       <c r="E127" t="n">
-        <v>55.59752774371913</v>
+        <v>-3.722197245960307</v>
       </c>
       <c r="F127" t="n">
-        <v>0.48725</v>
+        <v>0.2769</v>
       </c>
       <c r="G127" t="n">
-        <v>24.91836412805501</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0.48725</v>
-      </c>
-      <c r="I127" t="n">
-        <v>8.204140178429094</v>
-      </c>
+        <v>-18.5093493309418</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>0.49195</v>
+        <v>0.2799</v>
       </c>
       <c r="C128" t="n">
-        <v>73.59437515849658</v>
+        <v>-1.590465802171789</v>
       </c>
       <c r="D128" t="n">
-        <v>0.49195</v>
+        <v>0.2799</v>
       </c>
       <c r="E128" t="n">
-        <v>59.75286683193995</v>
+        <v>-3.560395870990213</v>
       </c>
       <c r="F128" t="n">
-        <v>0.49195</v>
+        <v>0.2799</v>
       </c>
       <c r="G128" t="n">
-        <v>25.61247683940799</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0.49195</v>
-      </c>
-      <c r="I128" t="n">
-        <v>8.474424034194376</v>
-      </c>
+        <v>-18.30917674200575</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>0.49665</v>
+        <v>0.2829</v>
       </c>
       <c r="C129" t="n">
-        <v>77.39917293824438</v>
+        <v>-1.555515550088074</v>
       </c>
       <c r="D129" t="n">
-        <v>0.49665</v>
+        <v>0.2829</v>
       </c>
       <c r="E129" t="n">
-        <v>64.61495453641157</v>
+        <v>-3.393286185926462</v>
       </c>
       <c r="F129" t="n">
-        <v>0.49665</v>
+        <v>0.2829</v>
       </c>
       <c r="G129" t="n">
-        <v>26.3119883415157</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0.49665</v>
-      </c>
-      <c r="I129" t="n">
-        <v>8.750152701659054</v>
-      </c>
+        <v>-18.10247491840912</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>0.50135</v>
+        <v>0.28595</v>
       </c>
       <c r="C130" t="n">
-        <v>81.39956422301923</v>
+        <v>-1.521482627455375</v>
       </c>
       <c r="D130" t="n">
-        <v>0.50135</v>
+        <v>0.28595</v>
       </c>
       <c r="E130" t="n">
-        <v>70.57166820874585</v>
+        <v>-3.225257754884962</v>
       </c>
       <c r="F130" t="n">
-        <v>0.50135</v>
+        <v>0.28595</v>
       </c>
       <c r="G130" t="n">
-        <v>27.01849373164658</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0.50135</v>
-      </c>
-      <c r="I130" t="n">
-        <v>9.03477172572665</v>
-      </c>
+        <v>-17.88632288675113</v>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>0.50605</v>
+        <v>0.28895</v>
       </c>
       <c r="C131" t="n">
-        <v>85.56832723634828</v>
+        <v>-1.486715841261863</v>
       </c>
       <c r="D131" t="n">
-        <v>0.50605</v>
+        <v>0.28895</v>
       </c>
       <c r="E131" t="n">
-        <v>78.53776697049977</v>
+        <v>-3.056514743638548</v>
       </c>
       <c r="F131" t="n">
-        <v>0.50605</v>
+        <v>0.28895</v>
       </c>
       <c r="G131" t="n">
-        <v>27.73659425192116</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0.50605</v>
-      </c>
-      <c r="I131" t="n">
-        <v>9.321560166955726</v>
-      </c>
+        <v>-17.66759352562187</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>0.51075</v>
+        <v>0.29195</v>
       </c>
       <c r="C132" t="n">
-        <v>89.91312440420167</v>
+        <v>-1.452315986848758</v>
       </c>
       <c r="D132" t="n">
-        <v>0.51075</v>
+        <v>0.29195</v>
       </c>
       <c r="E132" t="n">
-        <v>91.30416367257322</v>
+        <v>-2.882310297968853</v>
       </c>
       <c r="F132" t="n">
-        <v>0.51075</v>
+        <v>0.29195</v>
       </c>
       <c r="G132" t="n">
-        <v>28.45948006400106</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0.51075</v>
-      </c>
-      <c r="I132" t="n">
-        <v>9.616941201647906</v>
-      </c>
+        <v>-17.4313383240879</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>0.51545</v>
+        <v>0.29495</v>
       </c>
       <c r="C133" t="n">
-        <v>94.50674877329567</v>
+        <v>-1.417640933600348</v>
       </c>
       <c r="D133" t="n">
-        <v>0.51545</v>
+        <v>0.29495</v>
       </c>
       <c r="E133" t="n">
-        <v>97.64451510686214</v>
+        <v>-2.705094407149871</v>
       </c>
       <c r="F133" t="n">
-        <v>0.51545</v>
+        <v>0.29495</v>
       </c>
       <c r="G133" t="n">
-        <v>29.19040271231813</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0.51545</v>
-      </c>
-      <c r="I133" t="n">
-        <v>9.91491702941558</v>
-      </c>
+        <v>-17.17257444517143</v>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>0.52015</v>
+        <v>0.298</v>
       </c>
       <c r="C134" t="n">
-        <v>99.38408454607323</v>
+        <v>-1.384341874528462</v>
       </c>
       <c r="D134" t="n">
-        <v>0.52015</v>
+        <v>0.298</v>
       </c>
       <c r="E134" t="n">
-        <v>97.64451510686214</v>
+        <v>-2.524407698192731</v>
       </c>
       <c r="F134" t="n">
-        <v>0.52015</v>
+        <v>0.298</v>
       </c>
       <c r="G134" t="n">
-        <v>29.92874869792296</v>
-      </c>
-      <c r="H134" t="n">
-        <v>0.52015</v>
-      </c>
-      <c r="I134" t="n">
-        <v>10.21778468019443</v>
-      </c>
+        <v>-16.91192052464269</v>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>0.52485</v>
+        <v>0.301</v>
       </c>
       <c r="C135" t="n">
-        <v>104.544728436957</v>
+        <v>-1.350584150731068</v>
       </c>
       <c r="D135" t="n">
-        <v>0.52485</v>
+        <v>0.301</v>
       </c>
       <c r="E135" t="n">
-        <v>97.6446053108974</v>
+        <v>-2.342189745939343</v>
       </c>
       <c r="F135" t="n">
-        <v>0.52485</v>
+        <v>0.301</v>
       </c>
       <c r="G135" t="n">
-        <v>30.68003951136016</v>
-      </c>
-      <c r="H135" t="n">
-        <v>0.52485</v>
-      </c>
-      <c r="I135" t="n">
-        <v>10.52932999961919</v>
-      </c>
+        <v>-16.64216003998208</v>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>0.52955</v>
+        <v>0.304</v>
       </c>
       <c r="C136" t="n">
-        <v>110.066716205169</v>
+        <v>-1.317009892823877</v>
       </c>
       <c r="D136" t="n">
-        <v>0.52955</v>
+        <v>0.304</v>
       </c>
       <c r="E136" t="n">
-        <v>97.64451510686214</v>
+        <v>-2.153591613284926</v>
       </c>
       <c r="F136" t="n">
-        <v>0.52955</v>
+        <v>0.304</v>
       </c>
       <c r="G136" t="n">
-        <v>31.44353895389046</v>
-      </c>
-      <c r="H136" t="n">
-        <v>0.52955</v>
-      </c>
-      <c r="I136" t="n">
-        <v>10.84976567564687</v>
-      </c>
+        <v>-16.34318982131364</v>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>0.53425</v>
+        <v>0.30705</v>
       </c>
       <c r="C137" t="n">
-        <v>115.7225947850697</v>
+        <v>-1.282793504300975</v>
       </c>
       <c r="D137" t="n">
-        <v>0.53425</v>
+        <v>0.30705</v>
       </c>
       <c r="E137" t="n">
-        <v>97.64451510686214</v>
+        <v>-1.959889336309687</v>
       </c>
       <c r="F137" t="n">
-        <v>0.53425</v>
+        <v>0.30705</v>
       </c>
       <c r="G137" t="n">
-        <v>32.21335743559959</v>
-      </c>
-      <c r="H137" t="n">
-        <v>0.53425</v>
-      </c>
-      <c r="I137" t="n">
-        <v>11.17658199038478</v>
-      </c>
+        <v>-16.03047384546505</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>0.53895</v>
+        <v>0.31005</v>
       </c>
       <c r="C138" t="n">
-        <v>121.9785623041049</v>
+        <v>-1.249035780503581</v>
       </c>
       <c r="D138" t="n">
-        <v>0.53895</v>
+        <v>0.31005</v>
       </c>
       <c r="E138" t="n">
-        <v>97.64451510686214</v>
+        <v>-1.76924954592694</v>
       </c>
       <c r="F138" t="n">
-        <v>0.53895</v>
+        <v>0.31005</v>
       </c>
       <c r="G138" t="n">
-        <v>32.99286920070926</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0.53895</v>
-      </c>
-      <c r="I138" t="n">
-        <v>11.51292672559662</v>
-      </c>
+        <v>-15.70315300261254</v>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>0.5436</v>
+        <v>0.31305</v>
       </c>
       <c r="C139" t="n">
-        <v>128.6849998130684</v>
+        <v>-1.216837516772914</v>
       </c>
       <c r="D139" t="n">
-        <v>0.5436</v>
+        <v>0.31305</v>
       </c>
       <c r="E139" t="n">
-        <v>97.64451510686214</v>
+        <v>-1.576108724826991</v>
       </c>
       <c r="F139" t="n">
-        <v>0.5436</v>
+        <v>0.31305</v>
       </c>
       <c r="G139" t="n">
-        <v>33.77428281256208</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0.5436</v>
-      </c>
-      <c r="I139" t="n">
-        <v>11.85250431775499</v>
-      </c>
+        <v>-15.33700039572608</v>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>0.5483</v>
+        <v>0.3161</v>
       </c>
       <c r="C140" t="n">
-        <v>136.0187480376392</v>
+        <v>-1.184272321261841</v>
       </c>
       <c r="D140" t="n">
-        <v>0.5483</v>
+        <v>0.3161</v>
       </c>
       <c r="E140" t="n">
-        <v>97.64451510686214</v>
+        <v>-1.371330454675565</v>
       </c>
       <c r="F140" t="n">
-        <v>0.5483</v>
+        <v>0.3161</v>
       </c>
       <c r="G140" t="n">
-        <v>34.58723027041415</v>
-      </c>
-      <c r="H140" t="n">
-        <v>0.5483</v>
-      </c>
-      <c r="I140" t="n">
-        <v>12.20526856324783</v>
-      </c>
+        <v>-14.97548698188792</v>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>0.553</v>
+        <v>0.3191</v>
       </c>
       <c r="C141" t="n">
-        <v>144.0449375985636</v>
+        <v>-1.151890591640971</v>
       </c>
       <c r="D141" t="n">
-        <v>0.553</v>
+        <v>0.3191</v>
       </c>
       <c r="E141" t="n">
-        <v>97.64451510686214</v>
+        <v>-1.16823655215001</v>
       </c>
       <c r="F141" t="n">
-        <v>0.553</v>
+        <v>0.3191</v>
       </c>
       <c r="G141" t="n">
-        <v>35.41011641124652</v>
-      </c>
-      <c r="H141" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="I141" t="n">
-        <v>12.57053886061271</v>
-      </c>
+        <v>-14.59369857620903</v>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>0.5577</v>
+        <v>0.3221</v>
       </c>
       <c r="C142" t="n">
-        <v>153.0682507495485</v>
+        <v>-1.117674203118069</v>
       </c>
       <c r="D142" t="n">
-        <v>0.5577</v>
+        <v>0.3221</v>
       </c>
       <c r="E142" t="n">
-        <v>97.64451510686214</v>
+        <v>-0.958303096234553</v>
       </c>
       <c r="F142" t="n">
-        <v>0.5577</v>
+        <v>0.3221</v>
       </c>
       <c r="G142" t="n">
-        <v>36.24441363253776</v>
-      </c>
-      <c r="H142" t="n">
-        <v>0.5577</v>
-      </c>
-      <c r="I142" t="n">
-        <v>12.94733684524741</v>
-      </c>
+        <v>-14.17685848972074</v>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>0.5624</v>
+        <v>0.32515</v>
       </c>
       <c r="C143" t="n">
-        <v>163.2733922850319</v>
+        <v>-1.083733013430472</v>
       </c>
       <c r="D143" t="n">
-        <v>0.5624</v>
+        <v>0.32515</v>
       </c>
       <c r="E143" t="n">
-        <v>97.64451510686214</v>
+        <v>-0.7444904906352697</v>
       </c>
       <c r="F143" t="n">
-        <v>0.5624</v>
+        <v>0.32515</v>
       </c>
       <c r="G143" t="n">
-        <v>37.09343482861464</v>
-      </c>
-      <c r="H143" t="n">
-        <v>0.5624</v>
-      </c>
-      <c r="I143" t="n">
-        <v>13.33370578794745</v>
-      </c>
+        <v>-13.74884997552357</v>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>0.5671</v>
+        <v>0.32815</v>
       </c>
       <c r="C144" t="n">
-        <v>175.2255669417053</v>
+        <v>-1.050617420248789</v>
       </c>
       <c r="D144" t="n">
-        <v>0.5671</v>
+        <v>0.32815</v>
       </c>
       <c r="E144" t="n">
-        <v>97.64451510686214</v>
+        <v>-0.5300653877174877</v>
       </c>
       <c r="F144" t="n">
-        <v>0.5671</v>
+        <v>0.32815</v>
       </c>
       <c r="G144" t="n">
-        <v>37.93595293582786</v>
-      </c>
-      <c r="H144" t="n">
-        <v>0.5671</v>
-      </c>
-      <c r="I144" t="n">
-        <v>13.739727097875</v>
-      </c>
+        <v>-13.30554930646347</v>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>0.5718</v>
+        <v>0.33115</v>
       </c>
       <c r="C145" t="n">
-        <v>182.9672385277913</v>
+        <v>-1.008787197282453</v>
       </c>
       <c r="D145" t="n">
-        <v>0.5718</v>
+        <v>0.33115</v>
       </c>
       <c r="E145" t="n">
-        <v>97.64451510686214</v>
+        <v>-0.3323818781720058</v>
       </c>
       <c r="F145" t="n">
-        <v>0.5718</v>
+        <v>0.33115</v>
       </c>
       <c r="G145" t="n">
-        <v>38.80613984565909</v>
-      </c>
-      <c r="H145" t="n">
-        <v>0.5718</v>
-      </c>
-      <c r="I145" t="n">
-        <v>14.16518808707304</v>
-      </c>
+        <v>-12.84145817966839</v>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>0.5765</v>
+        <v>0.33415</v>
       </c>
       <c r="C146" t="n">
-        <v>182.9682467417347</v>
+        <v>-0.9760385358811764</v>
       </c>
       <c r="D146" t="n">
-        <v>0.5765</v>
+        <v>0.33415</v>
       </c>
       <c r="E146" t="n">
-        <v>97.64451510686214</v>
+        <v>-0.1086161911471174</v>
       </c>
       <c r="F146" t="n">
-        <v>0.5765</v>
+        <v>0.33415</v>
       </c>
       <c r="G146" t="n">
-        <v>39.71712443562553</v>
-      </c>
-      <c r="H146" t="n">
-        <v>0.5765</v>
-      </c>
-      <c r="I146" t="n">
-        <v>14.6107268194126</v>
-      </c>
+        <v>-12.33355245186155</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>0.5812</v>
+        <v>0.3372</v>
       </c>
       <c r="C147" t="n">
-        <v>182.968045098946</v>
+        <v>-0.9436568062603066</v>
       </c>
       <c r="D147" t="n">
-        <v>0.5812</v>
+        <v>0.3372</v>
       </c>
       <c r="E147" t="n">
-        <v>97.64442490282688</v>
+        <v>0.1191307284480131</v>
       </c>
       <c r="F147" t="n">
-        <v>0.5812</v>
+        <v>0.3372</v>
       </c>
       <c r="G147" t="n">
-        <v>40.62902927401607</v>
-      </c>
-      <c r="H147" t="n">
-        <v>0.5812</v>
-      </c>
-      <c r="I147" t="n">
-        <v>15.0714940094739</v>
-      </c>
+        <v>-11.82049206511215</v>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>0.5859</v>
+        <v>0.3402</v>
       </c>
       <c r="C148" t="n">
-        <v>182.9676418133687</v>
+        <v>-0.9103577471884206</v>
       </c>
       <c r="D148" t="n">
-        <v>0.5859</v>
+        <v>0.3402</v>
       </c>
       <c r="E148" t="n">
-        <v>97.64451510686214</v>
+        <v>0.343662037121025</v>
       </c>
       <c r="F148" t="n">
-        <v>0.5859</v>
+        <v>0.3402</v>
       </c>
       <c r="G148" t="n">
-        <v>41.57768269947577</v>
-      </c>
-      <c r="H148" t="n">
-        <v>0.5859</v>
-      </c>
-      <c r="I148" t="n">
-        <v>15.55331730727896</v>
-      </c>
+        <v>-11.29248316742933</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>0.5906</v>
+        <v>0.3432</v>
       </c>
       <c r="C149" t="n">
-        <v>182.9678434561573</v>
+        <v>-0.8772421540067378</v>
       </c>
       <c r="D149" t="n">
-        <v>0.5906</v>
+        <v>0.3432</v>
       </c>
       <c r="E149" t="n">
-        <v>97.64451510686214</v>
+        <v>0.553238202934025</v>
       </c>
       <c r="F149" t="n">
-        <v>0.5906</v>
+        <v>0.3432</v>
       </c>
       <c r="G149" t="n">
-        <v>42.55124418228117</v>
-      </c>
-      <c r="H149" t="n">
-        <v>0.5906</v>
-      </c>
-      <c r="I149" t="n">
-        <v>16.05815344203225</v>
-      </c>
+        <v>-10.72272153231178</v>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.34625</v>
       </c>
       <c r="C150" t="n">
-        <v>182.96744017058</v>
+        <v>-0.8426588337034292</v>
       </c>
       <c r="D150" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.34625</v>
       </c>
       <c r="E150" t="n">
-        <v>97.64451510686214</v>
+        <v>0.7932861103423393</v>
       </c>
       <c r="F150" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.34625</v>
       </c>
       <c r="G150" t="n">
-        <v>43.5673211422801</v>
-      </c>
-      <c r="H150" t="n">
-        <v>0.5953000000000001</v>
-      </c>
-      <c r="I150" t="n">
-        <v>16.57834564728148</v>
-      </c>
+        <v>-10.13388765910676</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>0.6</v>
+        <v>0.34925</v>
       </c>
       <c r="C151" t="n">
-        <v>182.9676418133687</v>
+        <v>-0.8078003145648157</v>
       </c>
       <c r="D151" t="n">
-        <v>0.6</v>
+        <v>0.34925</v>
       </c>
       <c r="E151" t="n">
-        <v>97.64451510686214</v>
+        <v>1.033231934864237</v>
       </c>
       <c r="F151" t="n">
-        <v>0.6</v>
+        <v>0.34925</v>
       </c>
       <c r="G151" t="n">
-        <v>44.61407304974912</v>
-      </c>
-      <c r="H151" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I151" t="n">
-        <v>16.98564308495108</v>
-      </c>
+        <v>-9.501582828819487</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.773033528371304</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="E152" t="n">
+        <v>1.274300671136716</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="G152" t="n">
+        <v>-8.863779695660154</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.7376246115620808</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1.529507887177876</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="G153" t="n">
+        <v>-8.159309640177057</v>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.7026743594783658</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1.775731809214386</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="G154" t="n">
+        <v>-7.467038944191347</v>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.6673571756142442</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2.029458823402506</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="G155" t="n">
+        <v>-6.742809362761771</v>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.6325903894207324</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2.282726464601753</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="G156" t="n">
+        <v>-5.986620895888326</v>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.5954385466545786</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2.550336751342512</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="G157" t="n">
+        <v>-5.170810207245948</v>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.5594792321747458</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="E158" t="n">
+        <v>2.816160587570984</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="G158" t="n">
+        <v>-4.3577486700396</v>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.5226025882438968</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="E159" t="n">
+        <v>3.086629195131405</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="G159" t="n">
+        <v>-3.492453255548652</v>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.4850838136973366</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="E160" t="n">
+        <v>3.360721745159609</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="G160" t="n">
+        <v>-2.595198955613836</v>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.4464642438095569</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="E161" t="n">
+        <v>3.636855952916143</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="G161" t="n">
+        <v>-1.676295088120272</v>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.4085785374825902</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="E162" t="n">
+        <v>3.914368279639301</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="G162" t="n">
+        <v>-0.7206213201697849</v>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.3688581722535912</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="E163" t="n">
+        <v>4.202037853560896</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0.2706195944843612</v>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.3290460740794906</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="E164" t="n">
+        <v>4.490626173460238</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="G164" t="n">
+        <v>1.302582314784726</v>
+      </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.2890505100151868</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="E165" t="n">
+        <v>4.752315652788842</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2.374064086978044</v>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.2484128153351716</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="E166" t="n">
+        <v>5.045344578247301</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="G166" t="n">
+        <v>3.453449669549954</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.2053900640825145</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="E167" t="n">
+        <v>5.352205734815191</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="G167" t="n">
+        <v>4.598127598727614</v>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.1631929093357719</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="E168" t="n">
+        <v>5.654983575926424</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="G168" t="n">
+        <v>5.754317599543656</v>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.119161095686997</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="E169" t="n">
+        <v>5.962916602801686</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="G169" t="n">
+        <v>6.943153773662575</v>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" t="n">
+        <v>0.40655</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.07870686689718509</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.40655</v>
+      </c>
+      <c r="E170" t="n">
+        <v>6.279271467806306</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.40655</v>
+      </c>
+      <c r="G170" t="n">
+        <v>8.193330389197946</v>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" t="n">
+        <v>0.40955</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.03366599085229246</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.40955</v>
+      </c>
+      <c r="E171" t="n">
+        <v>6.591032602922186</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.40955</v>
+      </c>
+      <c r="G171" t="n">
+        <v>9.443678826698074</v>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0.01385167471034376</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="E172" t="n">
+        <v>6.911572866269883</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="G172" t="n">
+        <v>10.74471474380003</v>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.06237840266909774</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="E173" t="n">
+        <v>7.238493310018607</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="G173" t="n">
+        <v>12.09128348156126</v>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.09393453578405307</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="E174" t="n">
+        <v>7.569446027780782</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="G174" t="n">
+        <v>13.46500008975331</v>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" t="n">
+        <v>0.4216</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.144846320315449</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.4216</v>
+      </c>
+      <c r="E175" t="n">
+        <v>7.893559192153055</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.4216</v>
+      </c>
+      <c r="G175" t="n">
+        <v>14.85469614066728</v>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" t="n">
+        <v>0.4246</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.1977762296390805</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0.4246</v>
+      </c>
+      <c r="E176" t="n">
+        <v>8.226604609086767</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.4246</v>
+      </c>
+      <c r="G176" t="n">
+        <v>16.29233051974706</v>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0.2513482695784233</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="E177" t="n">
+        <v>8.573124967027454</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="G177" t="n">
+        <v>17.77944962467541</v>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" t="n">
+        <v>0.43065</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.3064797695844935</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0.43065</v>
+      </c>
+      <c r="E178" t="n">
+        <v>8.917399501466976</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.43065</v>
+      </c>
+      <c r="G178" t="n">
+        <v>19.28461003590271</v>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" t="n">
+        <v>0.43365</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0.3619782013709701</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0.43365</v>
+      </c>
+      <c r="E179" t="n">
+        <v>9.261010497144794</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.43365</v>
+      </c>
+      <c r="G179" t="n">
+        <v>20.86520028965614</v>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.4203203544555968</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="E180" t="n">
+        <v>9.616616231976545</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="G180" t="n">
+        <v>22.44596236537431</v>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.4808640982226624</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="E181" t="n">
+        <v>9.971813635262631</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="G181" t="n">
+        <v>24.04356299363818</v>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.5427838361662519</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="E182" t="n">
+        <v>10.33114539544859</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="G182" t="n">
+        <v>25.67655894664095</v>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" t="n">
+        <v>0.44575</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0.6066299659569756</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0.44575</v>
+      </c>
+      <c r="E183" t="n">
+        <v>10.69946044963918</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.44575</v>
+      </c>
+      <c r="G183" t="n">
+        <v>27.36178877692833</v>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" t="n">
+        <v>0.44875</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.6713934251987151</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0.44875</v>
+      </c>
+      <c r="E184" t="n">
+        <v>11.06374322981634</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.44875</v>
+      </c>
+      <c r="G184" t="n">
+        <v>29.03344467200029</v>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" t="n">
+        <v>0.45175</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.7395510034092146</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0.45175</v>
+      </c>
+      <c r="E185" t="n">
+        <v>11.43501868771301</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.45175</v>
+      </c>
+      <c r="G185" t="n">
+        <v>30.74977427790778</v>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" t="n">
+        <v>0.45475</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.8092680416864416</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0.45475</v>
+      </c>
+      <c r="E186" t="n">
+        <v>11.80813163756519</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.45475</v>
+      </c>
+      <c r="G186" t="n">
+        <v>32.49187717852806</v>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" t="n">
+        <v>0.4578</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0.882654397767733</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0.4578</v>
+      </c>
+      <c r="E187" t="n">
+        <v>12.19232058059355</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0.4578</v>
+      </c>
+      <c r="G187" t="n">
+        <v>34.28140294141988</v>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0.9564994185745326</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="E188" t="n">
+        <v>12.57002726033446</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="G188" t="n">
+        <v>36.05838570088481</v>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>187</v>
+      </c>
+      <c r="B189" t="n">
+        <v>0.4638</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1.034380688965803</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0.4638</v>
+      </c>
+      <c r="E189" t="n">
+        <v>12.95692139985286</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.4638</v>
+      </c>
+      <c r="G189" t="n">
+        <v>37.88691504977533</v>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" t="n">
+        <v>0.46685</v>
+      </c>
+      <c r="C190" t="n">
+        <v>1.074651451865412</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0.46685</v>
+      </c>
+      <c r="E190" t="n">
+        <v>13.35239050183024</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.46685</v>
+      </c>
+      <c r="G190" t="n">
+        <v>39.75376069680554</v>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" t="n">
+        <v>0.46985</v>
+      </c>
+      <c r="C191" t="n">
+        <v>1.162348147382555</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0.46985</v>
+      </c>
+      <c r="E191" t="n">
+        <v>13.74612419473855</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0.46985</v>
+      </c>
+      <c r="G191" t="n">
+        <v>41.62576100277832</v>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" t="n">
+        <v>0.47285</v>
+      </c>
+      <c r="C192" t="n">
+        <v>1.249402712283987</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0.47285</v>
+      </c>
+      <c r="E192" t="n">
+        <v>14.14123600661347</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0.47285</v>
+      </c>
+      <c r="G192" t="n">
+        <v>43.50497783127067</v>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" t="n">
+        <v>0.4759</v>
+      </c>
+      <c r="C193" t="n">
+        <v>1.341502589166008</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0.4759</v>
+      </c>
+      <c r="E193" t="n">
+        <v>14.5469644386757</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0.4759</v>
+      </c>
+      <c r="G193" t="n">
+        <v>45.44433234742621</v>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" t="n">
+        <v>0.4789</v>
+      </c>
+      <c r="C194" t="n">
+        <v>1.43424459666374</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0.4789</v>
+      </c>
+      <c r="E194" t="n">
+        <v>14.95595952310326</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0.4789</v>
+      </c>
+      <c r="G194" t="n">
+        <v>47.38781059073581</v>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" t="n">
+        <v>0.4819</v>
+      </c>
+      <c r="C195" t="n">
+        <v>1.531389785526349</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0.4819</v>
+      </c>
+      <c r="E195" t="n">
+        <v>15.3673025139184</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0.4819</v>
+      </c>
+      <c r="G195" t="n">
+        <v>49.35431297732217</v>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" t="n">
+        <v>0.4849</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1.629635769730179</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0.4849</v>
+      </c>
+      <c r="E196" t="n">
+        <v>15.77726738576692</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0.4849</v>
+      </c>
+      <c r="G196" t="n">
+        <v>51.3151452390717</v>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" t="n">
+        <v>0.48795</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1.734578258926425</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0.48795</v>
+      </c>
+      <c r="E197" t="n">
+        <v>16.20157490315695</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0.48795</v>
+      </c>
+      <c r="G197" t="n">
+        <v>53.34883001387609</v>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" t="n">
+        <v>0.49095</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1.841538872914908</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0.49095</v>
+      </c>
+      <c r="E198" t="n">
+        <v>16.62251368529524</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0.49095</v>
+      </c>
+      <c r="G198" t="n">
+        <v>55.37254911472486</v>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" t="n">
+        <v>0.49395</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1.952810935323166</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0.49395</v>
+      </c>
+      <c r="E199" t="n">
+        <v>17.0532013830863</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0.49395</v>
+      </c>
+      <c r="G199" t="n">
+        <v>57.42272879814543</v>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="C200" t="n">
+        <v>2.069403508547317</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="E200" t="n">
+        <v>17.48945259818706</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="G200" t="n">
+        <v>59.5079601623754</v>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C201" t="n">
+        <v>2.186363013551876</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E201" t="n">
+        <v>17.916924685056</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G201" t="n">
+        <v>61.57137013708187</v>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/EQE/Plots/best Voc JVs.xlsx
+++ b/EQE/Plots/best Voc JVs.xlsx
@@ -413,48 +413,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I201"/>
+  <dimension ref="A1:I151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>V_CdS1_10</t>
+          <t>V_Mo_200Sb_25Se_13</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>J_CdS1_10</t>
+          <t>J_Mo_200Sb_25Se_13</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>V_CdS2_2</t>
+          <t>V_Mo_300Sb_35Se_12</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>J_CdS2_2</t>
+          <t>J_Mo_300Sb_35Se_12</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>V_CdS3_6</t>
+          <t>V_Mo_400Sb_30Se_11</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>J_CdS3_6</t>
+          <t>J_Mo_400Sb_30Se_11</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>V_2_CdS3_21</t>
+          <t>V_Mo_400deg_400Sb_35Se_2</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>J_2_CdS3_21</t>
+          <t>J_Mo_400deg_400Sb_35Se_2</t>
         </is>
       </c>
     </row>
@@ -466,25 +466,25 @@
         <v>-0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.987042395001961</v>
+        <v>-14.94475528358725</v>
       </c>
       <c r="D2" t="n">
         <v>-0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>-12.85647183961906</v>
+        <v>-24.13399942939242</v>
       </c>
       <c r="F2" t="n">
         <v>-0.1</v>
       </c>
       <c r="G2" t="n">
-        <v>-24.01418143766559</v>
+        <v>-15.67587975552999</v>
       </c>
       <c r="H2" t="n">
         <v>-0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>-12.43638074931563</v>
+        <v>-5.554813910759389</v>
       </c>
     </row>
     <row r="3">
@@ -492,28 +492,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.097</v>
+        <v>-0.0953</v>
       </c>
       <c r="C3" t="n">
-        <v>-5.954385466545786</v>
+        <v>-14.94011749944744</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.097</v>
+        <v>-0.0953</v>
       </c>
       <c r="E3" t="n">
-        <v>-12.80828871723049</v>
+        <v>-24.11857453936321</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.097</v>
+        <v>-0.0953</v>
       </c>
       <c r="G3" t="n">
-        <v>-24.00181025620344</v>
+        <v>-15.55606341071186</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.09445000000000001</v>
+        <v>-0.0953</v>
       </c>
       <c r="I3" t="n">
-        <v>-12.43021063441953</v>
+        <v>-5.501131470410666</v>
       </c>
     </row>
     <row r="4">
@@ -521,28 +521,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.09395000000000001</v>
+        <v>-0.0906</v>
       </c>
       <c r="C4" t="n">
-        <v>-5.958788647910663</v>
+        <v>-14.92015486336736</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.09395000000000001</v>
+        <v>-0.0906</v>
       </c>
       <c r="E4" t="n">
-        <v>-12.76791493565278</v>
+        <v>-24.08555986245858</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.09395000000000001</v>
+        <v>-0.0906</v>
       </c>
       <c r="G4" t="n">
-        <v>-24.00352847585097</v>
+        <v>-15.42906912818572</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.08895</v>
+        <v>-0.0906</v>
       </c>
       <c r="I4" t="n">
-        <v>-12.42052698187428</v>
+        <v>-5.447023654147928</v>
       </c>
     </row>
     <row r="5">
@@ -550,28 +550,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.09095</v>
+        <v>-0.0859</v>
       </c>
       <c r="C5" t="n">
-        <v>-5.955027597161497</v>
+        <v>-14.90200701238547</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.09095</v>
+        <v>-0.0859</v>
       </c>
       <c r="E5" t="n">
-        <v>-12.73111405509964</v>
+        <v>-24.04135988518188</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.09095</v>
+        <v>-0.0859</v>
       </c>
       <c r="G5" t="n">
-        <v>-23.98668992330527</v>
+        <v>-15.29728955385426</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0834</v>
+        <v>-0.0859</v>
       </c>
       <c r="I5" t="n">
-        <v>-12.41675635610444</v>
+        <v>-5.391044183863522</v>
       </c>
     </row>
     <row r="6">
@@ -579,28 +579,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.08795</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>-5.944753507310115</v>
+        <v>-14.88143944793932</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08795</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-12.68844340857756</v>
+        <v>-24.01041990108819</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.08795</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-23.96280667020475</v>
+        <v>-15.16182898582639</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0779</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-12.40587295899606</v>
+        <v>-5.332895296417639</v>
       </c>
     </row>
     <row r="7">
@@ -608,28 +608,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.0849</v>
+        <v>-0.0765</v>
       </c>
       <c r="C7" t="n">
-        <v>-5.933929019788126</v>
+        <v>-14.86450145368956</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0849</v>
+        <v>-0.0765</v>
       </c>
       <c r="E7" t="n">
-        <v>-12.64255715113336</v>
+        <v>-24.00248194598544</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0849</v>
+        <v>-0.0765</v>
       </c>
       <c r="G7" t="n">
-        <v>-23.95387192803765</v>
+        <v>-15.03600035130412</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.07235</v>
+        <v>-0.0765</v>
       </c>
       <c r="I7" t="n">
-        <v>-12.39533234604857</v>
+        <v>-5.27763896518706</v>
       </c>
     </row>
     <row r="8">
@@ -637,28 +637,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.0819</v>
+        <v>-0.0718</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.919802146242477</v>
+        <v>-14.83304517865428</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0819</v>
+        <v>-0.0718</v>
       </c>
       <c r="E8" t="n">
-        <v>-12.60376565429511</v>
+        <v>-23.96964767715133</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0819</v>
+        <v>-0.0718</v>
       </c>
       <c r="G8" t="n">
-        <v>-23.93789248531571</v>
+        <v>-14.89495694283669</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.06685000000000001</v>
+        <v>-0.0718</v>
       </c>
       <c r="I8" t="n">
-        <v>-12.38410616477929</v>
+        <v>-5.220170679203601</v>
       </c>
     </row>
     <row r="9">
@@ -666,28 +666,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0789</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.903015017288881</v>
+        <v>-14.81106611468732</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0789</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-12.57002726033446</v>
+        <v>-23.92427504741627</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0789</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-23.91864842526349</v>
+        <v>-14.75685832932639</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0613</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-12.36268215472341</v>
+        <v>-5.165552411844045</v>
       </c>
     </row>
     <row r="10">
@@ -695,28 +695,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0759</v>
+        <v>-0.0624</v>
       </c>
       <c r="C10" t="n">
-        <v>-5.878889252727157</v>
+        <v>-14.80078233246425</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0759</v>
+        <v>-0.0624</v>
       </c>
       <c r="E10" t="n">
-        <v>-12.53072534906413</v>
+        <v>-23.88801302524233</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0759</v>
+        <v>-0.0624</v>
       </c>
       <c r="G10" t="n">
-        <v>-23.87414653639273</v>
+        <v>-14.62906649816604</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0558</v>
+        <v>-0.0624</v>
       </c>
       <c r="I10" t="n">
-        <v>-12.34897078828765</v>
+        <v>-5.107743825129373</v>
       </c>
     </row>
     <row r="11">
@@ -724,28 +724,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.07285</v>
+        <v>-0.0577</v>
       </c>
       <c r="C11" t="n">
-        <v>-5.854396556385026</v>
+        <v>-14.75863898962853</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.07285</v>
+        <v>-0.0577</v>
       </c>
       <c r="E11" t="n">
-        <v>-12.48050056894723</v>
+        <v>-23.84597794481184</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.07285</v>
+        <v>-0.0577</v>
       </c>
       <c r="G11" t="n">
-        <v>-23.84115671916035</v>
+        <v>-14.48992493644175</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.05025</v>
+        <v>-0.0577</v>
       </c>
       <c r="I11" t="n">
-        <v>-12.33003196339826</v>
+        <v>-5.051041215791142</v>
       </c>
     </row>
     <row r="12">
@@ -753,28 +753,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.06985</v>
+        <v>-0.053</v>
       </c>
       <c r="C12" t="n">
-        <v>-5.831279854219419</v>
+        <v>-14.73020735642356</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.06985</v>
+        <v>-0.053</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.43155182491053</v>
+        <v>-23.8034016401698</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.06985</v>
+        <v>-0.053</v>
       </c>
       <c r="G12" t="n">
-        <v>-23.82672367412118</v>
+        <v>-14.34507783448803</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0447</v>
+        <v>-0.053</v>
       </c>
       <c r="I12" t="n">
-        <v>-12.32420463266306</v>
+        <v>-4.990595298409577</v>
       </c>
     </row>
     <row r="13">
@@ -782,28 +782,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.06685000000000001</v>
+        <v>-0.0483</v>
       </c>
       <c r="C13" t="n">
-        <v>-5.802750908292817</v>
+        <v>-14.70439707947154</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.06685000000000001</v>
+        <v>-0.0483</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.38954471715016</v>
+        <v>-23.75757799025846</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.06685000000000001</v>
+        <v>-0.0483</v>
       </c>
       <c r="G13" t="n">
-        <v>-23.81813257588358</v>
+        <v>-14.20612032244857</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0392</v>
+        <v>-0.0483</v>
       </c>
       <c r="I13" t="n">
-        <v>-12.30055252556137</v>
+        <v>-4.936827782878051</v>
       </c>
     </row>
     <row r="14">
@@ -811,28 +811,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.0638</v>
+        <v>-0.0436</v>
       </c>
       <c r="C14" t="n">
-        <v>-5.775689689487842</v>
+        <v>-14.67616708905527</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0638</v>
+        <v>-0.0436</v>
       </c>
       <c r="E14" t="n">
-        <v>-12.33952410280609</v>
+        <v>-23.72681841423529</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0638</v>
+        <v>-0.0436</v>
       </c>
       <c r="G14" t="n">
-        <v>-23.79974762565512</v>
+        <v>-14.06452476492668</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.03365</v>
+        <v>-0.0436</v>
       </c>
       <c r="I14" t="n">
-        <v>-12.28829799180941</v>
+        <v>-4.878678895432167</v>
       </c>
     </row>
     <row r="15">
@@ -840,28 +840,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0608</v>
+        <v>-0.03895</v>
       </c>
       <c r="C15" t="n">
-        <v>-5.752114322596726</v>
+        <v>-14.64370260007655</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0608</v>
+        <v>-0.03895</v>
       </c>
       <c r="E15" t="n">
-        <v>-12.29608783463588</v>
+        <v>-23.67828864326618</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0608</v>
+        <v>-0.03895</v>
       </c>
       <c r="G15" t="n">
-        <v>-23.80936965568123</v>
+        <v>-13.93121144322171</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.02815</v>
+        <v>-0.03895</v>
       </c>
       <c r="I15" t="n">
-        <v>-12.27655763429879</v>
+        <v>-4.816276248846132</v>
       </c>
     </row>
     <row r="16">
@@ -869,28 +869,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.0578</v>
+        <v>-0.03425</v>
       </c>
       <c r="C16" t="n">
-        <v>-5.725328302627054</v>
+        <v>-14.60135761445214</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0578</v>
+        <v>-0.03425</v>
       </c>
       <c r="E16" t="n">
-        <v>-12.25372343677305</v>
+        <v>-23.64040294845758</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0578</v>
+        <v>-0.03425</v>
       </c>
       <c r="G16" t="n">
-        <v>-23.78754826615774</v>
+        <v>-13.78538274294895</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0226</v>
+        <v>-0.03425</v>
       </c>
       <c r="I16" t="n">
-        <v>-12.26224639558146</v>
+        <v>-4.758127361400249</v>
       </c>
     </row>
     <row r="17">
@@ -898,28 +898,28 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.05475</v>
+        <v>-0.02955</v>
       </c>
       <c r="C17" t="n">
-        <v>-5.696248959029844</v>
+        <v>-14.57837033654174</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.05475</v>
+        <v>-0.02955</v>
       </c>
       <c r="E17" t="n">
-        <v>-12.21064445870531</v>
+        <v>-23.59178297345322</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.05475</v>
+        <v>-0.02955</v>
       </c>
       <c r="G17" t="n">
-        <v>-23.76589869859898</v>
+        <v>-13.64967677534132</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0171</v>
+        <v>-0.02955</v>
       </c>
       <c r="I17" t="n">
-        <v>-12.24793515686414</v>
+        <v>-4.702488191847056</v>
       </c>
     </row>
     <row r="18">
@@ -927,28 +927,28 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.05175</v>
+        <v>-0.02485</v>
       </c>
       <c r="C18" t="n">
-        <v>-5.659280582153893</v>
+        <v>-14.54671241871778</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.05175</v>
+        <v>-0.02485</v>
       </c>
       <c r="E18" t="n">
-        <v>-12.16123634167974</v>
+        <v>-23.55479931899721</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.05175</v>
+        <v>-0.02485</v>
       </c>
       <c r="G18" t="n">
-        <v>-23.73771989637966</v>
+        <v>-13.50532047254712</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.01155</v>
+        <v>-0.02485</v>
       </c>
       <c r="I18" t="n">
-        <v>-12.25384818363956</v>
+        <v>-4.641872124099885</v>
       </c>
     </row>
     <row r="19">
@@ -956,28 +956,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.04875</v>
+        <v>-0.02015</v>
       </c>
       <c r="C19" t="n">
-        <v>-5.634512686976457</v>
+        <v>-14.51747421435806</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.04875</v>
+        <v>-0.02015</v>
       </c>
       <c r="E19" t="n">
-        <v>-12.11004177414188</v>
+        <v>-23.50175934626518</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.04875</v>
+        <v>-0.02015</v>
       </c>
       <c r="G19" t="n">
-        <v>-23.73479892297888</v>
+        <v>-13.35771262532109</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.00605</v>
+        <v>-0.02015</v>
       </c>
       <c r="I19" t="n">
-        <v>-12.2343094864686</v>
+        <v>-4.584106074976615</v>
       </c>
     </row>
     <row r="20">
@@ -985,28 +985,28 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.04575</v>
+        <v>-0.01545</v>
       </c>
       <c r="C20" t="n">
-        <v>-5.605616809269447</v>
+        <v>-14.47996865566216</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.04575</v>
+        <v>-0.01545</v>
       </c>
       <c r="E20" t="n">
-        <v>-12.07370026657762</v>
+        <v>-23.45837120530581</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.04575</v>
+        <v>-0.01545</v>
       </c>
       <c r="G20" t="n">
-        <v>-23.72380231723475</v>
+        <v>-13.20660783408348</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0005</v>
+        <v>-0.01545</v>
       </c>
       <c r="I20" t="n">
-        <v>-12.2186271111077</v>
+        <v>-4.52446837183168</v>
       </c>
     </row>
     <row r="21">
@@ -1014,28 +1014,28 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.0427</v>
+        <v>-0.01075</v>
       </c>
       <c r="C21" t="n">
-        <v>-5.570850023075937</v>
+        <v>-14.45173866524588</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0427</v>
+        <v>-0.01075</v>
       </c>
       <c r="E21" t="n">
-        <v>-12.02648693161</v>
+        <v>-23.40415858011541</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0427</v>
+        <v>-0.01075</v>
       </c>
       <c r="G21" t="n">
-        <v>-23.69613898090968</v>
+        <v>-13.05004290219619</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00505</v>
+        <v>-0.01075</v>
       </c>
       <c r="I21" t="n">
-        <v>-12.19488930796579</v>
+        <v>-4.466404559568599</v>
       </c>
     </row>
     <row r="22">
@@ -1043,28 +1043,28 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.0397</v>
+        <v>-0.00605</v>
       </c>
       <c r="C22" t="n">
-        <v>-5.543880537216062</v>
+        <v>-14.41141010750834</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0397</v>
+        <v>-0.00605</v>
       </c>
       <c r="E22" t="n">
-        <v>-11.97605798572027</v>
+        <v>-23.35671125756941</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0397</v>
+        <v>-0.00605</v>
       </c>
       <c r="G22" t="n">
-        <v>-23.67586398906895</v>
+        <v>-12.90268045454992</v>
       </c>
       <c r="H22" t="n">
-        <v>0.01055</v>
+        <v>-0.00605</v>
       </c>
       <c r="I22" t="n">
-        <v>-12.17680744347863</v>
+        <v>-4.405831029412829</v>
       </c>
     </row>
     <row r="23">
@@ -1072,28 +1072,28 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.0367</v>
+        <v>-0.00135</v>
       </c>
       <c r="C23" t="n">
-        <v>-5.507095626230314</v>
+        <v>-14.38076040362782</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0367</v>
+        <v>-0.00135</v>
       </c>
       <c r="E23" t="n">
-        <v>-11.93798106908693</v>
+        <v>-23.29997291939178</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0367</v>
+        <v>-0.00135</v>
       </c>
       <c r="G23" t="n">
-        <v>-23.67019386423213</v>
+        <v>-12.74899896772482</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0161</v>
+        <v>-0.00135</v>
       </c>
       <c r="I23" t="n">
-        <v>-12.16001101959482</v>
+        <v>-4.347724679558348</v>
       </c>
     </row>
     <row r="24">
@@ -1101,28 +1101,28 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.03365</v>
+        <v>0.00335</v>
       </c>
       <c r="C24" t="n">
-        <v>-5.471870175311294</v>
+        <v>-14.34890084301516</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.03365</v>
+        <v>0.00335</v>
       </c>
       <c r="E24" t="n">
-        <v>-11.90015935966963</v>
+        <v>-23.25496110579776</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.03365</v>
+        <v>0.00335</v>
       </c>
       <c r="G24" t="n">
-        <v>-23.64802883077913</v>
+        <v>-12.59746472722263</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0216</v>
+        <v>0.00335</v>
       </c>
       <c r="I24" t="n">
-        <v>-12.14595686899817</v>
+        <v>-4.284471281144282</v>
       </c>
     </row>
     <row r="25">
@@ -1130,28 +1130,28 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.03065</v>
+        <v>0.00805</v>
       </c>
       <c r="C25" t="n">
-        <v>-5.438295917404103</v>
+        <v>-14.30232135882831</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.03065</v>
+        <v>0.00805</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.85075124264406</v>
+        <v>-23.19515583042133</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.03065</v>
+        <v>0.00805</v>
       </c>
       <c r="G25" t="n">
-        <v>-23.62826930483265</v>
+        <v>-12.44513293808621</v>
       </c>
       <c r="H25" t="n">
-        <v>0.02715</v>
+        <v>0.00805</v>
       </c>
       <c r="I25" t="n">
-        <v>-12.13447359960822</v>
+        <v>-4.224748502816542</v>
       </c>
     </row>
     <row r="26">
@@ -1159,28 +1159,28 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.02765</v>
+        <v>0.01275</v>
       </c>
       <c r="C26" t="n">
-        <v>-5.40453819360671</v>
+        <v>-14.26017801599259</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.02765</v>
+        <v>0.01275</v>
       </c>
       <c r="E26" t="n">
-        <v>-11.80348686623324</v>
+        <v>-23.14861054822792</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.02765</v>
+        <v>0.01275</v>
       </c>
       <c r="G26" t="n">
-        <v>-23.61933456266555</v>
+        <v>-12.29703429170066</v>
       </c>
       <c r="H26" t="n">
-        <v>0.03265</v>
+        <v>0.01275</v>
       </c>
       <c r="I26" t="n">
-        <v>-12.11493490243726</v>
+        <v>-4.162345856230506</v>
       </c>
     </row>
     <row r="27">
@@ -1188,28 +1188,28 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.0246</v>
+        <v>0.01745</v>
       </c>
       <c r="C27" t="n">
-        <v>-5.368945810907283</v>
+        <v>-14.21380017459442</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0246</v>
+        <v>0.01745</v>
       </c>
       <c r="E27" t="n">
-        <v>-11.74611628406719</v>
+        <v>-23.08907588495727</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0246</v>
+        <v>0.01745</v>
       </c>
       <c r="G27" t="n">
-        <v>-23.59527948760027</v>
+        <v>-12.13230982378633</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0382</v>
+        <v>0.01745</v>
       </c>
       <c r="I27" t="n">
-        <v>-12.09693873399032</v>
+        <v>-4.099262608182046</v>
       </c>
     </row>
     <row r="28">
@@ -1217,28 +1217,28 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.0216</v>
+        <v>0.02215</v>
       </c>
       <c r="C28" t="n">
-        <v>-5.333628627043161</v>
+        <v>-14.17266504570213</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0216</v>
+        <v>0.02215</v>
       </c>
       <c r="E28" t="n">
-        <v>-11.70303730599944</v>
+        <v>-23.02863918133403</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0216</v>
+        <v>0.02215</v>
       </c>
       <c r="G28" t="n">
-        <v>-23.57741000326607</v>
+        <v>-11.97451789400024</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0437</v>
+        <v>0.02215</v>
       </c>
       <c r="I28" t="n">
-        <v>-12.07714294869869</v>
+        <v>-4.037455487875633</v>
       </c>
     </row>
     <row r="29">
@@ -1246,28 +1246,28 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.0186</v>
+        <v>0.02685</v>
       </c>
       <c r="C29" t="n">
-        <v>-5.298127977288837</v>
+        <v>-14.13677262931573</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0186</v>
+        <v>0.02685</v>
       </c>
       <c r="E29" t="n">
-        <v>-11.65347606464425</v>
+        <v>-22.97623063684881</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0186</v>
+        <v>0.02685</v>
       </c>
       <c r="G29" t="n">
-        <v>-23.56039962875562</v>
+        <v>-11.811756622724</v>
       </c>
       <c r="H29" t="n">
-        <v>0.04925</v>
+        <v>0.02685</v>
       </c>
       <c r="I29" t="n">
-        <v>-12.06283170998137</v>
+        <v>-3.973606563181946</v>
       </c>
     </row>
     <row r="30">
@@ -1275,28 +1275,28 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.0156</v>
+        <v>0.03155</v>
       </c>
       <c r="C30" t="n">
-        <v>-5.267489173624898</v>
+        <v>-14.09745228552163</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0156</v>
+        <v>0.03155</v>
       </c>
       <c r="E30" t="n">
-        <v>-11.61218353708878</v>
+        <v>-22.89603924950395</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0156</v>
+        <v>0.03155</v>
       </c>
       <c r="G30" t="n">
-        <v>-23.52689434562898</v>
+        <v>-11.64850455228823</v>
       </c>
       <c r="H30" t="n">
-        <v>0.05475</v>
+        <v>0.03155</v>
       </c>
       <c r="I30" t="n">
-        <v>-12.03986517120147</v>
+        <v>-3.914862149456441</v>
       </c>
     </row>
     <row r="31">
@@ -1304,28 +1304,28 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.01255</v>
+        <v>0.03625</v>
       </c>
       <c r="C31" t="n">
-        <v>-5.230704262639151</v>
+        <v>-14.05087280133478</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.01255</v>
+        <v>0.03625</v>
       </c>
       <c r="E31" t="n">
-        <v>-11.55853898027694</v>
+        <v>-22.85003519152209</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.01255</v>
+        <v>0.03625</v>
       </c>
       <c r="G31" t="n">
-        <v>-23.50730664164726</v>
+        <v>-11.49482306546312</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0603</v>
+        <v>0.03625</v>
       </c>
       <c r="I31" t="n">
-        <v>-12.0264965889266</v>
+        <v>-3.853437867472641</v>
       </c>
     </row>
     <row r="32">
@@ -1333,28 +1333,28 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.009549999999999999</v>
+        <v>0.04095</v>
       </c>
       <c r="C32" t="n">
-        <v>-5.194561482269115</v>
+        <v>-14.00691467340086</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.009549999999999999</v>
+        <v>0.04095</v>
       </c>
       <c r="E32" t="n">
-        <v>-11.50744649562549</v>
+        <v>-22.77236951716446</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.009549999999999999</v>
+        <v>0.04095</v>
       </c>
       <c r="G32" t="n">
-        <v>-23.50387020235222</v>
+        <v>-11.32770595164613</v>
       </c>
       <c r="H32" t="n">
-        <v>0.06585000000000001</v>
+        <v>0.04095</v>
       </c>
       <c r="I32" t="n">
-        <v>-12.01578458389866</v>
+        <v>-3.792098660671643</v>
       </c>
     </row>
     <row r="33">
@@ -1362,28 +1362,28 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.00655</v>
+        <v>0.04565</v>
       </c>
       <c r="C33" t="n">
-        <v>-5.154749384095013</v>
+        <v>-13.97485346999952</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.00655</v>
+        <v>0.04565</v>
       </c>
       <c r="E33" t="n">
-        <v>-11.45895712457767</v>
+        <v>-22.70074751316917</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.00655</v>
+        <v>0.04565</v>
       </c>
       <c r="G33" t="n">
-        <v>-23.47655050995666</v>
+        <v>-11.16905512333088</v>
       </c>
       <c r="H33" t="n">
-        <v>0.07135</v>
+        <v>0.04565</v>
       </c>
       <c r="I33" t="n">
-        <v>-11.98921881142937</v>
+        <v>-3.728292273569358</v>
       </c>
     </row>
     <row r="34">
@@ -1391,28 +1391,28 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.0035</v>
+        <v>0.05035</v>
       </c>
       <c r="C34" t="n">
-        <v>-5.118606603724977</v>
+        <v>-13.93391998389592</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0035</v>
+        <v>0.05035</v>
       </c>
       <c r="E34" t="n">
-        <v>-11.41327503290631</v>
+        <v>-22.6299373454912</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0035</v>
+        <v>0.05035</v>
       </c>
       <c r="G34" t="n">
-        <v>-23.44373251468903</v>
+        <v>-10.99807296613265</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0769</v>
+        <v>0.05035</v>
       </c>
       <c r="I34" t="n">
-        <v>-11.97490757271205</v>
+        <v>-3.665591863843511</v>
       </c>
     </row>
     <row r="35">
@@ -1420,28 +1420,28 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.0005</v>
+        <v>0.05505</v>
       </c>
       <c r="C35" t="n">
-        <v>-5.085857942323702</v>
+        <v>-13.8901634987507</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0005</v>
+        <v>0.05505</v>
       </c>
       <c r="E35" t="n">
-        <v>-11.35835444001425</v>
+        <v>-22.54207861514936</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.0005</v>
+        <v>0.05505</v>
       </c>
       <c r="G35" t="n">
-        <v>-23.42156748123602</v>
+        <v>-10.82966750452191</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0824</v>
+        <v>0.05505</v>
       </c>
       <c r="I35" t="n">
-        <v>-11.94499965467404</v>
+        <v>-3.599190683665733</v>
       </c>
     </row>
     <row r="36">
@@ -1449,28 +1449,28 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>0.0025</v>
+        <v>0.05975</v>
       </c>
       <c r="C36" t="n">
-        <v>-5.024305136160518</v>
+        <v>-13.85548093909642</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0025</v>
+        <v>0.05975</v>
       </c>
       <c r="E36" t="n">
-        <v>-11.31185568525155</v>
+        <v>-22.46378151254493</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0025</v>
+        <v>0.05975</v>
       </c>
       <c r="G36" t="n">
-        <v>-23.41710011015247</v>
+        <v>-10.65966694564272</v>
       </c>
       <c r="H36" t="n">
-        <v>0.08795</v>
+        <v>0.05975</v>
       </c>
       <c r="I36" t="n">
-        <v>-11.92049058717012</v>
+        <v>-3.539255217380986</v>
       </c>
     </row>
     <row r="37">
@@ -1478,28 +1478,28 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>0.00555</v>
+        <v>0.06444999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>-5.002656161116537</v>
+        <v>-13.80769159817744</v>
       </c>
       <c r="D37" t="n">
-        <v>0.00555</v>
+        <v>0.06444999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>-11.26290694121486</v>
+        <v>-22.38755910275145</v>
       </c>
       <c r="F37" t="n">
-        <v>0.00555</v>
+        <v>0.06444999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>-23.39682511831174</v>
+        <v>-10.497396473526</v>
       </c>
       <c r="H37" t="n">
-        <v>0.09345000000000001</v>
+        <v>0.06444999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>-11.90994997422263</v>
+        <v>-3.475661518235708</v>
       </c>
     </row>
     <row r="38">
@@ -1507,28 +1507,28 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>0.00855</v>
+        <v>0.06915</v>
       </c>
       <c r="C38" t="n">
-        <v>-4.970457897385871</v>
+        <v>-13.76373347024352</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00855</v>
+        <v>0.06915</v>
       </c>
       <c r="E38" t="n">
-        <v>-11.21508110892874</v>
+        <v>-22.2905897648485</v>
       </c>
       <c r="F38" t="n">
-        <v>0.00855</v>
+        <v>0.06915</v>
       </c>
       <c r="G38" t="n">
-        <v>-23.37569101664725</v>
+        <v>-10.32678241569742</v>
       </c>
       <c r="H38" t="n">
-        <v>0.099</v>
+        <v>0.06915</v>
       </c>
       <c r="I38" t="n">
-        <v>-11.89298215825838</v>
+        <v>-3.412535732595846</v>
       </c>
     </row>
     <row r="39">
@@ -1536,28 +1536,28 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>0.01155</v>
+        <v>0.07385</v>
       </c>
       <c r="C39" t="n">
-        <v>-4.936516707698273</v>
+        <v>-13.72340491250599</v>
       </c>
       <c r="D39" t="n">
-        <v>0.01155</v>
+        <v>0.07385</v>
       </c>
       <c r="E39" t="n">
-        <v>-11.17348233271403</v>
+        <v>-22.19064369378201</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01155</v>
+        <v>0.07385</v>
       </c>
       <c r="G39" t="n">
-        <v>-23.35060500979346</v>
+        <v>-10.14457322772514</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1045</v>
+        <v>0.07385</v>
       </c>
       <c r="I39" t="n">
-        <v>-11.87052979571982</v>
+        <v>-3.345411413364242</v>
       </c>
     </row>
     <row r="40">
@@ -1565,28 +1565,28 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>0.01455</v>
+        <v>0.0785</v>
       </c>
       <c r="C40" t="n">
-        <v>-4.896429410688868</v>
+        <v>-13.66291207589968</v>
       </c>
       <c r="D40" t="n">
-        <v>0.01455</v>
+        <v>0.0785</v>
       </c>
       <c r="E40" t="n">
-        <v>-11.12203255796014</v>
+        <v>-22.0951176204432</v>
       </c>
       <c r="F40" t="n">
-        <v>0.01455</v>
+        <v>0.0785</v>
       </c>
       <c r="G40" t="n">
-        <v>-23.32002070006761</v>
+        <v>-9.96475668565553</v>
       </c>
       <c r="H40" t="n">
-        <v>0.11005</v>
+        <v>0.0785</v>
       </c>
       <c r="I40" t="n">
-        <v>-11.84679199257791</v>
+        <v>-3.284625195251464</v>
       </c>
     </row>
     <row r="41">
@@ -1594,28 +1594,28 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>0.0176</v>
+        <v>0.0832</v>
       </c>
       <c r="C41" t="n">
-        <v>-4.856525579569666</v>
+        <v>-13.59516009890062</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0176</v>
+        <v>0.0832</v>
       </c>
       <c r="E41" t="n">
-        <v>-11.06491718301012</v>
+        <v>-21.99499114130619</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0176</v>
+        <v>0.0832</v>
       </c>
       <c r="G41" t="n">
-        <v>-23.32173891971512</v>
+        <v>-9.797516872048654</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1156</v>
+        <v>0.0832</v>
       </c>
       <c r="I41" t="n">
-        <v>-11.81662698641923</v>
+        <v>-3.219670293181338</v>
       </c>
     </row>
     <row r="42">
@@ -1623,28 +1623,28 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>0.0206</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>-4.816530015505362</v>
+        <v>-13.5497904714459</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0206</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>-11.01673406062155</v>
+        <v>-21.88656589092541</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0206</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>-23.28565630711721</v>
+        <v>-9.623651269788239</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1211</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>-11.79366044763933</v>
+        <v>-3.157012421046893</v>
       </c>
     </row>
     <row r="43">
@@ -1652,28 +1652,28 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>0.0236</v>
+        <v>0.0926</v>
       </c>
       <c r="C43" t="n">
-        <v>-4.780295502190224</v>
+        <v>-13.49796827475316</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0236</v>
+        <v>0.0926</v>
       </c>
       <c r="E43" t="n">
-        <v>-10.96548845164049</v>
+        <v>-21.77155574597074</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0236</v>
+        <v>0.0926</v>
       </c>
       <c r="G43" t="n">
-        <v>-23.25558746328561</v>
+        <v>-9.443343928559107</v>
       </c>
       <c r="H43" t="n">
-        <v>0.12665</v>
+        <v>0.0926</v>
       </c>
       <c r="I43" t="n">
-        <v>-11.76478088208401</v>
+        <v>-3.090398552912107</v>
       </c>
     </row>
     <row r="44">
@@ -1681,28 +1681,28 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>0.02665</v>
+        <v>0.0973</v>
       </c>
       <c r="C44" t="n">
-        <v>-4.74195113113775</v>
+        <v>-13.44816250594731</v>
       </c>
       <c r="D44" t="n">
-        <v>0.02665</v>
+        <v>0.0973</v>
       </c>
       <c r="E44" t="n">
-        <v>-10.91648866616059</v>
+        <v>-21.64247377151575</v>
       </c>
       <c r="F44" t="n">
-        <v>0.02665</v>
+        <v>0.0973</v>
       </c>
       <c r="G44" t="n">
-        <v>-23.25146373613157</v>
+        <v>-9.257392396995483</v>
       </c>
       <c r="H44" t="n">
-        <v>0.13215</v>
+        <v>0.0973</v>
       </c>
       <c r="I44" t="n">
-        <v>-11.73195929867841</v>
+        <v>-3.019658538411373</v>
       </c>
     </row>
     <row r="45">
@@ -1710,28 +1710,28 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>0.02965</v>
+        <v>0.102</v>
       </c>
       <c r="C45" t="n">
-        <v>-4.702322498853852</v>
+        <v>-13.3910975967487</v>
       </c>
       <c r="D45" t="n">
-        <v>0.02965</v>
+        <v>0.102</v>
       </c>
       <c r="E45" t="n">
-        <v>-10.85967953986983</v>
+        <v>-21.53431913324073</v>
       </c>
       <c r="F45" t="n">
-        <v>0.02965</v>
+        <v>0.102</v>
       </c>
       <c r="G45" t="n">
-        <v>-23.20782095708457</v>
+        <v>-9.075183209023207</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1377</v>
+        <v>0.102</v>
       </c>
       <c r="I45" t="n">
-        <v>-11.70136581231862</v>
+        <v>-2.95427826042723</v>
       </c>
     </row>
     <row r="46">
@@ -1739,28 +1739,28 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>0.03265</v>
+        <v>0.1067</v>
       </c>
       <c r="C46" t="n">
-        <v>-4.668014377385848</v>
+        <v>-13.32798340388945</v>
       </c>
       <c r="D46" t="n">
-        <v>0.03265</v>
+        <v>0.1067</v>
       </c>
       <c r="E46" t="n">
-        <v>-10.80955684263934</v>
+        <v>-21.39603634718936</v>
       </c>
       <c r="F46" t="n">
-        <v>0.03265</v>
+        <v>0.1067</v>
       </c>
       <c r="G46" t="n">
-        <v>-23.18325041612503</v>
+        <v>-8.883832886704846</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1432</v>
+        <v>0.1067</v>
       </c>
       <c r="I46" t="n">
-        <v>-11.6652020833443</v>
+        <v>-2.884771836077141</v>
       </c>
     </row>
     <row r="47">
@@ -1768,28 +1768,28 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>0.0357</v>
+        <v>0.1114</v>
       </c>
       <c r="C47" t="n">
-        <v>-4.631321199345202</v>
+        <v>-13.26708728170577</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0357</v>
+        <v>0.1114</v>
       </c>
       <c r="E47" t="n">
-        <v>-10.76392579241118</v>
+        <v>-21.25622009253859</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0357</v>
+        <v>0.1114</v>
       </c>
       <c r="G47" t="n">
-        <v>-23.16469364393182</v>
+        <v>-8.696961106717117</v>
       </c>
       <c r="H47" t="n">
-        <v>0.14875</v>
+        <v>0.1114</v>
       </c>
       <c r="I47" t="n">
-        <v>-11.63263758805937</v>
+        <v>-2.819731858824211</v>
       </c>
     </row>
     <row r="48">
@@ -1797,28 +1797,28 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>0.0387</v>
+        <v>0.1161</v>
       </c>
       <c r="C48" t="n">
-        <v>-4.593068561237829</v>
+        <v>-13.20820758740897</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0387</v>
+        <v>0.1161</v>
       </c>
       <c r="E48" t="n">
-        <v>-10.70732083189325</v>
+        <v>-21.1188393468398</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0387</v>
+        <v>0.1161</v>
       </c>
       <c r="G48" t="n">
-        <v>-23.16211631446054</v>
+        <v>-8.49855554648064</v>
       </c>
       <c r="H48" t="n">
-        <v>0.15425</v>
+        <v>0.1161</v>
       </c>
       <c r="I48" t="n">
-        <v>-11.60718586411299</v>
+        <v>-2.753926204926053</v>
       </c>
     </row>
     <row r="49">
@@ -1826,28 +1826,28 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>0.0417</v>
+        <v>0.1208</v>
       </c>
       <c r="C49" t="n">
-        <v>-4.553715127789236</v>
+        <v>-13.13964903925516</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0417</v>
+        <v>0.1208</v>
       </c>
       <c r="E49" t="n">
-        <v>-10.66276165197247</v>
+        <v>-20.99417737011247</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0417</v>
+        <v>0.1208</v>
       </c>
       <c r="G49" t="n">
-        <v>-23.14527776191485</v>
+        <v>-8.312358615337255</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1598</v>
+        <v>0.1208</v>
       </c>
       <c r="I49" t="n">
-        <v>-11.57153631138001</v>
+        <v>-2.688333238984904</v>
       </c>
     </row>
     <row r="50">
@@ -1855,28 +1855,28 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0447</v>
+        <v>0.1255</v>
       </c>
       <c r="C50" t="n">
-        <v>-4.515370756736761</v>
+        <v>-13.06665434975022</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0447</v>
+        <v>0.1255</v>
       </c>
       <c r="E50" t="n">
-        <v>-10.61575248277768</v>
+        <v>-20.8295550057656</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0447</v>
+        <v>0.1255</v>
       </c>
       <c r="G50" t="n">
-        <v>-23.11486527415375</v>
+        <v>-8.109474512770143</v>
       </c>
       <c r="H50" t="n">
-        <v>0.16535</v>
+        <v>0.1255</v>
       </c>
       <c r="I50" t="n">
-        <v>-11.53922890421574</v>
+        <v>-2.618571589086404</v>
       </c>
     </row>
     <row r="51">
@@ -1884,28 +1884,28 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>0.04775</v>
+        <v>0.1302</v>
       </c>
       <c r="C51" t="n">
-        <v>-4.479503175202031</v>
+        <v>-13.01120258286111</v>
       </c>
       <c r="D51" t="n">
-        <v>0.04775</v>
+        <v>0.1302</v>
       </c>
       <c r="E51" t="n">
-        <v>-10.55480899958706</v>
+        <v>-20.66619549791235</v>
       </c>
       <c r="F51" t="n">
-        <v>0.04775</v>
+        <v>0.1302</v>
       </c>
       <c r="G51" t="n">
-        <v>-23.06933245349448</v>
+        <v>-7.916099643918758</v>
       </c>
       <c r="H51" t="n">
-        <v>0.17085</v>
+        <v>0.1302</v>
       </c>
       <c r="I51" t="n">
-        <v>-11.49569531578221</v>
+        <v>-2.546895747574837</v>
       </c>
     </row>
     <row r="52">
@@ -1913,28 +1913,28 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>0.05075</v>
+        <v>0.1349</v>
       </c>
       <c r="C52" t="n">
-        <v>-4.44198440065547</v>
+        <v>-12.93961939287698</v>
       </c>
       <c r="D52" t="n">
-        <v>0.05075</v>
+        <v>0.1349</v>
       </c>
       <c r="E52" t="n">
-        <v>-10.49080302980393</v>
+        <v>-20.4934547703922</v>
       </c>
       <c r="F52" t="n">
-        <v>0.05075</v>
+        <v>0.1349</v>
       </c>
       <c r="G52" t="n">
-        <v>-23.0499165714775</v>
+        <v>-7.716221686203717</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1764</v>
+        <v>0.1349</v>
       </c>
       <c r="I52" t="n">
-        <v>-11.45199033526822</v>
+        <v>-2.473816165547019</v>
       </c>
     </row>
     <row r="53">
@@ -1942,28 +1942,28 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>0.05375</v>
+        <v>0.1396</v>
       </c>
       <c r="C53" t="n">
-        <v>-4.40272270015198</v>
+        <v>-12.86642306058336</v>
       </c>
       <c r="D53" t="n">
-        <v>0.05375</v>
+        <v>0.1396</v>
       </c>
       <c r="E53" t="n">
-        <v>-10.44307928040424</v>
+        <v>-20.30754425372432</v>
       </c>
       <c r="F53" t="n">
-        <v>0.05375</v>
+        <v>0.1396</v>
       </c>
       <c r="G53" t="n">
-        <v>-23.02672060623599</v>
+        <v>-7.505791546558966</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1819</v>
+        <v>0.1396</v>
       </c>
       <c r="I53" t="n">
-        <v>-11.40502890522573</v>
+        <v>-2.402735850315073</v>
       </c>
     </row>
     <row r="54">
@@ -1971,28 +1971,28 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>0.0568</v>
+        <v>0.1443</v>
       </c>
       <c r="C54" t="n">
-        <v>-4.358690886503204</v>
+        <v>-12.7920168715576</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0568</v>
+        <v>0.1443</v>
       </c>
       <c r="E54" t="n">
-        <v>-10.39035346957013</v>
+        <v>-20.13516434234521</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0568</v>
+        <v>0.1443</v>
       </c>
       <c r="G54" t="n">
-        <v>-23.02483056462371</v>
+        <v>-7.305668189264164</v>
       </c>
       <c r="H54" t="n">
-        <v>0.18745</v>
+        <v>0.1443</v>
       </c>
       <c r="I54" t="n">
-        <v>-11.36106683659107</v>
+        <v>-2.331017471212104</v>
       </c>
     </row>
     <row r="55">
@@ -2000,28 +2000,28 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>0.0598</v>
+        <v>0.149</v>
       </c>
       <c r="C55" t="n">
-        <v>-4.321355577846847</v>
+        <v>-12.71055318492778</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0598</v>
+        <v>0.149</v>
       </c>
       <c r="E55" t="n">
-        <v>-10.33752557584961</v>
+        <v>-19.93545260828276</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0598</v>
+        <v>0.149</v>
       </c>
       <c r="G55" t="n">
-        <v>-22.98256236129473</v>
+        <v>-7.100268741004507</v>
       </c>
       <c r="H55" t="n">
-        <v>0.19295</v>
+        <v>0.149</v>
       </c>
       <c r="I55" t="n">
-        <v>-11.30622137084803</v>
+        <v>-2.253854280409739</v>
       </c>
     </row>
     <row r="56">
@@ -2029,28 +2029,28 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.1537</v>
       </c>
       <c r="C56" t="n">
-        <v>-4.282919473849271</v>
+        <v>-12.62929114108665</v>
       </c>
       <c r="D56" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.1537</v>
       </c>
       <c r="E56" t="n">
-        <v>-10.27959353780827</v>
+        <v>-19.73321516123306</v>
       </c>
       <c r="F56" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.1537</v>
       </c>
       <c r="G56" t="n">
-        <v>-22.96520834285478</v>
+        <v>-6.884071711235382</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1985</v>
+        <v>0.1537</v>
       </c>
       <c r="I56" t="n">
-        <v>-11.24674831893292</v>
+        <v>-2.183667254597225</v>
       </c>
     </row>
     <row r="57">
@@ -2058,28 +2058,28 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>0.06585000000000001</v>
+        <v>0.1584</v>
       </c>
       <c r="C57" t="n">
-        <v>-4.241089250882935</v>
+        <v>-12.5433913131057</v>
       </c>
       <c r="D57" t="n">
-        <v>0.06585000000000001</v>
+        <v>0.1584</v>
       </c>
       <c r="E57" t="n">
-        <v>-10.22758230717908</v>
+        <v>-19.52340057522166</v>
       </c>
       <c r="F57" t="n">
-        <v>0.06585000000000001</v>
+        <v>0.1584</v>
       </c>
       <c r="G57" t="n">
-        <v>-22.93445221116417</v>
+        <v>-6.658058698275831</v>
       </c>
       <c r="H57" t="n">
-        <v>0.204</v>
+        <v>0.1584</v>
       </c>
       <c r="I57" t="n">
-        <v>-11.18393312144909</v>
+        <v>-2.105270473644217</v>
       </c>
     </row>
     <row r="58">
@@ -2087,28 +2087,28 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>0.06884999999999999</v>
+        <v>0.1631</v>
       </c>
       <c r="C58" t="n">
-        <v>-4.204029141061882</v>
+        <v>-12.45628162839262</v>
       </c>
       <c r="D58" t="n">
-        <v>0.06884999999999999</v>
+        <v>0.1631</v>
       </c>
       <c r="E58" t="n">
-        <v>-10.1656690365675</v>
+        <v>-19.29725905882844</v>
       </c>
       <c r="F58" t="n">
-        <v>0.06884999999999999</v>
+        <v>0.1631</v>
       </c>
       <c r="G58" t="n">
-        <v>-22.91056895806365</v>
+        <v>-6.440818720292725</v>
       </c>
       <c r="H58" t="n">
-        <v>0.20955</v>
+        <v>0.1631</v>
       </c>
       <c r="I58" t="n">
-        <v>-11.13611473100437</v>
+        <v>-2.036061812433938</v>
       </c>
     </row>
     <row r="59">
@@ -2116,28 +2116,28 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>0.07185</v>
+        <v>0.1678</v>
       </c>
       <c r="C59" t="n">
-        <v>-4.164217042887782</v>
+        <v>-12.36513908790579</v>
       </c>
       <c r="D59" t="n">
-        <v>0.07185</v>
+        <v>0.1678</v>
       </c>
       <c r="E59" t="n">
-        <v>-10.10834949584465</v>
+        <v>-19.06985468594162</v>
       </c>
       <c r="F59" t="n">
-        <v>0.07185</v>
+        <v>0.1678</v>
       </c>
       <c r="G59" t="n">
-        <v>-22.8846238413861</v>
+        <v>-6.223578742309617</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2151</v>
+        <v>0.1678</v>
       </c>
       <c r="I59" t="n">
-        <v>-11.07115713251495</v>
+        <v>-1.961621027481271</v>
       </c>
     </row>
     <row r="60">
@@ -2145,28 +2145,28 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>0.07485</v>
+        <v>0.1725</v>
       </c>
       <c r="C60" t="n">
-        <v>-4.124680143548987</v>
+        <v>-12.27863433155878</v>
       </c>
       <c r="D60" t="n">
-        <v>0.07485</v>
+        <v>0.1725</v>
       </c>
       <c r="E60" t="n">
-        <v>-10.05230599120201</v>
+        <v>-18.81475767423041</v>
       </c>
       <c r="F60" t="n">
-        <v>0.07485</v>
+        <v>0.1725</v>
       </c>
       <c r="G60" t="n">
-        <v>-22.86108423221508</v>
+        <v>-5.993455286389077</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2206</v>
+        <v>0.1725</v>
       </c>
       <c r="I60" t="n">
-        <v>-11.00662801422665</v>
+        <v>-1.886839941797392</v>
       </c>
     </row>
     <row r="61">
@@ -2174,28 +2174,28 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>0.0779</v>
+        <v>0.1772</v>
       </c>
       <c r="C61" t="n">
-        <v>-4.088537363178951</v>
+        <v>-12.17156201076562</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0779</v>
+        <v>0.1772</v>
       </c>
       <c r="E61" t="n">
-        <v>-9.995394782024835</v>
+        <v>-18.55948025444868</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0779</v>
+        <v>0.1772</v>
       </c>
       <c r="G61" t="n">
-        <v>-22.82311157800489</v>
+        <v>-5.770632467966414</v>
       </c>
       <c r="H61" t="n">
-        <v>0.22615</v>
+        <v>0.1772</v>
       </c>
       <c r="I61" t="n">
-        <v>-10.9353289087607</v>
+        <v>-1.808825999166997</v>
       </c>
     </row>
     <row r="62">
@@ -2203,28 +2203,28 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>0.0809</v>
+        <v>0.1819</v>
       </c>
       <c r="C62" t="n">
-        <v>-4.051385520412796</v>
+        <v>-12.07618497171635</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0809</v>
+        <v>0.1819</v>
       </c>
       <c r="E62" t="n">
-        <v>-9.939759608927863</v>
+        <v>-18.29545304324688</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0809</v>
+        <v>0.1819</v>
       </c>
       <c r="G62" t="n">
-        <v>-22.78342070414719</v>
+        <v>-5.544496755216984</v>
       </c>
       <c r="H62" t="n">
-        <v>0.23165</v>
+        <v>0.1819</v>
       </c>
       <c r="I62" t="n">
-        <v>-10.84577654672713</v>
+        <v>-1.734512826988535</v>
       </c>
     </row>
     <row r="63">
@@ -2232,28 +2232,28 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>0.0839</v>
+        <v>0.1866</v>
       </c>
       <c r="C63" t="n">
-        <v>-4.014325410591745</v>
+        <v>-11.98423586007477</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0839</v>
+        <v>0.1866</v>
       </c>
       <c r="E63" t="n">
-        <v>-9.879071332953274</v>
+        <v>-18.01771481868577</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0839</v>
+        <v>0.1866</v>
       </c>
       <c r="G63" t="n">
-        <v>-22.74665080369027</v>
+        <v>-5.320140189420817</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2372</v>
+        <v>0.1866</v>
       </c>
       <c r="I63" t="n">
-        <v>-10.74979698167681</v>
+        <v>-1.654712305519277</v>
       </c>
     </row>
     <row r="64">
@@ -2261,28 +2261,28 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>0.08695</v>
+        <v>0.1913</v>
       </c>
       <c r="C64" t="n">
-        <v>-3.972770386460714</v>
+        <v>-11.86929947052279</v>
       </c>
       <c r="D64" t="n">
-        <v>0.08695</v>
+        <v>0.1913</v>
       </c>
       <c r="E64" t="n">
-        <v>-9.826906977994462</v>
+        <v>-17.71931987005046</v>
       </c>
       <c r="F64" t="n">
-        <v>0.08695</v>
+        <v>0.1913</v>
       </c>
       <c r="G64" t="n">
-        <v>-22.72637581184953</v>
+        <v>-5.078605653041406</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2427</v>
+        <v>0.1913</v>
       </c>
       <c r="I64" t="n">
-        <v>-10.64858995817285</v>
+        <v>-1.575549847921041</v>
       </c>
     </row>
     <row r="65">
@@ -2290,28 +2290,28 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>0.08995</v>
+        <v>0.19595</v>
       </c>
       <c r="C65" t="n">
-        <v>-3.932591356506207</v>
+        <v>-11.74407929874774</v>
       </c>
       <c r="D65" t="n">
-        <v>0.08995</v>
+        <v>0.19595</v>
       </c>
       <c r="E65" t="n">
-        <v>-9.767290572327246</v>
+        <v>-17.43427511863341</v>
       </c>
       <c r="F65" t="n">
-        <v>0.08995</v>
+        <v>0.19595</v>
       </c>
       <c r="G65" t="n">
-        <v>-22.71726924771768</v>
+        <v>-4.835721418973312</v>
       </c>
       <c r="H65" t="n">
-        <v>0.24825</v>
+        <v>0.19595</v>
       </c>
       <c r="I65" t="n">
-        <v>-10.53932750688788</v>
+        <v>-1.496557540688411</v>
       </c>
     </row>
     <row r="66">
@@ -2319,28 +2319,28 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>0.09295</v>
+        <v>0.20065</v>
       </c>
       <c r="C66" t="n">
-        <v>-3.892962724222309</v>
+        <v>-11.6204722692822</v>
       </c>
       <c r="D66" t="n">
-        <v>0.09295</v>
+        <v>0.20065</v>
       </c>
       <c r="E66" t="n">
-        <v>-9.711042901911776</v>
+        <v>-17.13308384490508</v>
       </c>
       <c r="F66" t="n">
-        <v>0.09295</v>
+        <v>0.20065</v>
       </c>
       <c r="G66" t="n">
-        <v>-22.70300802464326</v>
+        <v>-4.585659247197219</v>
       </c>
       <c r="H66" t="n">
-        <v>0.25375</v>
+        <v>0.20065</v>
       </c>
       <c r="I66" t="n">
-        <v>-10.41386850400066</v>
+        <v>-1.41947942506885</v>
       </c>
     </row>
     <row r="67">
@@ -2348,28 +2348,28 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>0.096</v>
+        <v>0.20535</v>
       </c>
       <c r="C67" t="n">
-        <v>-3.855902614401256</v>
+        <v>-11.49363895519764</v>
       </c>
       <c r="D67" t="n">
-        <v>0.096</v>
+        <v>0.20535</v>
       </c>
       <c r="E67" t="n">
-        <v>-9.652038993563059</v>
+        <v>-16.81755012957064</v>
       </c>
       <c r="F67" t="n">
-        <v>0.096</v>
+        <v>0.20535</v>
       </c>
       <c r="G67" t="n">
-        <v>-22.67345464670592</v>
+        <v>-4.338357820693433</v>
       </c>
       <c r="H67" t="n">
-        <v>0.2593</v>
+        <v>0.20535</v>
       </c>
       <c r="I67" t="n">
-        <v>-10.28866658923412</v>
+        <v>-1.334489317448605</v>
       </c>
     </row>
     <row r="68">
@@ -2377,28 +2377,28 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>0.099</v>
+        <v>0.21005</v>
       </c>
       <c r="C68" t="n">
-        <v>-3.814714522050632</v>
+        <v>-11.35753007283346</v>
       </c>
       <c r="D68" t="n">
-        <v>0.099</v>
+        <v>0.21005</v>
       </c>
       <c r="E68" t="n">
-        <v>-9.586961153472563</v>
+        <v>-16.47134704224829</v>
       </c>
       <c r="F68" t="n">
-        <v>0.099</v>
+        <v>0.21005</v>
       </c>
       <c r="G68" t="n">
-        <v>-22.64905592771114</v>
+        <v>-4.079829363415597</v>
       </c>
       <c r="H68" t="n">
-        <v>0.2648</v>
+        <v>0.21005</v>
       </c>
       <c r="I68" t="n">
-        <v>-10.14186927233126</v>
+        <v>-1.249414134645558</v>
       </c>
     </row>
     <row r="69">
@@ -2406,28 +2406,28 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>0.102</v>
+        <v>0.21475</v>
       </c>
       <c r="C69" t="n">
-        <v>-3.774994156821633</v>
+        <v>-11.22061461931453</v>
       </c>
       <c r="D69" t="n">
-        <v>0.102</v>
+        <v>0.21475</v>
       </c>
       <c r="E69" t="n">
-        <v>-9.529182239760846</v>
+        <v>-16.1306464010767</v>
       </c>
       <c r="F69" t="n">
-        <v>0.102</v>
+        <v>0.21475</v>
       </c>
       <c r="G69" t="n">
-        <v>-22.61417606886649</v>
+        <v>-3.815349966328567</v>
       </c>
       <c r="H69" t="n">
-        <v>0.27035</v>
+        <v>0.21475</v>
       </c>
       <c r="I69" t="n">
-        <v>-9.969963015642904</v>
+        <v>-1.163318049648873</v>
       </c>
     </row>
     <row r="70">
@@ -2435,28 +2435,28 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>0.10505</v>
+        <v>0.21945</v>
       </c>
       <c r="C70" t="n">
-        <v>-3.73619112104365</v>
+        <v>-11.08087616675397</v>
       </c>
       <c r="D70" t="n">
-        <v>0.10505</v>
+        <v>0.21945</v>
       </c>
       <c r="E70" t="n">
-        <v>-9.46665647183076</v>
+        <v>-15.76270414125704</v>
       </c>
       <c r="F70" t="n">
-        <v>0.10505</v>
+        <v>0.21945</v>
       </c>
       <c r="G70" t="n">
-        <v>-22.57259515339651</v>
+        <v>-3.554122113673365</v>
       </c>
       <c r="H70" t="n">
-        <v>0.2759</v>
+        <v>0.21945</v>
       </c>
       <c r="I70" t="n">
-        <v>-9.788030322248401</v>
+        <v>-1.078455554802833</v>
       </c>
     </row>
     <row r="71">
@@ -2464,28 +2464,28 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>0.10805</v>
+        <v>0.22415</v>
       </c>
       <c r="C71" t="n">
-        <v>-3.696470755814651</v>
+        <v>-10.9231915060002</v>
       </c>
       <c r="D71" t="n">
-        <v>0.10805</v>
+        <v>0.22415</v>
       </c>
       <c r="E71" t="n">
-        <v>-9.399536974011935</v>
+        <v>-15.37266189279902</v>
       </c>
       <c r="F71" t="n">
-        <v>0.10805</v>
+        <v>0.22415</v>
       </c>
       <c r="G71" t="n">
-        <v>-22.54888372226074</v>
+        <v>-3.273200944742371</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2814</v>
+        <v>0.22415</v>
       </c>
       <c r="I71" t="n">
-        <v>-9.589986773291878</v>
+        <v>-0.9875952595691784</v>
       </c>
     </row>
     <row r="72">
@@ -2493,28 +2493,28 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>0.11105</v>
+        <v>0.22885</v>
       </c>
       <c r="C72" t="n">
-        <v>-3.659410645993598</v>
+        <v>-10.75441649186862</v>
       </c>
       <c r="D72" t="n">
-        <v>0.11105</v>
+        <v>0.22885</v>
       </c>
       <c r="E72" t="n">
-        <v>-9.341502853084176</v>
+        <v>-14.99263229225471</v>
       </c>
       <c r="F72" t="n">
-        <v>0.11105</v>
+        <v>0.22885</v>
       </c>
       <c r="G72" t="n">
-        <v>-22.51915852235865</v>
+        <v>-2.990561978753052</v>
       </c>
       <c r="H72" t="n">
-        <v>0.28695</v>
+        <v>0.22885</v>
       </c>
       <c r="I72" t="n">
-        <v>-9.373175791526409</v>
+        <v>-0.9020947008521155</v>
       </c>
     </row>
     <row r="73">
@@ -2522,28 +2522,28 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>0.11405</v>
+        <v>0.23355</v>
       </c>
       <c r="C73" t="n">
-        <v>-3.620057212545006</v>
+        <v>-10.57172812531758</v>
       </c>
       <c r="D73" t="n">
-        <v>0.11405</v>
+        <v>0.23355</v>
       </c>
       <c r="E73" t="n">
-        <v>-9.275455225572724</v>
+        <v>-14.60655902134808</v>
       </c>
       <c r="F73" t="n">
-        <v>0.11405</v>
+        <v>0.23355</v>
       </c>
       <c r="G73" t="n">
-        <v>-22.48943332245656</v>
+        <v>-2.712892354253887</v>
       </c>
       <c r="H73" t="n">
-        <v>0.29245</v>
+        <v>0.23355</v>
       </c>
       <c r="I73" t="n">
-        <v>-9.141710786882717</v>
+        <v>-0.8122553078120973</v>
       </c>
     </row>
     <row r="74">
@@ -2551,28 +2551,28 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>0.1171</v>
+        <v>0.23825</v>
       </c>
       <c r="C74" t="n">
-        <v>-3.579969915535601</v>
+        <v>-10.37754611981135</v>
       </c>
       <c r="D74" t="n">
-        <v>0.1171</v>
+        <v>0.23825</v>
       </c>
       <c r="E74" t="n">
-        <v>-9.202670127557784</v>
+        <v>-14.18043515878664</v>
       </c>
       <c r="F74" t="n">
-        <v>0.1171</v>
+        <v>0.23825</v>
       </c>
       <c r="G74" t="n">
-        <v>-22.44922698270459</v>
+        <v>-2.426265645093458</v>
       </c>
       <c r="H74" t="n">
-        <v>0.298</v>
+        <v>0.23825</v>
       </c>
       <c r="I74" t="n">
-        <v>-8.872710916621134</v>
+        <v>-0.7213524749870409</v>
       </c>
     </row>
     <row r="75">
@@ -2580,28 +2580,28 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>0.1201</v>
+        <v>0.24295</v>
       </c>
       <c r="C75" t="n">
-        <v>-3.541258612702719</v>
+        <v>-10.16945076188566</v>
       </c>
       <c r="D75" t="n">
-        <v>0.1201</v>
+        <v>0.24295</v>
       </c>
       <c r="E75" t="n">
-        <v>-9.143615177765861</v>
+        <v>-13.74646354515771</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1201</v>
+        <v>0.24295</v>
       </c>
       <c r="G75" t="n">
-        <v>-22.43135749837039</v>
+        <v>-2.129270803688142</v>
       </c>
       <c r="H75" t="n">
-        <v>0.3035</v>
+        <v>0.24295</v>
       </c>
       <c r="I75" t="n">
-        <v>-8.589999679923789</v>
+        <v>-0.6262809582046353</v>
       </c>
     </row>
     <row r="76">
@@ -2609,28 +2609,28 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>0.1231</v>
+        <v>0.24765</v>
       </c>
       <c r="C76" t="n">
-        <v>-3.503831571101261</v>
+        <v>-9.962766903480793</v>
       </c>
       <c r="D76" t="n">
-        <v>0.1231</v>
+        <v>0.24765</v>
       </c>
       <c r="E76" t="n">
-        <v>-9.081752948597483</v>
+        <v>-13.29778867378163</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1231</v>
+        <v>0.24765</v>
       </c>
       <c r="G76" t="n">
-        <v>-22.37963908698005</v>
+        <v>-1.821539730668298</v>
       </c>
       <c r="H76" t="n">
-        <v>0.30905</v>
+        <v>0.24765</v>
       </c>
       <c r="I76" t="n">
-        <v>-8.28012279847559</v>
+        <v>-0.5320601932502599</v>
       </c>
     </row>
     <row r="77">
@@ -2638,28 +2638,28 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>0.12615</v>
+        <v>0.25235</v>
       </c>
       <c r="C77" t="n">
-        <v>-3.46346907525655</v>
+        <v>-9.731079339278653</v>
       </c>
       <c r="D77" t="n">
-        <v>0.12615</v>
+        <v>0.25235</v>
       </c>
       <c r="E77" t="n">
-        <v>-9.008661601923297</v>
+        <v>-12.82719422183773</v>
       </c>
       <c r="F77" t="n">
-        <v>0.12615</v>
+        <v>0.25235</v>
       </c>
       <c r="G77" t="n">
-        <v>-22.36331600032861</v>
+        <v>-1.519636897667769</v>
       </c>
       <c r="H77" t="n">
-        <v>0.31455</v>
+        <v>0.25235</v>
       </c>
       <c r="I77" t="n">
-        <v>-7.941109263351401</v>
+        <v>-0.4374140523818694</v>
       </c>
     </row>
     <row r="78">
@@ -2667,28 +2667,28 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>0.12915</v>
+        <v>0.25705</v>
       </c>
       <c r="C78" t="n">
-        <v>-3.428610556117937</v>
+        <v>-9.487293207755247</v>
       </c>
       <c r="D78" t="n">
-        <v>0.12915</v>
+        <v>0.25705</v>
       </c>
       <c r="E78" t="n">
-        <v>-8.938836907614435</v>
+        <v>-12.3548858932239</v>
       </c>
       <c r="F78" t="n">
-        <v>0.12915</v>
+        <v>0.25705</v>
       </c>
       <c r="G78" t="n">
-        <v>-22.3232814825414</v>
+        <v>-1.20196714166762</v>
       </c>
       <c r="H78" t="n">
-        <v>0.3201</v>
+        <v>0.25705</v>
       </c>
       <c r="I78" t="n">
-        <v>-7.572701986430549</v>
+        <v>-0.3401305808465844</v>
       </c>
     </row>
     <row r="79">
@@ -2696,28 +2696,28 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>0.13215</v>
+        <v>0.26175</v>
       </c>
       <c r="C79" t="n">
-        <v>-3.389807520339954</v>
+        <v>-9.209832730521004</v>
       </c>
       <c r="D79" t="n">
-        <v>0.13215</v>
+        <v>0.26175</v>
       </c>
       <c r="E79" t="n">
-        <v>-8.869930959283321</v>
+        <v>-11.85253962086899</v>
       </c>
       <c r="F79" t="n">
-        <v>0.13215</v>
+        <v>0.26175</v>
       </c>
       <c r="G79" t="n">
-        <v>-22.28668340404923</v>
+        <v>-0.8730703548934208</v>
       </c>
       <c r="H79" t="n">
-        <v>0.32565</v>
+        <v>0.26175</v>
       </c>
       <c r="I79" t="n">
-        <v>-7.172929958787893</v>
+        <v>-0.2391463388593669</v>
       </c>
     </row>
     <row r="80">
@@ -2725,28 +2725,28 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>0.1352</v>
+        <v>0.26645</v>
       </c>
       <c r="C80" t="n">
-        <v>-3.34806903031872</v>
+        <v>-8.912812902784054</v>
       </c>
       <c r="D80" t="n">
-        <v>0.1352</v>
+        <v>0.26645</v>
       </c>
       <c r="E80" t="n">
-        <v>-8.798728146007837</v>
+        <v>-11.33549009076692</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1352</v>
+        <v>0.26645</v>
       </c>
       <c r="G80" t="n">
-        <v>-22.24544613250875</v>
+        <v>-0.529449593333583</v>
       </c>
       <c r="H80" t="n">
-        <v>0.33115</v>
+        <v>0.26645</v>
       </c>
       <c r="I80" t="n">
-        <v>-6.74265014082567</v>
+        <v>-0.136673281173096</v>
       </c>
     </row>
     <row r="81">
@@ -2754,28 +2754,28 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>0.1382</v>
+        <v>0.27115</v>
       </c>
       <c r="C81" t="n">
-        <v>-3.310458522827058</v>
+        <v>-8.608130649076973</v>
       </c>
       <c r="D81" t="n">
-        <v>0.1382</v>
+        <v>0.27115</v>
       </c>
       <c r="E81" t="n">
-        <v>-8.73257843560997</v>
+        <v>-10.80797689257486</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1382</v>
+        <v>0.27115</v>
       </c>
       <c r="G81" t="n">
-        <v>-22.20523979275679</v>
+        <v>-0.1892644258903944</v>
       </c>
       <c r="H81" t="n">
-        <v>0.3367</v>
+        <v>0.27115</v>
       </c>
       <c r="I81" t="n">
-        <v>-6.270464959194153</v>
+        <v>-0.02994646434667277</v>
       </c>
     </row>
     <row r="82">
@@ -2783,28 +2783,28 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>0.1412</v>
+        <v>0.27585</v>
       </c>
       <c r="C82" t="n">
-        <v>-3.273031481225599</v>
+        <v>-8.255659054450913</v>
       </c>
       <c r="D82" t="n">
-        <v>0.1412</v>
+        <v>0.27585</v>
       </c>
       <c r="E82" t="n">
-        <v>-8.656271478013663</v>
+        <v>-10.24636656905507</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1412</v>
+        <v>0.27585</v>
       </c>
       <c r="G82" t="n">
-        <v>-22.17087539980639</v>
+        <v>0.159264327264656</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3422</v>
+        <v>0.27585</v>
       </c>
       <c r="I82" t="n">
-        <v>-5.766486546639714</v>
+        <v>0.07427063458706057</v>
       </c>
     </row>
     <row r="83">
@@ -2812,28 +2812,28 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>0.1442</v>
+        <v>0.28055</v>
       </c>
       <c r="C83" t="n">
-        <v>-3.237989496196783</v>
+        <v>-7.884636323265585</v>
       </c>
       <c r="D83" t="n">
-        <v>0.1442</v>
+        <v>0.28055</v>
       </c>
       <c r="E83" t="n">
-        <v>-8.581597846600021</v>
+        <v>-9.689988079580273</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1442</v>
+        <v>0.28055</v>
       </c>
       <c r="G83" t="n">
-        <v>-22.14269659758707</v>
+        <v>0.5177317634000124</v>
       </c>
       <c r="H83" t="n">
-        <v>0.34775</v>
+        <v>0.28055</v>
       </c>
       <c r="I83" t="n">
-        <v>-5.220859858536652</v>
+        <v>0.18312433098356</v>
       </c>
     </row>
     <row r="84">
@@ -2841,28 +2841,28 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>0.14725</v>
+        <v>0.28525</v>
       </c>
       <c r="C84" t="n">
-        <v>-3.196709670901056</v>
+        <v>-7.482560602622354</v>
       </c>
       <c r="D84" t="n">
-        <v>0.14725</v>
+        <v>0.28525</v>
       </c>
       <c r="E84" t="n">
-        <v>-8.504933598901255</v>
+        <v>-9.094641446873778</v>
       </c>
       <c r="F84" t="n">
-        <v>0.14725</v>
+        <v>0.28525</v>
       </c>
       <c r="G84" t="n">
-        <v>-22.08599534921892</v>
+        <v>0.9008618573013133</v>
       </c>
       <c r="H84" t="n">
-        <v>0.35325</v>
+        <v>0.28525</v>
       </c>
       <c r="I84" t="n">
-        <v>-4.642925763269328</v>
+        <v>0.2976355270364621</v>
       </c>
     </row>
     <row r="85">
@@ -2870,28 +2870,28 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>0.15025</v>
+        <v>0.28995</v>
       </c>
       <c r="C85" t="n">
-        <v>-3.159099163409394</v>
+        <v>-7.053061462717601</v>
       </c>
       <c r="D85" t="n">
-        <v>0.15025</v>
+        <v>0.28995</v>
       </c>
       <c r="E85" t="n">
-        <v>-8.429902677385154</v>
+        <v>-8.486305433090051</v>
       </c>
       <c r="F85" t="n">
-        <v>0.15025</v>
+        <v>0.28995</v>
       </c>
       <c r="G85" t="n">
-        <v>-22.05077184644476</v>
+        <v>1.281783354984768</v>
       </c>
       <c r="H85" t="n">
-        <v>0.3588</v>
+        <v>0.28995</v>
       </c>
       <c r="I85" t="n">
-        <v>-4.016916189436617</v>
+        <v>0.4088713285514469</v>
       </c>
     </row>
     <row r="86">
@@ -2899,28 +2899,28 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>0.15325</v>
+        <v>0.29465</v>
       </c>
       <c r="C86" t="n">
-        <v>-3.1196539970157</v>
+        <v>-6.582830479497935</v>
       </c>
       <c r="D86" t="n">
-        <v>0.15325</v>
+        <v>0.29465</v>
       </c>
       <c r="E86" t="n">
-        <v>-8.357730076688716</v>
+        <v>-7.852982901539702</v>
       </c>
       <c r="F86" t="n">
-        <v>0.15325</v>
+        <v>0.29465</v>
       </c>
       <c r="G86" t="n">
-        <v>-21.99905343505442</v>
+        <v>1.673563784072632</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3643</v>
+        <v>0.29465</v>
       </c>
       <c r="I86" t="n">
-        <v>-3.354657190589363</v>
+        <v>0.5249564154862055</v>
       </c>
     </row>
     <row r="87">
@@ -2928,28 +2928,28 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>0.1563</v>
+        <v>0.29935</v>
       </c>
       <c r="C87" t="n">
-        <v>-3.080759228292616</v>
+        <v>-6.05795430054391</v>
       </c>
       <c r="D87" t="n">
-        <v>0.1563</v>
+        <v>0.29935</v>
       </c>
       <c r="E87" t="n">
-        <v>-8.270500250245847</v>
+        <v>-7.197470177315747</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1563</v>
+        <v>0.29935</v>
       </c>
       <c r="G87" t="n">
-        <v>-21.96795365943431</v>
+        <v>2.065712312530136</v>
       </c>
       <c r="H87" t="n">
-        <v>0.36985</v>
+        <v>0.29935</v>
       </c>
       <c r="I87" t="n">
-        <v>-2.637295637878395</v>
+        <v>0.6432109195824416</v>
       </c>
     </row>
     <row r="88">
@@ -2957,28 +2957,28 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>0.1593</v>
+        <v>0.30405</v>
       </c>
       <c r="C88" t="n">
-        <v>-3.043056987855852</v>
+        <v>-5.506662916271797</v>
       </c>
       <c r="D88" t="n">
-        <v>0.1593</v>
+        <v>0.30405</v>
       </c>
       <c r="E88" t="n">
-        <v>-8.195928701718621</v>
+        <v>-6.516700323219396</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1593</v>
+        <v>0.30405</v>
       </c>
       <c r="G88" t="n">
-        <v>-21.94029032310924</v>
+        <v>2.472707515563159</v>
       </c>
       <c r="H88" t="n">
-        <v>0.3754</v>
+        <v>0.30405</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.874600879889192</v>
+        <v>0.7648684309907997</v>
       </c>
     </row>
     <row r="89">
@@ -2986,28 +2986,28 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>0.1623</v>
+        <v>0.3087</v>
       </c>
       <c r="C89" t="n">
-        <v>-3.00315315673665</v>
+        <v>-4.908993690601521</v>
       </c>
       <c r="D89" t="n">
-        <v>0.1623</v>
+        <v>0.3087</v>
       </c>
       <c r="E89" t="n">
-        <v>-8.117171754848318</v>
+        <v>-5.822941088045813</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1623</v>
+        <v>0.3087</v>
       </c>
       <c r="G89" t="n">
-        <v>-21.896819366027</v>
+        <v>2.888353053782745</v>
       </c>
       <c r="H89" t="n">
-        <v>0.3809</v>
+        <v>0.3087</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.072485943397177</v>
+        <v>0.8890781978832493</v>
       </c>
     </row>
     <row r="90">
@@ -3015,28 +3015,28 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>0.16535</v>
+        <v>0.3134</v>
       </c>
       <c r="C90" t="n">
-        <v>-2.964441853903769</v>
+        <v>-4.259703911027198</v>
       </c>
       <c r="D90" t="n">
-        <v>0.16535</v>
+        <v>0.3134</v>
       </c>
       <c r="E90" t="n">
-        <v>-8.031626296031323</v>
+        <v>-5.103924722999832</v>
       </c>
       <c r="F90" t="n">
-        <v>0.16535</v>
+        <v>0.3134</v>
       </c>
       <c r="G90" t="n">
-        <v>-21.86228315111185</v>
+        <v>3.320869813110875</v>
       </c>
       <c r="H90" t="n">
-        <v>0.38645</v>
+        <v>0.3134</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2113264351911656</v>
+        <v>1.013415577549903</v>
       </c>
     </row>
     <row r="91">
@@ -3044,28 +3044,28 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>0.16835</v>
+        <v>0.3181</v>
       </c>
       <c r="C91" t="n">
-        <v>-2.926189215796395</v>
+        <v>-3.55173607994476</v>
       </c>
       <c r="D91" t="n">
-        <v>0.16835</v>
+        <v>0.3181</v>
       </c>
       <c r="E91" t="n">
-        <v>-7.951950603183273</v>
+        <v>-4.348195315603617</v>
       </c>
       <c r="F91" t="n">
-        <v>0.16835</v>
+        <v>0.3181</v>
       </c>
       <c r="G91" t="n">
-        <v>-21.81898401599435</v>
+        <v>3.757865114769637</v>
       </c>
       <c r="H91" t="n">
-        <v>0.39195</v>
+        <v>0.3181</v>
       </c>
       <c r="I91" t="n">
-        <v>0.7033074021143132</v>
+        <v>1.143708220012771</v>
       </c>
     </row>
     <row r="92">
@@ -3073,28 +3073,28 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>0.17135</v>
+        <v>0.3228</v>
       </c>
       <c r="C92" t="n">
-        <v>-2.887294447073311</v>
+        <v>-2.788316481973211</v>
       </c>
       <c r="D92" t="n">
-        <v>0.17135</v>
+        <v>0.3228</v>
       </c>
       <c r="E92" t="n">
-        <v>-7.867936387662523</v>
+        <v>-3.573793672908882</v>
       </c>
       <c r="F92" t="n">
-        <v>0.17135</v>
+        <v>0.3228</v>
       </c>
       <c r="G92" t="n">
-        <v>-21.76331369941471</v>
+        <v>4.213204035015505</v>
       </c>
       <c r="H92" t="n">
-        <v>0.3975</v>
+        <v>0.3228</v>
       </c>
       <c r="I92" t="n">
-        <v>1.683241622070104</v>
+        <v>1.275872516497305</v>
       </c>
     </row>
     <row r="93">
@@ -3102,28 +3102,28 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>0.17435</v>
+        <v>0.3275</v>
       </c>
       <c r="C93" t="n">
-        <v>-2.852711126770002</v>
+        <v>-1.96783197480305</v>
       </c>
       <c r="D93" t="n">
-        <v>0.17435</v>
+        <v>0.3275</v>
       </c>
       <c r="E93" t="n">
-        <v>-7.782288845959109</v>
+        <v>-2.763581028216497</v>
       </c>
       <c r="F93" t="n">
-        <v>0.17435</v>
+        <v>0.3275</v>
       </c>
       <c r="G93" t="n">
-        <v>-21.70850249265883</v>
+        <v>4.682776130887492</v>
       </c>
       <c r="H93" t="n">
-        <v>0.403</v>
+        <v>0.3275</v>
       </c>
       <c r="I93" t="n">
-        <v>2.69265527986278</v>
+        <v>1.411865196207977</v>
       </c>
     </row>
     <row r="94">
@@ -3131,28 +3131,28 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>0.1774</v>
+        <v>0.3322</v>
       </c>
       <c r="C94" t="n">
-        <v>-2.815834482839153</v>
+        <v>-1.071328136297633</v>
       </c>
       <c r="D94" t="n">
-        <v>0.1774</v>
+        <v>0.3322</v>
       </c>
       <c r="E94" t="n">
-        <v>-7.692404864469413</v>
+        <v>-1.921977379254134</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1774</v>
+        <v>0.3322</v>
       </c>
       <c r="G94" t="n">
-        <v>-21.68169826615752</v>
+        <v>5.161612060895443</v>
       </c>
       <c r="H94" t="n">
-        <v>0.40855</v>
+        <v>0.3322</v>
       </c>
       <c r="I94" t="n">
-        <v>3.783394479827563</v>
+        <v>1.55151610877918</v>
       </c>
     </row>
     <row r="95">
@@ -3160,28 +3160,28 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>0.1804</v>
+        <v>0.3369</v>
       </c>
       <c r="C95" t="n">
-        <v>-2.777673577676882</v>
+        <v>-0.1046526073289049</v>
       </c>
       <c r="D95" t="n">
-        <v>0.1804</v>
+        <v>0.3369</v>
       </c>
       <c r="E95" t="n">
-        <v>-7.602878173082175</v>
+        <v>-1.055928436736701</v>
       </c>
       <c r="F95" t="n">
-        <v>0.1804</v>
+        <v>0.3369</v>
       </c>
       <c r="G95" t="n">
-        <v>-21.61331312418624</v>
+        <v>5.643208736175701</v>
       </c>
       <c r="H95" t="n">
-        <v>0.41405</v>
+        <v>0.3369</v>
       </c>
       <c r="I95" t="n">
-        <v>4.919381189030358</v>
+        <v>1.694272265522693</v>
       </c>
     </row>
     <row r="96">
@@ -3189,28 +3189,28 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>0.1834</v>
+        <v>0.3416</v>
       </c>
       <c r="C96" t="n">
-        <v>-2.742539859702964</v>
+        <v>0.9469145356773357</v>
       </c>
       <c r="D96" t="n">
-        <v>0.1834</v>
+        <v>0.3416</v>
       </c>
       <c r="E96" t="n">
-        <v>-7.516975424162721</v>
+        <v>-0.1464913532599012</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1834</v>
+        <v>0.3416</v>
       </c>
       <c r="G96" t="n">
-        <v>-21.60455020398388</v>
+        <v>6.145664375735614</v>
       </c>
       <c r="H96" t="n">
-        <v>0.4196</v>
+        <v>0.3416</v>
       </c>
       <c r="I96" t="n">
-        <v>6.132751422554978</v>
+        <v>1.841920245277383</v>
       </c>
     </row>
     <row r="97">
@@ -3218,28 +3218,28 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>0.18645</v>
+        <v>0.3463</v>
       </c>
       <c r="C97" t="n">
-        <v>-2.697682449548274</v>
+        <v>2.070468154245078</v>
       </c>
       <c r="D97" t="n">
-        <v>0.18645</v>
+        <v>0.3463</v>
       </c>
       <c r="E97" t="n">
-        <v>-7.432552877096305</v>
+        <v>0.8069652994230763</v>
       </c>
       <c r="F97" t="n">
-        <v>0.18645</v>
+        <v>0.3463</v>
       </c>
       <c r="G97" t="n">
-        <v>-21.54028878916665</v>
+        <v>6.645175220338398</v>
       </c>
       <c r="H97" t="n">
-        <v>0.42515</v>
+        <v>0.3463</v>
       </c>
       <c r="I97" t="n">
-        <v>7.426933022010365</v>
+        <v>1.993183920301201</v>
       </c>
     </row>
     <row r="98">
@@ -3247,28 +3247,28 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>0.18945</v>
+        <v>0.351</v>
       </c>
       <c r="C98" t="n">
-        <v>-2.661906600958645</v>
+        <v>3.2287043324671</v>
       </c>
       <c r="D98" t="n">
-        <v>0.18945</v>
+        <v>0.351</v>
       </c>
       <c r="E98" t="n">
-        <v>-7.336135590875955</v>
+        <v>1.777290106699404</v>
       </c>
       <c r="F98" t="n">
-        <v>0.18945</v>
+        <v>0.351</v>
       </c>
       <c r="G98" t="n">
-        <v>-21.48410300669275</v>
+        <v>7.165913128590478</v>
       </c>
       <c r="H98" t="n">
-        <v>0.43065</v>
+        <v>0.351</v>
       </c>
       <c r="I98" t="n">
-        <v>8.766105042583092</v>
+        <v>2.145340884744452</v>
       </c>
     </row>
     <row r="99">
@@ -3276,28 +3276,28 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>0.19245</v>
+        <v>0.3557</v>
       </c>
       <c r="C99" t="n">
-        <v>-2.621819303949239</v>
+        <v>4.449853060759678</v>
       </c>
       <c r="D99" t="n">
-        <v>0.19245</v>
+        <v>0.3557</v>
       </c>
       <c r="E99" t="n">
-        <v>-7.244005785885097</v>
+        <v>2.802819783553971</v>
       </c>
       <c r="F99" t="n">
-        <v>0.19245</v>
+        <v>0.3557</v>
       </c>
       <c r="G99" t="n">
-        <v>-21.43169730744339</v>
+        <v>7.699534514779992</v>
       </c>
       <c r="H99" t="n">
-        <v>0.4362</v>
+        <v>0.3557</v>
       </c>
       <c r="I99" t="n">
-        <v>10.17349111117373</v>
+        <v>2.301538920370847</v>
       </c>
     </row>
     <row r="100">
@@ -3305,28 +3305,28 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>0.1955</v>
+        <v>0.3604</v>
       </c>
       <c r="C100" t="n">
-        <v>-2.585126125908594</v>
+        <v>5.75831311655402</v>
       </c>
       <c r="D100" t="n">
-        <v>0.1955</v>
+        <v>0.3604</v>
       </c>
       <c r="E100" t="n">
-        <v>-7.144168722969795</v>
+        <v>3.869392296451182</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1955</v>
+        <v>0.3604</v>
       </c>
       <c r="G100" t="n">
-        <v>-21.37259055156871</v>
+        <v>8.230947304751663</v>
       </c>
       <c r="H100" t="n">
-        <v>0.4417</v>
+        <v>0.3604</v>
       </c>
       <c r="I100" t="n">
-        <v>11.64592047429401</v>
+        <v>2.464457895438684</v>
       </c>
     </row>
     <row r="101">
@@ -3334,28 +3334,28 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>0.1985</v>
+        <v>0.3651</v>
       </c>
       <c r="C101" t="n">
-        <v>-2.548799879648354</v>
+        <v>7.142994146472305</v>
       </c>
       <c r="D101" t="n">
-        <v>0.1985</v>
+        <v>0.3651</v>
       </c>
       <c r="E101" t="n">
-        <v>-7.047802478192652</v>
+        <v>4.983682744000172</v>
       </c>
       <c r="F101" t="n">
-        <v>0.1985</v>
+        <v>0.3651</v>
       </c>
       <c r="G101" t="n">
-        <v>-21.30953189050474</v>
+        <v>8.773955224867018</v>
       </c>
       <c r="H101" t="n">
-        <v>0.44725</v>
+        <v>0.3651</v>
       </c>
       <c r="I101" t="n">
-        <v>13.20670245488472</v>
+        <v>2.626015667581671</v>
       </c>
     </row>
     <row r="102">
@@ -3363,28 +3363,28 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>0.2015</v>
+        <v>0.3698</v>
       </c>
       <c r="C102" t="n">
-        <v>-2.511097639211591</v>
+        <v>8.599258366374714</v>
       </c>
       <c r="D102" t="n">
-        <v>0.2015</v>
+        <v>0.3698</v>
       </c>
       <c r="E102" t="n">
-        <v>-6.94281022951332</v>
+        <v>6.146502962518267</v>
       </c>
       <c r="F102" t="n">
-        <v>0.2015</v>
+        <v>0.3698</v>
       </c>
       <c r="G102" t="n">
-        <v>-21.25403339588986</v>
+        <v>9.325184030904358</v>
       </c>
       <c r="H102" t="n">
-        <v>0.45275</v>
+        <v>0.3698</v>
       </c>
       <c r="I102" t="n">
-        <v>14.82344394974139</v>
+        <v>2.79318840178966</v>
       </c>
     </row>
     <row r="103">
@@ -3392,28 +3392,28 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>0.2045</v>
+        <v>0.3745</v>
       </c>
       <c r="C103" t="n">
-        <v>-2.473670597610132</v>
+        <v>10.12246799212143</v>
       </c>
       <c r="D103" t="n">
-        <v>0.2045</v>
+        <v>0.3745</v>
       </c>
       <c r="E103" t="n">
-        <v>-6.840982550312898</v>
+        <v>7.331423169674709</v>
       </c>
       <c r="F103" t="n">
-        <v>0.2045</v>
+        <v>0.3745</v>
       </c>
       <c r="G103" t="n">
-        <v>-21.18942833714311</v>
+        <v>9.881198128747032</v>
       </c>
       <c r="H103" t="n">
-        <v>0.4583</v>
+        <v>0.3745</v>
       </c>
       <c r="I103" t="n">
-        <v>16.5275097095858</v>
+        <v>2.963423842578558</v>
       </c>
     </row>
     <row r="104">
@@ -3421,28 +3421,28 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>0.20755</v>
+        <v>0.3792</v>
       </c>
       <c r="C104" t="n">
-        <v>-2.438628612581315</v>
+        <v>11.73399715931336</v>
       </c>
       <c r="D104" t="n">
-        <v>0.20755</v>
+        <v>0.3792</v>
       </c>
       <c r="E104" t="n">
-        <v>-6.734867389882984</v>
+        <v>8.570646206056805</v>
       </c>
       <c r="F104" t="n">
-        <v>0.20755</v>
+        <v>0.3792</v>
       </c>
       <c r="G104" t="n">
-        <v>-21.12894700555042</v>
+        <v>10.44604661146109</v>
       </c>
       <c r="H104" t="n">
-        <v>0.4638</v>
+        <v>0.3792</v>
       </c>
       <c r="I104" t="n">
-        <v>18.28659232725371</v>
+        <v>3.136466764399957</v>
       </c>
     </row>
     <row r="105">
@@ -3450,28 +3450,28 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>0.21055</v>
+        <v>0.3839</v>
       </c>
       <c r="C105" t="n">
-        <v>-2.398541315571909</v>
+        <v>13.39250909626951</v>
       </c>
       <c r="D105" t="n">
-        <v>0.21055</v>
+        <v>0.3839</v>
       </c>
       <c r="E105" t="n">
-        <v>-6.636612611707138</v>
+        <v>9.853798607609818</v>
       </c>
       <c r="F105" t="n">
-        <v>0.21055</v>
+        <v>0.3839</v>
       </c>
       <c r="G105" t="n">
-        <v>-21.06898113985197</v>
+        <v>11.01610983524506</v>
       </c>
       <c r="H105" t="n">
-        <v>0.46935</v>
+        <v>0.3839</v>
       </c>
       <c r="I105" t="n">
-        <v>20.13394186635182</v>
+        <v>3.313848520544311</v>
       </c>
     </row>
     <row r="106">
@@ -3479,28 +3479,28 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>0.21355</v>
+        <v>0.3886</v>
       </c>
       <c r="C106" t="n">
-        <v>-2.364049728213703</v>
+        <v>15.1371225039953</v>
       </c>
       <c r="D106" t="n">
-        <v>0.21355</v>
+        <v>0.3886</v>
       </c>
       <c r="E106" t="n">
-        <v>-6.524627685308277</v>
+        <v>11.18079017029849</v>
       </c>
       <c r="F106" t="n">
-        <v>0.21355</v>
+        <v>0.3886</v>
       </c>
       <c r="G106" t="n">
-        <v>-20.98032100603996</v>
+        <v>11.59488474411053</v>
       </c>
       <c r="H106" t="n">
-        <v>0.47485</v>
+        <v>0.3886</v>
       </c>
       <c r="I106" t="n">
-        <v>22.01137071556839</v>
+        <v>3.496292250065447</v>
       </c>
     </row>
     <row r="107">
@@ -3508,28 +3508,28 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>0.2166</v>
+        <v>0.3933</v>
       </c>
       <c r="C107" t="n">
-        <v>-2.327998680788768</v>
+        <v>16.95291581612784</v>
       </c>
       <c r="D107" t="n">
-        <v>0.2166</v>
+        <v>0.3933</v>
       </c>
       <c r="E107" t="n">
-        <v>-6.410907349840337</v>
+        <v>12.55315436272222</v>
       </c>
       <c r="F107" t="n">
-        <v>0.2166</v>
+        <v>0.3933</v>
       </c>
       <c r="G107" t="n">
-        <v>-20.91794963283499</v>
+        <v>12.18089894057894</v>
       </c>
       <c r="H107" t="n">
-        <v>0.4804</v>
+        <v>0.3933</v>
       </c>
       <c r="I107" t="n">
-        <v>23.99531974278278</v>
+        <v>3.683840490554766</v>
       </c>
     </row>
     <row r="108">
@@ -3537,28 +3537,28 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>0.2196</v>
+        <v>0.398</v>
       </c>
       <c r="C108" t="n">
-        <v>-2.291855900418732</v>
+        <v>18.85279417114314</v>
       </c>
       <c r="D108" t="n">
-        <v>0.2196</v>
+        <v>0.398</v>
       </c>
       <c r="E108" t="n">
-        <v>-6.295145356644067</v>
+        <v>13.97034996066945</v>
       </c>
       <c r="F108" t="n">
-        <v>0.2196</v>
+        <v>0.398</v>
       </c>
       <c r="G108" t="n">
-        <v>-20.8445816538859</v>
+        <v>12.77304812654137</v>
       </c>
       <c r="H108" t="n">
-        <v>0.48595</v>
+        <v>0.398</v>
       </c>
       <c r="I108" t="n">
-        <v>26.05219610022737</v>
+        <v>3.87491935113041</v>
       </c>
     </row>
     <row r="109">
@@ -3566,28 +3566,28 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>0.2226</v>
+        <v>0.4027</v>
       </c>
       <c r="C109" t="n">
-        <v>-2.25818990956644</v>
+        <v>20.83937892529415</v>
       </c>
       <c r="D109" t="n">
-        <v>0.2226</v>
+        <v>0.4027</v>
       </c>
       <c r="E109" t="n">
-        <v>-6.179689612107046</v>
+        <v>15.43255737221071</v>
       </c>
       <c r="F109" t="n">
-        <v>0.2226</v>
+        <v>0.4027</v>
       </c>
       <c r="G109" t="n">
-        <v>-20.76296622062871</v>
+        <v>13.37004395420406</v>
       </c>
       <c r="H109" t="n">
-        <v>0.49145</v>
+        <v>0.4027</v>
       </c>
       <c r="I109" t="n">
-        <v>28.1598902095245</v>
+        <v>4.067444489813708</v>
       </c>
     </row>
     <row r="110">
@@ -3595,28 +3595,28 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>0.22565</v>
+        <v>0.4074</v>
       </c>
       <c r="C110" t="n">
-        <v>-2.222230595086607</v>
+        <v>22.87435794873019</v>
       </c>
       <c r="D110" t="n">
-        <v>0.22565</v>
+        <v>0.4074</v>
       </c>
       <c r="E110" t="n">
-        <v>-6.061579712523198</v>
+        <v>16.94347496279159</v>
       </c>
       <c r="F110" t="n">
-        <v>0.22565</v>
+        <v>0.4074</v>
       </c>
       <c r="G110" t="n">
-        <v>-20.67636795039371</v>
+        <v>13.96912567829473</v>
       </c>
       <c r="H110" t="n">
-        <v>0.497</v>
+        <v>0.4074</v>
       </c>
       <c r="I110" t="n">
-        <v>30.36767729380268</v>
+        <v>4.264095774862952</v>
       </c>
     </row>
     <row r="111">
@@ -3624,28 +3624,28 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>0.22865</v>
+        <v>0.4121</v>
       </c>
       <c r="C111" t="n">
-        <v>-2.183427559308624</v>
+        <v>24.98999408764131</v>
       </c>
       <c r="D111" t="n">
-        <v>0.22865</v>
+        <v>0.4121</v>
       </c>
       <c r="E111" t="n">
-        <v>-5.951942692511916</v>
+        <v>18.50653048575191</v>
       </c>
       <c r="F111" t="n">
-        <v>0.22865</v>
+        <v>0.4121</v>
       </c>
       <c r="G111" t="n">
-        <v>-20.59320611945375</v>
+        <v>14.57507859061869</v>
       </c>
       <c r="H111" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.4121</v>
       </c>
       <c r="I111" t="n">
-        <v>32.62791035469765</v>
+        <v>4.466234409202993</v>
       </c>
     </row>
     <row r="112">
@@ -3653,2250 +3653,1160 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>0.23165</v>
+        <v>0.4168</v>
       </c>
       <c r="C112" t="n">
-        <v>-2.15022023318184</v>
+        <v>27.19314319684288</v>
       </c>
       <c r="D112" t="n">
-        <v>0.23165</v>
+        <v>0.4168</v>
       </c>
       <c r="E112" t="n">
-        <v>-5.830617182005948</v>
+        <v>20.13245822128745</v>
       </c>
       <c r="F112" t="n">
-        <v>0.23165</v>
+        <v>0.4168</v>
       </c>
       <c r="G112" t="n">
-        <v>-20.51055975440805</v>
-      </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+        <v>15.18992723770898</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.4168</v>
+      </c>
+      <c r="I112" t="n">
+        <v>4.669861859242087</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>0.23465</v>
+        <v>0.4215</v>
       </c>
       <c r="C113" t="n">
-        <v>-2.114352651647109</v>
+        <v>29.46263278352269</v>
       </c>
       <c r="D113" t="n">
-        <v>0.23465</v>
+        <v>0.4215</v>
       </c>
       <c r="E113" t="n">
-        <v>-5.701482330689122</v>
+        <v>21.79329491846806</v>
       </c>
       <c r="F113" t="n">
-        <v>0.23465</v>
+        <v>0.4215</v>
       </c>
       <c r="G113" t="n">
-        <v>-20.41330852235844</v>
-      </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+        <v>15.80637098206771</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.4215</v>
+      </c>
+      <c r="I113" t="n">
+        <v>4.877530380464327</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>0.2377</v>
+        <v>0.42615</v>
       </c>
       <c r="C114" t="n">
-        <v>-2.077109075935853</v>
+        <v>31.78394456689524</v>
       </c>
       <c r="D114" t="n">
-        <v>0.2377</v>
+        <v>0.42615</v>
       </c>
       <c r="E114" t="n">
-        <v>-5.57770683090916</v>
+        <v>23.49219771852777</v>
       </c>
       <c r="F114" t="n">
-        <v>0.2377</v>
+        <v>0.42615</v>
       </c>
       <c r="G114" t="n">
-        <v>-20.31657275620308</v>
-      </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+        <v>16.42232392726692</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.42615</v>
+      </c>
+      <c r="I114" t="n">
+        <v>5.088176533084672</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>0.2407</v>
+        <v>0.43085</v>
       </c>
       <c r="C115" t="n">
-        <v>-2.041608426181528</v>
+        <v>34.18551018016548</v>
       </c>
       <c r="D115" t="n">
-        <v>0.2407</v>
+        <v>0.43085</v>
       </c>
       <c r="E115" t="n">
-        <v>-5.450868844536703</v>
+        <v>25.28067312559924</v>
       </c>
       <c r="F115" t="n">
-        <v>0.2407</v>
+        <v>0.43085</v>
       </c>
       <c r="G115" t="n">
-        <v>-20.21485415306991</v>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+        <v>17.04956525313512</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.43085</v>
+      </c>
+      <c r="I115" t="n">
+        <v>5.303671971124793</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>0.2437</v>
+        <v>0.43555</v>
       </c>
       <c r="C116" t="n">
-        <v>-2.005557378756594</v>
+        <v>36.66874112285424</v>
       </c>
       <c r="D116" t="n">
-        <v>0.2437</v>
+        <v>0.43555</v>
       </c>
       <c r="E116" t="n">
-        <v>-5.319947542707589</v>
+        <v>27.13995870034867</v>
       </c>
       <c r="F116" t="n">
-        <v>0.2437</v>
+        <v>0.43555</v>
       </c>
       <c r="G116" t="n">
-        <v>-20.09079869451898</v>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+        <v>17.68048757269973</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.43555</v>
+      </c>
+      <c r="I116" t="n">
+        <v>5.521677127057601</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>0.24675</v>
+        <v>0.44025</v>
       </c>
       <c r="C117" t="n">
-        <v>-1.97124925728859</v>
+        <v>39.23565382284838</v>
       </c>
       <c r="D117" t="n">
-        <v>0.24675</v>
+        <v>0.44025</v>
       </c>
       <c r="E117" t="n">
-        <v>-5.185045008308232</v>
+        <v>29.06770913785935</v>
       </c>
       <c r="F117" t="n">
-        <v>0.24675</v>
+        <v>0.44025</v>
       </c>
       <c r="G117" t="n">
-        <v>-19.98976737924482</v>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+        <v>18.31772893144317</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="I117" t="n">
+        <v>5.747041286302874</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>0.24975</v>
+        <v>0.44495</v>
       </c>
       <c r="C118" t="n">
-        <v>-1.935840340479367</v>
+        <v>41.88463513783841</v>
       </c>
       <c r="D118" t="n">
-        <v>0.24975</v>
+        <v>0.44495</v>
       </c>
       <c r="E118" t="n">
-        <v>-5.046008117009008</v>
+        <v>31.08052198061886</v>
       </c>
       <c r="F118" t="n">
-        <v>0.24975</v>
+        <v>0.44495</v>
       </c>
       <c r="G118" t="n">
-        <v>-19.86725831837666</v>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
+        <v>18.95319114323335</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.44495</v>
+      </c>
+      <c r="I118" t="n">
+        <v>5.974234561978413</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>0.25275</v>
+        <v>0.44965</v>
       </c>
       <c r="C119" t="n">
-        <v>-1.90134875312116</v>
+        <v>44.57858279470578</v>
       </c>
       <c r="D119" t="n">
-        <v>0.25275</v>
+        <v>0.44965</v>
       </c>
       <c r="E119" t="n">
-        <v>-4.9120243285874</v>
+        <v>33.17614212774572</v>
       </c>
       <c r="F119" t="n">
-        <v>0.25275</v>
+        <v>0.44965</v>
       </c>
       <c r="G119" t="n">
-        <v>-19.74114099624871</v>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+        <v>19.59067790155655</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.44965</v>
+      </c>
+      <c r="I119" t="n">
+        <v>6.202108439116376</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>0.2558</v>
+        <v>0.45435</v>
       </c>
       <c r="C120" t="n">
-        <v>-1.866857165762953</v>
+        <v>47.37556991659257</v>
       </c>
       <c r="D120" t="n">
-        <v>0.2558</v>
+        <v>0.45435</v>
       </c>
       <c r="E120" t="n">
-        <v>-4.772987437288176</v>
+        <v>35.38262303420535</v>
       </c>
       <c r="F120" t="n">
-        <v>0.2558</v>
+        <v>0.45435</v>
       </c>
       <c r="G120" t="n">
-        <v>-19.614164564297</v>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
+        <v>20.23564934706246</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.45435</v>
+      </c>
+      <c r="I120" t="n">
+        <v>6.436533105330175</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>0.2588</v>
+        <v>0.45905</v>
       </c>
       <c r="C121" t="n">
-        <v>-1.828971459435986</v>
+        <v>50.26047329434717</v>
       </c>
       <c r="D121" t="n">
-        <v>0.2588</v>
+        <v>0.45905</v>
       </c>
       <c r="E121" t="n">
-        <v>-4.630377644964377</v>
+        <v>37.70537694211327</v>
       </c>
       <c r="F121" t="n">
-        <v>0.2588</v>
+        <v>0.45905</v>
       </c>
       <c r="G121" t="n">
-        <v>-19.47481695088315</v>
-      </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
+        <v>20.89019137617903</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.45905</v>
+      </c>
+      <c r="I121" t="n">
+        <v>6.678529462813444</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>0.2618</v>
+        <v>0.46375</v>
       </c>
       <c r="C122" t="n">
-        <v>-1.794571605022881</v>
+        <v>53.24801285154381</v>
       </c>
       <c r="D122" t="n">
-        <v>0.2618</v>
+        <v>0.46375</v>
       </c>
       <c r="E122" t="n">
-        <v>-4.491340753665153</v>
+        <v>40.15757364061722</v>
       </c>
       <c r="F122" t="n">
-        <v>0.2618</v>
+        <v>0.46375</v>
       </c>
       <c r="G122" t="n">
-        <v>-19.32498819761943</v>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
+        <v>21.54884384825659</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.46375</v>
+      </c>
+      <c r="I122" t="n">
+        <v>6.920610895479515</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>0.2648</v>
+        <v>0.46845</v>
       </c>
       <c r="C123" t="n">
-        <v>-1.75870402348815</v>
+        <v>56.32548509249515</v>
       </c>
       <c r="D123" t="n">
-        <v>0.2648</v>
+        <v>0.46845</v>
       </c>
       <c r="E123" t="n">
-        <v>-4.340258081768787</v>
+        <v>42.77276903083339</v>
       </c>
       <c r="F123" t="n">
-        <v>0.2648</v>
+        <v>0.46845</v>
       </c>
       <c r="G123" t="n">
-        <v>-19.17790859579173</v>
-      </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+        <v>22.21056381508116</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.46845</v>
+      </c>
+      <c r="I123" t="n">
+        <v>7.169583417952634</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>0.26785</v>
+        <v>0.47315</v>
       </c>
       <c r="C124" t="n">
-        <v>-1.724487634965248</v>
+        <v>59.52152329319485</v>
       </c>
       <c r="D124" t="n">
-        <v>0.26785</v>
+        <v>0.47315</v>
       </c>
       <c r="E124" t="n">
-        <v>-4.200251403048607</v>
+        <v>45.58948023581717</v>
       </c>
       <c r="F124" t="n">
-        <v>0.26785</v>
+        <v>0.47315</v>
       </c>
       <c r="G124" t="n">
-        <v>-19.01141311194707</v>
-      </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
+        <v>22.87792797224022</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.47315</v>
+      </c>
+      <c r="I124" t="n">
+        <v>7.42098058313564</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>0.27085</v>
+        <v>0.47785</v>
       </c>
       <c r="C125" t="n">
-        <v>-1.691188575893362</v>
+        <v>62.84641123586597</v>
       </c>
       <c r="D125" t="n">
-        <v>0.27085</v>
+        <v>0.47785</v>
       </c>
       <c r="E125" t="n">
-        <v>-4.043094799410461</v>
+        <v>48.59056848886946</v>
       </c>
       <c r="F125" t="n">
-        <v>0.27085</v>
+        <v>0.47785</v>
       </c>
       <c r="G125" t="n">
-        <v>-18.86622355173165</v>
-      </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+        <v>23.5514271188933</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47785</v>
+      </c>
+      <c r="I125" t="n">
+        <v>7.675695680447965</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>0.27385</v>
+        <v>0.48255</v>
       </c>
       <c r="C126" t="n">
-        <v>-1.656696988535155</v>
+        <v>66.30599656138047</v>
       </c>
       <c r="D126" t="n">
-        <v>0.27385</v>
+        <v>0.48255</v>
       </c>
       <c r="E126" t="n">
-        <v>-3.885427781340233</v>
+        <v>51.91350473972428</v>
       </c>
       <c r="F126" t="n">
-        <v>0.27385</v>
+        <v>0.48255</v>
       </c>
       <c r="G126" t="n">
-        <v>-18.70024353378124</v>
-      </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
+        <v>24.23265635230884</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.48255</v>
+      </c>
+      <c r="I126" t="n">
+        <v>7.938067544212564</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>0.2769</v>
+        <v>0.48725</v>
       </c>
       <c r="C127" t="n">
-        <v>-1.623397929463269</v>
+        <v>69.89685134233063</v>
       </c>
       <c r="D127" t="n">
-        <v>0.2769</v>
+        <v>0.48725</v>
       </c>
       <c r="E127" t="n">
-        <v>-3.722197245960307</v>
+        <v>55.59752774371913</v>
       </c>
       <c r="F127" t="n">
-        <v>0.2769</v>
+        <v>0.48725</v>
       </c>
       <c r="G127" t="n">
-        <v>-18.5093493309418</v>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
+        <v>24.91836412805501</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.48725</v>
+      </c>
+      <c r="I127" t="n">
+        <v>8.204140178429094</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>0.2799</v>
+        <v>0.49195</v>
       </c>
       <c r="C128" t="n">
-        <v>-1.590465802171789</v>
+        <v>73.59437515849658</v>
       </c>
       <c r="D128" t="n">
-        <v>0.2799</v>
+        <v>0.49195</v>
       </c>
       <c r="E128" t="n">
-        <v>-3.560395870990213</v>
+        <v>59.75286683193995</v>
       </c>
       <c r="F128" t="n">
-        <v>0.2799</v>
+        <v>0.49195</v>
       </c>
       <c r="G128" t="n">
-        <v>-18.30917674200575</v>
-      </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
+        <v>25.61247683940799</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.49195</v>
+      </c>
+      <c r="I128" t="n">
+        <v>8.474424034194376</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>0.2829</v>
+        <v>0.49665</v>
       </c>
       <c r="C129" t="n">
-        <v>-1.555515550088074</v>
+        <v>77.39917293824438</v>
       </c>
       <c r="D129" t="n">
-        <v>0.2829</v>
+        <v>0.49665</v>
       </c>
       <c r="E129" t="n">
-        <v>-3.393286185926462</v>
+        <v>64.61495453641157</v>
       </c>
       <c r="F129" t="n">
-        <v>0.2829</v>
+        <v>0.49665</v>
       </c>
       <c r="G129" t="n">
-        <v>-18.10247491840912</v>
-      </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
+        <v>26.3119883415157</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.49665</v>
+      </c>
+      <c r="I129" t="n">
+        <v>8.750152701659054</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>0.28595</v>
+        <v>0.50135</v>
       </c>
       <c r="C130" t="n">
-        <v>-1.521482627455375</v>
+        <v>81.39956422301923</v>
       </c>
       <c r="D130" t="n">
-        <v>0.28595</v>
+        <v>0.50135</v>
       </c>
       <c r="E130" t="n">
-        <v>-3.225257754884962</v>
+        <v>70.57166820874585</v>
       </c>
       <c r="F130" t="n">
-        <v>0.28595</v>
+        <v>0.50135</v>
       </c>
       <c r="G130" t="n">
-        <v>-17.88632288675113</v>
-      </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+        <v>27.01849373164658</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.50135</v>
+      </c>
+      <c r="I130" t="n">
+        <v>9.03477172572665</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>0.28895</v>
+        <v>0.50605</v>
       </c>
       <c r="C131" t="n">
-        <v>-1.486715841261863</v>
+        <v>85.56832723634828</v>
       </c>
       <c r="D131" t="n">
-        <v>0.28895</v>
+        <v>0.50605</v>
       </c>
       <c r="E131" t="n">
-        <v>-3.056514743638548</v>
+        <v>78.53776697049977</v>
       </c>
       <c r="F131" t="n">
-        <v>0.28895</v>
+        <v>0.50605</v>
       </c>
       <c r="G131" t="n">
-        <v>-17.66759352562187</v>
-      </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
+        <v>27.73659425192116</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.50605</v>
+      </c>
+      <c r="I131" t="n">
+        <v>9.321560166955726</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>0.29195</v>
+        <v>0.51075</v>
       </c>
       <c r="C132" t="n">
-        <v>-1.452315986848758</v>
+        <v>89.91312440420167</v>
       </c>
       <c r="D132" t="n">
-        <v>0.29195</v>
+        <v>0.51075</v>
       </c>
       <c r="E132" t="n">
-        <v>-2.882310297968853</v>
+        <v>91.30416367257322</v>
       </c>
       <c r="F132" t="n">
-        <v>0.29195</v>
+        <v>0.51075</v>
       </c>
       <c r="G132" t="n">
-        <v>-17.4313383240879</v>
-      </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
+        <v>28.45948006400106</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.51075</v>
+      </c>
+      <c r="I132" t="n">
+        <v>9.616941201647906</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>0.29495</v>
+        <v>0.51545</v>
       </c>
       <c r="C133" t="n">
-        <v>-1.417640933600348</v>
+        <v>94.50674877329567</v>
       </c>
       <c r="D133" t="n">
-        <v>0.29495</v>
+        <v>0.51545</v>
       </c>
       <c r="E133" t="n">
-        <v>-2.705094407149871</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F133" t="n">
-        <v>0.29495</v>
+        <v>0.51545</v>
       </c>
       <c r="G133" t="n">
-        <v>-17.17257444517143</v>
-      </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
+        <v>29.19040271231813</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.51545</v>
+      </c>
+      <c r="I133" t="n">
+        <v>9.91491702941558</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>0.298</v>
+        <v>0.52015</v>
       </c>
       <c r="C134" t="n">
-        <v>-1.384341874528462</v>
+        <v>99.38408454607323</v>
       </c>
       <c r="D134" t="n">
-        <v>0.298</v>
+        <v>0.52015</v>
       </c>
       <c r="E134" t="n">
-        <v>-2.524407698192731</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F134" t="n">
-        <v>0.298</v>
+        <v>0.52015</v>
       </c>
       <c r="G134" t="n">
-        <v>-16.91192052464269</v>
-      </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
+        <v>29.92874869792296</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.52015</v>
+      </c>
+      <c r="I134" t="n">
+        <v>10.21778468019443</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>0.301</v>
+        <v>0.52485</v>
       </c>
       <c r="C135" t="n">
-        <v>-1.350584150731068</v>
+        <v>104.544728436957</v>
       </c>
       <c r="D135" t="n">
-        <v>0.301</v>
+        <v>0.52485</v>
       </c>
       <c r="E135" t="n">
-        <v>-2.342189745939343</v>
+        <v>97.6446053108974</v>
       </c>
       <c r="F135" t="n">
-        <v>0.301</v>
+        <v>0.52485</v>
       </c>
       <c r="G135" t="n">
-        <v>-16.64216003998208</v>
-      </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
+        <v>30.68003951136016</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.52485</v>
+      </c>
+      <c r="I135" t="n">
+        <v>10.52932999961919</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>0.304</v>
+        <v>0.52955</v>
       </c>
       <c r="C136" t="n">
-        <v>-1.317009892823877</v>
+        <v>110.066716205169</v>
       </c>
       <c r="D136" t="n">
-        <v>0.304</v>
+        <v>0.52955</v>
       </c>
       <c r="E136" t="n">
-        <v>-2.153591613284926</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F136" t="n">
-        <v>0.304</v>
+        <v>0.52955</v>
       </c>
       <c r="G136" t="n">
-        <v>-16.34318982131364</v>
-      </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
+        <v>31.44353895389046</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.52955</v>
+      </c>
+      <c r="I136" t="n">
+        <v>10.84976567564687</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>0.30705</v>
+        <v>0.53425</v>
       </c>
       <c r="C137" t="n">
-        <v>-1.282793504300975</v>
+        <v>115.7225947850697</v>
       </c>
       <c r="D137" t="n">
-        <v>0.30705</v>
+        <v>0.53425</v>
       </c>
       <c r="E137" t="n">
-        <v>-1.959889336309687</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F137" t="n">
-        <v>0.30705</v>
+        <v>0.53425</v>
       </c>
       <c r="G137" t="n">
-        <v>-16.03047384546505</v>
-      </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
+        <v>32.21335743559959</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.53425</v>
+      </c>
+      <c r="I137" t="n">
+        <v>11.17658199038478</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>0.31005</v>
+        <v>0.53895</v>
       </c>
       <c r="C138" t="n">
-        <v>-1.249035780503581</v>
+        <v>121.9785623041049</v>
       </c>
       <c r="D138" t="n">
-        <v>0.31005</v>
+        <v>0.53895</v>
       </c>
       <c r="E138" t="n">
-        <v>-1.76924954592694</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F138" t="n">
-        <v>0.31005</v>
+        <v>0.53895</v>
       </c>
       <c r="G138" t="n">
-        <v>-15.70315300261254</v>
-      </c>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
+        <v>32.99286920070926</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.53895</v>
+      </c>
+      <c r="I138" t="n">
+        <v>11.51292672559662</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>0.31305</v>
+        <v>0.5436</v>
       </c>
       <c r="C139" t="n">
-        <v>-1.216837516772914</v>
+        <v>128.6849998130684</v>
       </c>
       <c r="D139" t="n">
-        <v>0.31305</v>
+        <v>0.5436</v>
       </c>
       <c r="E139" t="n">
-        <v>-1.576108724826991</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F139" t="n">
-        <v>0.31305</v>
+        <v>0.5436</v>
       </c>
       <c r="G139" t="n">
-        <v>-15.33700039572608</v>
-      </c>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
+        <v>33.77428281256208</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.5436</v>
+      </c>
+      <c r="I139" t="n">
+        <v>11.85250431775499</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>0.3161</v>
+        <v>0.5483</v>
       </c>
       <c r="C140" t="n">
-        <v>-1.184272321261841</v>
+        <v>136.0187480376392</v>
       </c>
       <c r="D140" t="n">
-        <v>0.3161</v>
+        <v>0.5483</v>
       </c>
       <c r="E140" t="n">
-        <v>-1.371330454675565</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F140" t="n">
-        <v>0.3161</v>
+        <v>0.5483</v>
       </c>
       <c r="G140" t="n">
-        <v>-14.97548698188792</v>
-      </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
+        <v>34.58723027041415</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.5483</v>
+      </c>
+      <c r="I140" t="n">
+        <v>12.20526856324783</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>0.3191</v>
+        <v>0.553</v>
       </c>
       <c r="C141" t="n">
-        <v>-1.151890591640971</v>
+        <v>144.0449375985636</v>
       </c>
       <c r="D141" t="n">
-        <v>0.3191</v>
+        <v>0.553</v>
       </c>
       <c r="E141" t="n">
-        <v>-1.16823655215001</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F141" t="n">
-        <v>0.3191</v>
+        <v>0.553</v>
       </c>
       <c r="G141" t="n">
-        <v>-14.59369857620903</v>
-      </c>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
+        <v>35.41011641124652</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="I141" t="n">
+        <v>12.57053886061271</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>0.3221</v>
+        <v>0.5577</v>
       </c>
       <c r="C142" t="n">
-        <v>-1.117674203118069</v>
+        <v>153.0682507495485</v>
       </c>
       <c r="D142" t="n">
-        <v>0.3221</v>
+        <v>0.5577</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.958303096234553</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F142" t="n">
-        <v>0.3221</v>
+        <v>0.5577</v>
       </c>
       <c r="G142" t="n">
-        <v>-14.17685848972074</v>
-      </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
+        <v>36.24441363253776</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.5577</v>
+      </c>
+      <c r="I142" t="n">
+        <v>12.94733684524741</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>0.32515</v>
+        <v>0.5624</v>
       </c>
       <c r="C143" t="n">
-        <v>-1.083733013430472</v>
+        <v>163.2733922850319</v>
       </c>
       <c r="D143" t="n">
-        <v>0.32515</v>
+        <v>0.5624</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.7444904906352697</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F143" t="n">
-        <v>0.32515</v>
+        <v>0.5624</v>
       </c>
       <c r="G143" t="n">
-        <v>-13.74884997552357</v>
-      </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
+        <v>37.09343482861464</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.5624</v>
+      </c>
+      <c r="I143" t="n">
+        <v>13.33370578794745</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>0.32815</v>
+        <v>0.5671</v>
       </c>
       <c r="C144" t="n">
-        <v>-1.050617420248789</v>
+        <v>175.2255669417053</v>
       </c>
       <c r="D144" t="n">
-        <v>0.32815</v>
+        <v>0.5671</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.5300653877174877</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F144" t="n">
-        <v>0.32815</v>
+        <v>0.5671</v>
       </c>
       <c r="G144" t="n">
-        <v>-13.30554930646347</v>
-      </c>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
+        <v>37.93595293582786</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.5671</v>
+      </c>
+      <c r="I144" t="n">
+        <v>13.739727097875</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>0.33115</v>
+        <v>0.5718</v>
       </c>
       <c r="C145" t="n">
-        <v>-1.008787197282453</v>
+        <v>182.9672385277913</v>
       </c>
       <c r="D145" t="n">
-        <v>0.33115</v>
+        <v>0.5718</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.3323818781720058</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F145" t="n">
-        <v>0.33115</v>
+        <v>0.5718</v>
       </c>
       <c r="G145" t="n">
-        <v>-12.84145817966839</v>
-      </c>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
+        <v>38.80613984565909</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.5718</v>
+      </c>
+      <c r="I145" t="n">
+        <v>14.16518808707304</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>0.33415</v>
+        <v>0.5765</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.9760385358811764</v>
+        <v>182.9682467417347</v>
       </c>
       <c r="D146" t="n">
-        <v>0.33415</v>
+        <v>0.5765</v>
       </c>
       <c r="E146" t="n">
-        <v>-0.1086161911471174</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F146" t="n">
-        <v>0.33415</v>
+        <v>0.5765</v>
       </c>
       <c r="G146" t="n">
-        <v>-12.33355245186155</v>
-      </c>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
+        <v>39.71712443562553</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.5765</v>
+      </c>
+      <c r="I146" t="n">
+        <v>14.6107268194126</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>0.3372</v>
+        <v>0.5812</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.9436568062603066</v>
+        <v>182.968045098946</v>
       </c>
       <c r="D147" t="n">
-        <v>0.3372</v>
+        <v>0.5812</v>
       </c>
       <c r="E147" t="n">
-        <v>0.1191307284480131</v>
+        <v>97.64442490282688</v>
       </c>
       <c r="F147" t="n">
-        <v>0.3372</v>
+        <v>0.5812</v>
       </c>
       <c r="G147" t="n">
-        <v>-11.82049206511215</v>
-      </c>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
+        <v>40.62902927401607</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.5812</v>
+      </c>
+      <c r="I147" t="n">
+        <v>15.0714940094739</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>0.3402</v>
+        <v>0.5859</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.9103577471884206</v>
+        <v>182.9676418133687</v>
       </c>
       <c r="D148" t="n">
-        <v>0.3402</v>
+        <v>0.5859</v>
       </c>
       <c r="E148" t="n">
-        <v>0.343662037121025</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F148" t="n">
-        <v>0.3402</v>
+        <v>0.5859</v>
       </c>
       <c r="G148" t="n">
-        <v>-11.29248316742933</v>
-      </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
+        <v>41.57768269947577</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.5859</v>
+      </c>
+      <c r="I148" t="n">
+        <v>15.55331730727896</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>0.3432</v>
+        <v>0.5906</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.8772421540067378</v>
+        <v>182.9678434561573</v>
       </c>
       <c r="D149" t="n">
-        <v>0.3432</v>
+        <v>0.5906</v>
       </c>
       <c r="E149" t="n">
-        <v>0.553238202934025</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F149" t="n">
-        <v>0.3432</v>
+        <v>0.5906</v>
       </c>
       <c r="G149" t="n">
-        <v>-10.72272153231178</v>
-      </c>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
+        <v>42.55124418228117</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0.5906</v>
+      </c>
+      <c r="I149" t="n">
+        <v>16.05815344203225</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>0.34625</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.8426588337034292</v>
+        <v>182.96744017058</v>
       </c>
       <c r="D150" t="n">
-        <v>0.34625</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="E150" t="n">
-        <v>0.7932861103423393</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F150" t="n">
-        <v>0.34625</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="G150" t="n">
-        <v>-10.13388765910676</v>
-      </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
+        <v>43.5673211422801</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0.5953000000000001</v>
+      </c>
+      <c r="I150" t="n">
+        <v>16.57834564728148</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>0.34925</v>
+        <v>0.6</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.8078003145648157</v>
+        <v>182.9676418133687</v>
       </c>
       <c r="D151" t="n">
-        <v>0.34925</v>
+        <v>0.6</v>
       </c>
       <c r="E151" t="n">
-        <v>1.033231934864237</v>
+        <v>97.64451510686214</v>
       </c>
       <c r="F151" t="n">
-        <v>0.34925</v>
+        <v>0.6</v>
       </c>
       <c r="G151" t="n">
-        <v>-9.501582828819487</v>
-      </c>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>150</v>
-      </c>
-      <c r="B152" t="n">
-        <v>0.35225</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.773033528371304</v>
-      </c>
-      <c r="D152" t="n">
-        <v>0.35225</v>
-      </c>
-      <c r="E152" t="n">
-        <v>1.274300671136716</v>
-      </c>
-      <c r="F152" t="n">
-        <v>0.35225</v>
-      </c>
-      <c r="G152" t="n">
-        <v>-8.863779695660154</v>
-      </c>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>151</v>
-      </c>
-      <c r="B153" t="n">
-        <v>0.3553</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.7376246115620808</v>
-      </c>
-      <c r="D153" t="n">
-        <v>0.3553</v>
-      </c>
-      <c r="E153" t="n">
-        <v>1.529507887177876</v>
-      </c>
-      <c r="F153" t="n">
-        <v>0.3553</v>
-      </c>
-      <c r="G153" t="n">
-        <v>-8.159309640177057</v>
-      </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>152</v>
-      </c>
-      <c r="B154" t="n">
-        <v>0.3583</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.7026743594783658</v>
-      </c>
-      <c r="D154" t="n">
-        <v>0.3583</v>
-      </c>
-      <c r="E154" t="n">
-        <v>1.775731809214386</v>
-      </c>
-      <c r="F154" t="n">
-        <v>0.3583</v>
-      </c>
-      <c r="G154" t="n">
-        <v>-7.467038944191347</v>
-      </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>153</v>
-      </c>
-      <c r="B155" t="n">
-        <v>0.3613</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.6673571756142442</v>
-      </c>
-      <c r="D155" t="n">
-        <v>0.3613</v>
-      </c>
-      <c r="E155" t="n">
-        <v>2.029458823402506</v>
-      </c>
-      <c r="F155" t="n">
-        <v>0.3613</v>
-      </c>
-      <c r="G155" t="n">
-        <v>-6.742809362761771</v>
-      </c>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>154</v>
-      </c>
-      <c r="B156" t="n">
-        <v>0.3643</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-0.6325903894207324</v>
-      </c>
-      <c r="D156" t="n">
-        <v>0.3643</v>
-      </c>
-      <c r="E156" t="n">
-        <v>2.282726464601753</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0.3643</v>
-      </c>
-      <c r="G156" t="n">
-        <v>-5.986620895888326</v>
-      </c>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>155</v>
-      </c>
-      <c r="B157" t="n">
-        <v>0.36735</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.5954385466545786</v>
-      </c>
-      <c r="D157" t="n">
-        <v>0.36735</v>
-      </c>
-      <c r="E157" t="n">
-        <v>2.550336751342512</v>
-      </c>
-      <c r="F157" t="n">
-        <v>0.36735</v>
-      </c>
-      <c r="G157" t="n">
-        <v>-5.170810207245948</v>
-      </c>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>156</v>
-      </c>
-      <c r="B158" t="n">
-        <v>0.37035</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.5594792321747458</v>
-      </c>
-      <c r="D158" t="n">
-        <v>0.37035</v>
-      </c>
-      <c r="E158" t="n">
-        <v>2.816160587570984</v>
-      </c>
-      <c r="F158" t="n">
-        <v>0.37035</v>
-      </c>
-      <c r="G158" t="n">
-        <v>-4.3577486700396</v>
-      </c>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>157</v>
-      </c>
-      <c r="B159" t="n">
-        <v>0.37335</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.5226025882438968</v>
-      </c>
-      <c r="D159" t="n">
-        <v>0.37335</v>
-      </c>
-      <c r="E159" t="n">
-        <v>3.086629195131405</v>
-      </c>
-      <c r="F159" t="n">
-        <v>0.37335</v>
-      </c>
-      <c r="G159" t="n">
-        <v>-3.492453255548652</v>
-      </c>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>158</v>
-      </c>
-      <c r="B160" t="n">
-        <v>0.3764</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.4850838136973366</v>
-      </c>
-      <c r="D160" t="n">
-        <v>0.3764</v>
-      </c>
-      <c r="E160" t="n">
-        <v>3.360721745159609</v>
-      </c>
-      <c r="F160" t="n">
-        <v>0.3764</v>
-      </c>
-      <c r="G160" t="n">
-        <v>-2.595198955613836</v>
-      </c>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>159</v>
-      </c>
-      <c r="B161" t="n">
-        <v>0.3794</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.4464642438095569</v>
-      </c>
-      <c r="D161" t="n">
-        <v>0.3794</v>
-      </c>
-      <c r="E161" t="n">
-        <v>3.636855952916143</v>
-      </c>
-      <c r="F161" t="n">
-        <v>0.3794</v>
-      </c>
-      <c r="G161" t="n">
-        <v>-1.676295088120272</v>
-      </c>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>160</v>
-      </c>
-      <c r="B162" t="n">
-        <v>0.3824</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.4085785374825902</v>
-      </c>
-      <c r="D162" t="n">
-        <v>0.3824</v>
-      </c>
-      <c r="E162" t="n">
-        <v>3.914368279639301</v>
-      </c>
-      <c r="F162" t="n">
-        <v>0.3824</v>
-      </c>
-      <c r="G162" t="n">
-        <v>-0.7206213201697849</v>
-      </c>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>161</v>
-      </c>
-      <c r="B163" t="n">
-        <v>0.38545</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.3688581722535912</v>
-      </c>
-      <c r="D163" t="n">
-        <v>0.38545</v>
-      </c>
-      <c r="E163" t="n">
-        <v>4.202037853560896</v>
-      </c>
-      <c r="F163" t="n">
-        <v>0.38545</v>
-      </c>
-      <c r="G163" t="n">
-        <v>0.2706195944843612</v>
-      </c>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>162</v>
-      </c>
-      <c r="B164" t="n">
-        <v>0.38845</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.3290460740794906</v>
-      </c>
-      <c r="D164" t="n">
-        <v>0.38845</v>
-      </c>
-      <c r="E164" t="n">
-        <v>4.490626173460238</v>
-      </c>
-      <c r="F164" t="n">
-        <v>0.38845</v>
-      </c>
-      <c r="G164" t="n">
-        <v>1.302582314784726</v>
-      </c>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>163</v>
-      </c>
-      <c r="B165" t="n">
-        <v>0.39145</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.2890505100151868</v>
-      </c>
-      <c r="D165" t="n">
-        <v>0.39145</v>
-      </c>
-      <c r="E165" t="n">
-        <v>4.752315652788842</v>
-      </c>
-      <c r="F165" t="n">
-        <v>0.39145</v>
-      </c>
-      <c r="G165" t="n">
-        <v>2.374064086978044</v>
-      </c>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>164</v>
-      </c>
-      <c r="B166" t="n">
-        <v>0.39445</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.2484128153351716</v>
-      </c>
-      <c r="D166" t="n">
-        <v>0.39445</v>
-      </c>
-      <c r="E166" t="n">
-        <v>5.045344578247301</v>
-      </c>
-      <c r="F166" t="n">
-        <v>0.39445</v>
-      </c>
-      <c r="G166" t="n">
-        <v>3.453449669549954</v>
-      </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>165</v>
-      </c>
-      <c r="B167" t="n">
-        <v>0.3975</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.2053900640825145</v>
-      </c>
-      <c r="D167" t="n">
-        <v>0.3975</v>
-      </c>
-      <c r="E167" t="n">
-        <v>5.352205734815191</v>
-      </c>
-      <c r="F167" t="n">
-        <v>0.3975</v>
-      </c>
-      <c r="G167" t="n">
-        <v>4.598127598727614</v>
-      </c>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>166</v>
-      </c>
-      <c r="B168" t="n">
-        <v>0.4005</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.1631929093357719</v>
-      </c>
-      <c r="D168" t="n">
-        <v>0.4005</v>
-      </c>
-      <c r="E168" t="n">
-        <v>5.654983575926424</v>
-      </c>
-      <c r="F168" t="n">
-        <v>0.4005</v>
-      </c>
-      <c r="G168" t="n">
-        <v>5.754317599543656</v>
-      </c>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>167</v>
-      </c>
-      <c r="B169" t="n">
-        <v>0.4035</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.119161095686997</v>
-      </c>
-      <c r="D169" t="n">
-        <v>0.4035</v>
-      </c>
-      <c r="E169" t="n">
-        <v>5.962916602801686</v>
-      </c>
-      <c r="F169" t="n">
-        <v>0.4035</v>
-      </c>
-      <c r="G169" t="n">
-        <v>6.943153773662575</v>
-      </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>168</v>
-      </c>
-      <c r="B170" t="n">
-        <v>0.40655</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.07870686689718509</v>
-      </c>
-      <c r="D170" t="n">
-        <v>0.40655</v>
-      </c>
-      <c r="E170" t="n">
-        <v>6.279271467806306</v>
-      </c>
-      <c r="F170" t="n">
-        <v>0.40655</v>
-      </c>
-      <c r="G170" t="n">
-        <v>8.193330389197946</v>
-      </c>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>169</v>
-      </c>
-      <c r="B171" t="n">
-        <v>0.40955</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.03366599085229246</v>
-      </c>
-      <c r="D171" t="n">
-        <v>0.40955</v>
-      </c>
-      <c r="E171" t="n">
-        <v>6.591032602922186</v>
-      </c>
-      <c r="F171" t="n">
-        <v>0.40955</v>
-      </c>
-      <c r="G171" t="n">
-        <v>9.443678826698074</v>
-      </c>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>170</v>
-      </c>
-      <c r="B172" t="n">
-        <v>0.41255</v>
-      </c>
-      <c r="C172" t="n">
-        <v>0.01385167471034376</v>
-      </c>
-      <c r="D172" t="n">
-        <v>0.41255</v>
-      </c>
-      <c r="E172" t="n">
-        <v>6.911572866269883</v>
-      </c>
-      <c r="F172" t="n">
-        <v>0.41255</v>
-      </c>
-      <c r="G172" t="n">
-        <v>10.74471474380003</v>
-      </c>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>171</v>
-      </c>
-      <c r="B173" t="n">
-        <v>0.4156</v>
-      </c>
-      <c r="C173" t="n">
-        <v>0.06237840266909774</v>
-      </c>
-      <c r="D173" t="n">
-        <v>0.4156</v>
-      </c>
-      <c r="E173" t="n">
-        <v>7.238493310018607</v>
-      </c>
-      <c r="F173" t="n">
-        <v>0.4156</v>
-      </c>
-      <c r="G173" t="n">
-        <v>12.09128348156126</v>
-      </c>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>172</v>
-      </c>
-      <c r="B174" t="n">
-        <v>0.4186</v>
-      </c>
-      <c r="C174" t="n">
-        <v>0.09393453578405307</v>
-      </c>
-      <c r="D174" t="n">
-        <v>0.4186</v>
-      </c>
-      <c r="E174" t="n">
-        <v>7.569446027780782</v>
-      </c>
-      <c r="F174" t="n">
-        <v>0.4186</v>
-      </c>
-      <c r="G174" t="n">
-        <v>13.46500008975331</v>
-      </c>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>173</v>
-      </c>
-      <c r="B175" t="n">
-        <v>0.4216</v>
-      </c>
-      <c r="C175" t="n">
-        <v>0.144846320315449</v>
-      </c>
-      <c r="D175" t="n">
-        <v>0.4216</v>
-      </c>
-      <c r="E175" t="n">
-        <v>7.893559192153055</v>
-      </c>
-      <c r="F175" t="n">
-        <v>0.4216</v>
-      </c>
-      <c r="G175" t="n">
-        <v>14.85469614066728</v>
-      </c>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>174</v>
-      </c>
-      <c r="B176" t="n">
-        <v>0.4246</v>
-      </c>
-      <c r="C176" t="n">
-        <v>0.1977762296390805</v>
-      </c>
-      <c r="D176" t="n">
-        <v>0.4246</v>
-      </c>
-      <c r="E176" t="n">
-        <v>8.226604609086767</v>
-      </c>
-      <c r="F176" t="n">
-        <v>0.4246</v>
-      </c>
-      <c r="G176" t="n">
-        <v>16.29233051974706</v>
-      </c>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>175</v>
-      </c>
-      <c r="B177" t="n">
-        <v>0.42765</v>
-      </c>
-      <c r="C177" t="n">
-        <v>0.2513482695784233</v>
-      </c>
-      <c r="D177" t="n">
-        <v>0.42765</v>
-      </c>
-      <c r="E177" t="n">
-        <v>8.573124967027454</v>
-      </c>
-      <c r="F177" t="n">
-        <v>0.42765</v>
-      </c>
-      <c r="G177" t="n">
-        <v>17.77944962467541</v>
-      </c>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>176</v>
-      </c>
-      <c r="B178" t="n">
-        <v>0.43065</v>
-      </c>
-      <c r="C178" t="n">
-        <v>0.3064797695844935</v>
-      </c>
-      <c r="D178" t="n">
-        <v>0.43065</v>
-      </c>
-      <c r="E178" t="n">
-        <v>8.917399501466976</v>
-      </c>
-      <c r="F178" t="n">
-        <v>0.43065</v>
-      </c>
-      <c r="G178" t="n">
-        <v>19.28461003590271</v>
-      </c>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>177</v>
-      </c>
-      <c r="B179" t="n">
-        <v>0.43365</v>
-      </c>
-      <c r="C179" t="n">
-        <v>0.3619782013709701</v>
-      </c>
-      <c r="D179" t="n">
-        <v>0.43365</v>
-      </c>
-      <c r="E179" t="n">
-        <v>9.261010497144794</v>
-      </c>
-      <c r="F179" t="n">
-        <v>0.43365</v>
-      </c>
-      <c r="G179" t="n">
-        <v>20.86520028965614</v>
-      </c>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>178</v>
-      </c>
-      <c r="B180" t="n">
-        <v>0.4367</v>
-      </c>
-      <c r="C180" t="n">
-        <v>0.4203203544555968</v>
-      </c>
-      <c r="D180" t="n">
-        <v>0.4367</v>
-      </c>
-      <c r="E180" t="n">
-        <v>9.616616231976545</v>
-      </c>
-      <c r="F180" t="n">
-        <v>0.4367</v>
-      </c>
-      <c r="G180" t="n">
-        <v>22.44596236537431</v>
-      </c>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>179</v>
-      </c>
-      <c r="B181" t="n">
-        <v>0.4397</v>
-      </c>
-      <c r="C181" t="n">
-        <v>0.4808640982226624</v>
-      </c>
-      <c r="D181" t="n">
-        <v>0.4397</v>
-      </c>
-      <c r="E181" t="n">
-        <v>9.971813635262631</v>
-      </c>
-      <c r="F181" t="n">
-        <v>0.4397</v>
-      </c>
-      <c r="G181" t="n">
-        <v>24.04356299363818</v>
-      </c>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>180</v>
-      </c>
-      <c r="B182" t="n">
-        <v>0.4427</v>
-      </c>
-      <c r="C182" t="n">
-        <v>0.5427838361662519</v>
-      </c>
-      <c r="D182" t="n">
-        <v>0.4427</v>
-      </c>
-      <c r="E182" t="n">
-        <v>10.33114539544859</v>
-      </c>
-      <c r="F182" t="n">
-        <v>0.4427</v>
-      </c>
-      <c r="G182" t="n">
-        <v>25.67655894664095</v>
-      </c>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>181</v>
-      </c>
-      <c r="B183" t="n">
-        <v>0.44575</v>
-      </c>
-      <c r="C183" t="n">
-        <v>0.6066299659569756</v>
-      </c>
-      <c r="D183" t="n">
-        <v>0.44575</v>
-      </c>
-      <c r="E183" t="n">
-        <v>10.69946044963918</v>
-      </c>
-      <c r="F183" t="n">
-        <v>0.44575</v>
-      </c>
-      <c r="G183" t="n">
-        <v>27.36178877692833</v>
-      </c>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>182</v>
-      </c>
-      <c r="B184" t="n">
-        <v>0.44875</v>
-      </c>
-      <c r="C184" t="n">
-        <v>0.6713934251987151</v>
-      </c>
-      <c r="D184" t="n">
-        <v>0.44875</v>
-      </c>
-      <c r="E184" t="n">
-        <v>11.06374322981634</v>
-      </c>
-      <c r="F184" t="n">
-        <v>0.44875</v>
-      </c>
-      <c r="G184" t="n">
-        <v>29.03344467200029</v>
-      </c>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>183</v>
-      </c>
-      <c r="B185" t="n">
-        <v>0.45175</v>
-      </c>
-      <c r="C185" t="n">
-        <v>0.7395510034092146</v>
-      </c>
-      <c r="D185" t="n">
-        <v>0.45175</v>
-      </c>
-      <c r="E185" t="n">
-        <v>11.43501868771301</v>
-      </c>
-      <c r="F185" t="n">
-        <v>0.45175</v>
-      </c>
-      <c r="G185" t="n">
-        <v>30.74977427790778</v>
-      </c>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>184</v>
-      </c>
-      <c r="B186" t="n">
-        <v>0.45475</v>
-      </c>
-      <c r="C186" t="n">
-        <v>0.8092680416864416</v>
-      </c>
-      <c r="D186" t="n">
-        <v>0.45475</v>
-      </c>
-      <c r="E186" t="n">
-        <v>11.80813163756519</v>
-      </c>
-      <c r="F186" t="n">
-        <v>0.45475</v>
-      </c>
-      <c r="G186" t="n">
-        <v>32.49187717852806</v>
-      </c>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>185</v>
-      </c>
-      <c r="B187" t="n">
-        <v>0.4578</v>
-      </c>
-      <c r="C187" t="n">
-        <v>0.882654397767733</v>
-      </c>
-      <c r="D187" t="n">
-        <v>0.4578</v>
-      </c>
-      <c r="E187" t="n">
-        <v>12.19232058059355</v>
-      </c>
-      <c r="F187" t="n">
-        <v>0.4578</v>
-      </c>
-      <c r="G187" t="n">
-        <v>34.28140294141988</v>
-      </c>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>186</v>
-      </c>
-      <c r="B188" t="n">
-        <v>0.4608</v>
-      </c>
-      <c r="C188" t="n">
-        <v>0.9564994185745326</v>
-      </c>
-      <c r="D188" t="n">
-        <v>0.4608</v>
-      </c>
-      <c r="E188" t="n">
-        <v>12.57002726033446</v>
-      </c>
-      <c r="F188" t="n">
-        <v>0.4608</v>
-      </c>
-      <c r="G188" t="n">
-        <v>36.05838570088481</v>
-      </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>187</v>
-      </c>
-      <c r="B189" t="n">
-        <v>0.4638</v>
-      </c>
-      <c r="C189" t="n">
-        <v>1.034380688965803</v>
-      </c>
-      <c r="D189" t="n">
-        <v>0.4638</v>
-      </c>
-      <c r="E189" t="n">
-        <v>12.95692139985286</v>
-      </c>
-      <c r="F189" t="n">
-        <v>0.4638</v>
-      </c>
-      <c r="G189" t="n">
-        <v>37.88691504977533</v>
-      </c>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>188</v>
-      </c>
-      <c r="B190" t="n">
-        <v>0.46685</v>
-      </c>
-      <c r="C190" t="n">
-        <v>1.074651451865412</v>
-      </c>
-      <c r="D190" t="n">
-        <v>0.46685</v>
-      </c>
-      <c r="E190" t="n">
-        <v>13.35239050183024</v>
-      </c>
-      <c r="F190" t="n">
-        <v>0.46685</v>
-      </c>
-      <c r="G190" t="n">
-        <v>39.75376069680554</v>
-      </c>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>189</v>
-      </c>
-      <c r="B191" t="n">
-        <v>0.46985</v>
-      </c>
-      <c r="C191" t="n">
-        <v>1.162348147382555</v>
-      </c>
-      <c r="D191" t="n">
-        <v>0.46985</v>
-      </c>
-      <c r="E191" t="n">
-        <v>13.74612419473855</v>
-      </c>
-      <c r="F191" t="n">
-        <v>0.46985</v>
-      </c>
-      <c r="G191" t="n">
-        <v>41.62576100277832</v>
-      </c>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>190</v>
-      </c>
-      <c r="B192" t="n">
-        <v>0.47285</v>
-      </c>
-      <c r="C192" t="n">
-        <v>1.249402712283987</v>
-      </c>
-      <c r="D192" t="n">
-        <v>0.47285</v>
-      </c>
-      <c r="E192" t="n">
-        <v>14.14123600661347</v>
-      </c>
-      <c r="F192" t="n">
-        <v>0.47285</v>
-      </c>
-      <c r="G192" t="n">
-        <v>43.50497783127067</v>
-      </c>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>191</v>
-      </c>
-      <c r="B193" t="n">
-        <v>0.4759</v>
-      </c>
-      <c r="C193" t="n">
-        <v>1.341502589166008</v>
-      </c>
-      <c r="D193" t="n">
-        <v>0.4759</v>
-      </c>
-      <c r="E193" t="n">
-        <v>14.5469644386757</v>
-      </c>
-      <c r="F193" t="n">
-        <v>0.4759</v>
-      </c>
-      <c r="G193" t="n">
-        <v>45.44433234742621</v>
-      </c>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>192</v>
-      </c>
-      <c r="B194" t="n">
-        <v>0.4789</v>
-      </c>
-      <c r="C194" t="n">
-        <v>1.43424459666374</v>
-      </c>
-      <c r="D194" t="n">
-        <v>0.4789</v>
-      </c>
-      <c r="E194" t="n">
-        <v>14.95595952310326</v>
-      </c>
-      <c r="F194" t="n">
-        <v>0.4789</v>
-      </c>
-      <c r="G194" t="n">
-        <v>47.38781059073581</v>
-      </c>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>193</v>
-      </c>
-      <c r="B195" t="n">
-        <v>0.4819</v>
-      </c>
-      <c r="C195" t="n">
-        <v>1.531389785526349</v>
-      </c>
-      <c r="D195" t="n">
-        <v>0.4819</v>
-      </c>
-      <c r="E195" t="n">
-        <v>15.3673025139184</v>
-      </c>
-      <c r="F195" t="n">
-        <v>0.4819</v>
-      </c>
-      <c r="G195" t="n">
-        <v>49.35431297732217</v>
-      </c>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>194</v>
-      </c>
-      <c r="B196" t="n">
-        <v>0.4849</v>
-      </c>
-      <c r="C196" t="n">
-        <v>1.629635769730179</v>
-      </c>
-      <c r="D196" t="n">
-        <v>0.4849</v>
-      </c>
-      <c r="E196" t="n">
-        <v>15.77726738576692</v>
-      </c>
-      <c r="F196" t="n">
-        <v>0.4849</v>
-      </c>
-      <c r="G196" t="n">
-        <v>51.3151452390717</v>
-      </c>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>195</v>
-      </c>
-      <c r="B197" t="n">
-        <v>0.48795</v>
-      </c>
-      <c r="C197" t="n">
-        <v>1.734578258926425</v>
-      </c>
-      <c r="D197" t="n">
-        <v>0.48795</v>
-      </c>
-      <c r="E197" t="n">
-        <v>16.20157490315695</v>
-      </c>
-      <c r="F197" t="n">
-        <v>0.48795</v>
-      </c>
-      <c r="G197" t="n">
-        <v>53.34883001387609</v>
-      </c>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>196</v>
-      </c>
-      <c r="B198" t="n">
-        <v>0.49095</v>
-      </c>
-      <c r="C198" t="n">
-        <v>1.841538872914908</v>
-      </c>
-      <c r="D198" t="n">
-        <v>0.49095</v>
-      </c>
-      <c r="E198" t="n">
-        <v>16.62251368529524</v>
-      </c>
-      <c r="F198" t="n">
-        <v>0.49095</v>
-      </c>
-      <c r="G198" t="n">
-        <v>55.37254911472486</v>
-      </c>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>197</v>
-      </c>
-      <c r="B199" t="n">
-        <v>0.49395</v>
-      </c>
-      <c r="C199" t="n">
-        <v>1.952810935323166</v>
-      </c>
-      <c r="D199" t="n">
-        <v>0.49395</v>
-      </c>
-      <c r="E199" t="n">
-        <v>17.0532013830863</v>
-      </c>
-      <c r="F199" t="n">
-        <v>0.49395</v>
-      </c>
-      <c r="G199" t="n">
-        <v>57.42272879814543</v>
-      </c>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>198</v>
-      </c>
-      <c r="B200" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="C200" t="n">
-        <v>2.069403508547317</v>
-      </c>
-      <c r="D200" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="E200" t="n">
-        <v>17.48945259818706</v>
-      </c>
-      <c r="F200" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="G200" t="n">
-        <v>59.5079601623754</v>
-      </c>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>199</v>
-      </c>
-      <c r="B201" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C201" t="n">
-        <v>2.186363013551876</v>
-      </c>
-      <c r="D201" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E201" t="n">
-        <v>17.916924685056</v>
-      </c>
-      <c r="F201" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G201" t="n">
-        <v>61.57137013708187</v>
-      </c>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
+        <v>44.61407304974912</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I151" t="n">
+        <v>16.98564308495108</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
